--- a/Exercícios/tabela_periodica_color.xlsx
+++ b/Exercícios/tabela_periodica_color.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48629E5-9004-417F-B4F6-B26B91412AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabela_periodica" sheetId="1" r:id="rId1"/>
@@ -1604,305 +1604,305 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2213,80 +2213,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="44">
+      <c r="D1" s="65">
         <v>1</v>
       </c>
-      <c r="E1" s="44">
+      <c r="E1" s="65">
         <v>2</v>
       </c>
-      <c r="F1" s="44">
+      <c r="F1" s="65">
         <v>3</v>
       </c>
-      <c r="G1" s="44">
+      <c r="G1" s="65">
         <v>4</v>
       </c>
-      <c r="H1" s="44">
+      <c r="H1" s="65">
         <v>5</v>
       </c>
-      <c r="I1" s="44">
+      <c r="I1" s="65">
         <v>6</v>
       </c>
-      <c r="J1" s="44">
+      <c r="J1" s="65">
         <v>7</v>
       </c>
-      <c r="K1" s="44">
+      <c r="K1" s="65">
         <v>8</v>
       </c>
-      <c r="L1" s="44">
+      <c r="L1" s="65">
         <v>9</v>
       </c>
-      <c r="M1" s="44">
+      <c r="M1" s="65">
         <v>10</v>
       </c>
-      <c r="N1" s="44">
+      <c r="N1" s="65">
         <v>11</v>
       </c>
-      <c r="O1" s="44">
+      <c r="O1" s="65">
         <v>12</v>
       </c>
-      <c r="P1" s="44">
+      <c r="P1" s="65">
         <v>13</v>
       </c>
-      <c r="Q1" s="44">
+      <c r="Q1" s="65">
         <v>14</v>
       </c>
-      <c r="R1" s="44">
+      <c r="R1" s="65">
         <v>15</v>
       </c>
-      <c r="S1" s="44">
+      <c r="S1" s="65">
         <v>16</v>
       </c>
-      <c r="T1" s="44">
+      <c r="T1" s="65">
         <v>17</v>
       </c>
-      <c r="U1" s="44">
+      <c r="U1" s="65">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
     </row>
     <row r="3" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="6"/>
@@ -2309,2123 +2309,2123 @@
       <c r="U3" s="6"/>
     </row>
     <row r="4" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44">
+      <c r="A4" s="65"/>
+      <c r="B4" s="65">
         <v>1</v>
       </c>
       <c r="C4" s="7"/>
-      <c r="D4" s="65">
+      <c r="D4" s="67">
         <v>1</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="126" t="s">
         <v>228</v>
       </c>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="U4" s="73">
+      <c r="G4" s="126"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="126"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="126"/>
+      <c r="N4" s="126"/>
+      <c r="O4" s="126"/>
+      <c r="U4" s="107">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+      <c r="A5" s="65"/>
+      <c r="B5" s="65"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="46"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="U5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="126"/>
+      <c r="M5" s="126"/>
+      <c r="N5" s="126"/>
+      <c r="O5" s="126"/>
+      <c r="U5" s="90"/>
     </row>
     <row r="6" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
+      <c r="A6" s="65"/>
+      <c r="B6" s="65"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="U6" s="64" t="s">
+      <c r="F6" s="126"/>
+      <c r="G6" s="126"/>
+      <c r="H6" s="126"/>
+      <c r="I6" s="126"/>
+      <c r="J6" s="126"/>
+      <c r="K6" s="126"/>
+      <c r="L6" s="126"/>
+      <c r="M6" s="126"/>
+      <c r="N6" s="126"/>
+      <c r="O6" s="126"/>
+      <c r="U6" s="101" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
-      <c r="B7" s="44"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="65"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="62"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="U7" s="64"/>
+      <c r="D7" s="69"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="126"/>
+      <c r="K7" s="126"/>
+      <c r="L7" s="126"/>
+      <c r="M7" s="126"/>
+      <c r="N7" s="126"/>
+      <c r="O7" s="126"/>
+      <c r="U7" s="101"/>
     </row>
     <row r="8" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="65"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="62"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58"/>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58"/>
-      <c r="U8" s="64"/>
+      <c r="D8" s="69"/>
+      <c r="F8" s="126"/>
+      <c r="G8" s="126"/>
+      <c r="H8" s="126"/>
+      <c r="I8" s="126"/>
+      <c r="J8" s="126"/>
+      <c r="K8" s="126"/>
+      <c r="L8" s="126"/>
+      <c r="M8" s="126"/>
+      <c r="N8" s="126"/>
+      <c r="O8" s="126"/>
+      <c r="U8" s="101"/>
     </row>
     <row r="9" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="44"/>
-      <c r="B9" s="44"/>
+      <c r="A9" s="65"/>
+      <c r="B9" s="65"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58"/>
-      <c r="O9" s="58"/>
-      <c r="U9" s="68" t="s">
+      <c r="F9" s="126"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="126"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="126"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="126"/>
+      <c r="M9" s="126"/>
+      <c r="N9" s="126"/>
+      <c r="O9" s="126"/>
+      <c r="U9" s="90" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="44"/>
-      <c r="B10" s="44"/>
+      <c r="A10" s="65"/>
+      <c r="B10" s="65"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="46"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="58"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58"/>
-      <c r="M10" s="58"/>
-      <c r="N10" s="58"/>
-      <c r="O10" s="58"/>
-      <c r="U10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="126"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="126"/>
+      <c r="K10" s="126"/>
+      <c r="L10" s="126"/>
+      <c r="M10" s="126"/>
+      <c r="N10" s="126"/>
+      <c r="O10" s="126"/>
+      <c r="U10" s="90"/>
     </row>
     <row r="11" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="44"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="65"/>
+      <c r="B11" s="65"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="76">
+      <c r="D11" s="70">
         <v>1.008</v>
       </c>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="58"/>
-      <c r="N11" s="58"/>
-      <c r="O11" s="58"/>
-      <c r="U11" s="71">
+      <c r="F11" s="126"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="126"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="126"/>
+      <c r="K11" s="126"/>
+      <c r="L11" s="126"/>
+      <c r="M11" s="126"/>
+      <c r="N11" s="126"/>
+      <c r="O11" s="126"/>
+      <c r="U11" s="104">
         <v>4.0026000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
-      <c r="B12" s="44"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="65"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="77"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
-      <c r="U12" s="72"/>
+      <c r="D12" s="71"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="126"/>
+      <c r="H12" s="126"/>
+      <c r="I12" s="126"/>
+      <c r="J12" s="126"/>
+      <c r="K12" s="126"/>
+      <c r="L12" s="126"/>
+      <c r="M12" s="126"/>
+      <c r="N12" s="126"/>
+      <c r="O12" s="126"/>
+      <c r="U12" s="105"/>
     </row>
     <row r="13" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44">
+      <c r="A13" s="65"/>
+      <c r="B13" s="65">
         <v>2</v>
       </c>
       <c r="C13" s="7"/>
-      <c r="D13" s="47">
+      <c r="D13" s="72">
         <v>3</v>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="76">
         <v>4</v>
       </c>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="90">
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="126"/>
+      <c r="M13" s="126"/>
+      <c r="N13" s="126"/>
+      <c r="O13" s="126"/>
+      <c r="P13" s="98">
         <v>5</v>
       </c>
-      <c r="Q13" s="65">
+      <c r="Q13" s="67">
         <v>6</v>
       </c>
-      <c r="R13" s="65">
+      <c r="R13" s="67">
         <v>7</v>
       </c>
-      <c r="S13" s="65">
+      <c r="S13" s="67">
         <v>8</v>
       </c>
-      <c r="T13" s="66">
+      <c r="T13" s="106">
         <v>9</v>
       </c>
-      <c r="U13" s="73">
+      <c r="U13" s="107">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
-      <c r="B14" s="44"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="65"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="91"/>
-      <c r="Q14" s="46"/>
-      <c r="R14" s="46"/>
-      <c r="S14" s="46"/>
-      <c r="T14" s="67"/>
-      <c r="U14" s="68"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="126"/>
+      <c r="H14" s="126"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="126"/>
+      <c r="K14" s="126"/>
+      <c r="L14" s="126"/>
+      <c r="M14" s="126"/>
+      <c r="N14" s="126"/>
+      <c r="O14" s="126"/>
+      <c r="P14" s="99"/>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="68"/>
+      <c r="S14" s="68"/>
+      <c r="T14" s="91"/>
+      <c r="U14" s="90"/>
     </row>
     <row r="15" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="44"/>
-      <c r="B15" s="44"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="65"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="54" t="s">
+      <c r="E15" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="58"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="61" t="s">
+      <c r="F15" s="126"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="126"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
+      <c r="K15" s="126"/>
+      <c r="L15" s="126"/>
+      <c r="M15" s="126"/>
+      <c r="N15" s="126"/>
+      <c r="O15" s="126"/>
+      <c r="P15" s="89" t="s">
         <v>54</v>
       </c>
-      <c r="Q15" s="62" t="s">
+      <c r="Q15" s="69" t="s">
         <v>55</v>
       </c>
-      <c r="R15" s="62" t="s">
+      <c r="R15" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="S15" s="62" t="s">
+      <c r="S15" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="T15" s="63" t="s">
+      <c r="T15" s="100" t="s">
         <v>58</v>
       </c>
-      <c r="U15" s="64" t="s">
+      <c r="U15" s="101" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="44"/>
-      <c r="B16" s="44"/>
+      <c r="A16" s="65"/>
+      <c r="B16" s="65"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="58"/>
-      <c r="O16" s="58"/>
-      <c r="P16" s="61"/>
-      <c r="Q16" s="62"/>
-      <c r="R16" s="62"/>
-      <c r="S16" s="62"/>
-      <c r="T16" s="63"/>
-      <c r="U16" s="64"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="126"/>
+      <c r="H16" s="126"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="126"/>
+      <c r="K16" s="126"/>
+      <c r="L16" s="126"/>
+      <c r="M16" s="126"/>
+      <c r="N16" s="126"/>
+      <c r="O16" s="126"/>
+      <c r="P16" s="89"/>
+      <c r="Q16" s="69"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="69"/>
+      <c r="T16" s="100"/>
+      <c r="U16" s="101"/>
     </row>
     <row r="17" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="44"/>
-      <c r="B17" s="44"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="65"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="61"/>
-      <c r="Q17" s="62"/>
-      <c r="R17" s="62"/>
-      <c r="S17" s="62"/>
-      <c r="T17" s="63"/>
-      <c r="U17" s="64"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="126"/>
+      <c r="G17" s="126"/>
+      <c r="H17" s="126"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="126"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="126"/>
+      <c r="O17" s="126"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="69"/>
+      <c r="R17" s="69"/>
+      <c r="S17" s="69"/>
+      <c r="T17" s="100"/>
+      <c r="U17" s="101"/>
     </row>
     <row r="18" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="44"/>
-      <c r="B18" s="44"/>
+      <c r="A18" s="65"/>
+      <c r="B18" s="65"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="58"/>
-      <c r="O18" s="58"/>
-      <c r="P18" s="91" t="s">
+      <c r="F18" s="126"/>
+      <c r="G18" s="126"/>
+      <c r="H18" s="126"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="126"/>
+      <c r="K18" s="126"/>
+      <c r="L18" s="126"/>
+      <c r="M18" s="126"/>
+      <c r="N18" s="126"/>
+      <c r="O18" s="126"/>
+      <c r="P18" s="99" t="s">
         <v>166</v>
       </c>
-      <c r="Q18" s="46" t="s">
+      <c r="Q18" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="R18" s="46" t="s">
+      <c r="R18" s="68" t="s">
         <v>177</v>
       </c>
-      <c r="S18" s="46" t="s">
+      <c r="S18" s="68" t="s">
         <v>184</v>
       </c>
-      <c r="T18" s="67" t="s">
+      <c r="T18" s="91" t="s">
         <v>197</v>
       </c>
-      <c r="U18" s="68" t="s">
+      <c r="U18" s="90" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="44"/>
-      <c r="B19" s="44"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="65"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="58"/>
-      <c r="O19" s="58"/>
-      <c r="P19" s="91"/>
-      <c r="Q19" s="46"/>
-      <c r="R19" s="46"/>
-      <c r="S19" s="46"/>
-      <c r="T19" s="67"/>
-      <c r="U19" s="68"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="126"/>
+      <c r="O19" s="126"/>
+      <c r="P19" s="99"/>
+      <c r="Q19" s="68"/>
+      <c r="R19" s="68"/>
+      <c r="S19" s="68"/>
+      <c r="T19" s="91"/>
+      <c r="U19" s="90"/>
     </row>
     <row r="20" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="44"/>
-      <c r="B20" s="44"/>
+      <c r="A20" s="65"/>
+      <c r="B20" s="65"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="56">
+      <c r="D20" s="74">
         <v>6.94</v>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="63">
         <v>9.0122</v>
       </c>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
-      <c r="O20" s="58"/>
-      <c r="P20" s="74">
+      <c r="F20" s="126"/>
+      <c r="G20" s="126"/>
+      <c r="H20" s="126"/>
+      <c r="I20" s="126"/>
+      <c r="J20" s="126"/>
+      <c r="K20" s="126"/>
+      <c r="L20" s="126"/>
+      <c r="M20" s="126"/>
+      <c r="N20" s="126"/>
+      <c r="O20" s="126"/>
+      <c r="P20" s="92">
         <v>10.81</v>
       </c>
-      <c r="Q20" s="76">
+      <c r="Q20" s="70">
         <v>12.010999999999999</v>
       </c>
-      <c r="R20" s="76">
+      <c r="R20" s="70">
         <v>14.007</v>
       </c>
-      <c r="S20" s="76">
+      <c r="S20" s="70">
         <v>15.999000000000001</v>
       </c>
-      <c r="T20" s="69">
+      <c r="T20" s="102">
         <v>18.998000000000001</v>
       </c>
-      <c r="U20" s="71">
+      <c r="U20" s="104">
         <v>20.18</v>
       </c>
     </row>
     <row r="21" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="44"/>
-      <c r="B21" s="44"/>
+      <c r="A21" s="65"/>
+      <c r="B21" s="65"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="58"/>
-      <c r="O21" s="58"/>
-      <c r="P21" s="75"/>
-      <c r="Q21" s="77"/>
-      <c r="R21" s="77"/>
-      <c r="S21" s="77"/>
-      <c r="T21" s="70"/>
-      <c r="U21" s="72"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="126"/>
+      <c r="G21" s="126"/>
+      <c r="H21" s="126"/>
+      <c r="I21" s="126"/>
+      <c r="J21" s="126"/>
+      <c r="K21" s="126"/>
+      <c r="L21" s="126"/>
+      <c r="M21" s="126"/>
+      <c r="N21" s="126"/>
+      <c r="O21" s="126"/>
+      <c r="P21" s="93"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="71"/>
+      <c r="S21" s="71"/>
+      <c r="T21" s="103"/>
+      <c r="U21" s="105"/>
     </row>
     <row r="22" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="44"/>
-      <c r="B22" s="44">
+      <c r="A22" s="65"/>
+      <c r="B22" s="65">
         <v>3</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="47">
+      <c r="D22" s="72">
         <v>11</v>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="76">
         <v>12</v>
       </c>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
-      <c r="P22" s="92">
+      <c r="F22" s="126"/>
+      <c r="G22" s="126"/>
+      <c r="H22" s="126"/>
+      <c r="I22" s="126"/>
+      <c r="J22" s="126"/>
+      <c r="K22" s="126"/>
+      <c r="L22" s="126"/>
+      <c r="M22" s="126"/>
+      <c r="N22" s="126"/>
+      <c r="O22" s="126"/>
+      <c r="P22" s="94">
         <v>13</v>
       </c>
-      <c r="Q22" s="90">
+      <c r="Q22" s="98">
         <v>14</v>
       </c>
-      <c r="R22" s="65">
+      <c r="R22" s="67">
         <v>15</v>
       </c>
-      <c r="S22" s="65">
+      <c r="S22" s="67">
         <v>16</v>
       </c>
-      <c r="T22" s="66">
+      <c r="T22" s="106">
         <v>17</v>
       </c>
-      <c r="U22" s="73">
+      <c r="U22" s="107">
         <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="65"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="58"/>
-      <c r="O23" s="58"/>
-      <c r="P23" s="93"/>
-      <c r="Q23" s="91"/>
-      <c r="R23" s="46"/>
-      <c r="S23" s="46"/>
-      <c r="T23" s="67"/>
-      <c r="U23" s="68"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="126"/>
+      <c r="H23" s="126"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="126"/>
+      <c r="K23" s="126"/>
+      <c r="L23" s="126"/>
+      <c r="M23" s="126"/>
+      <c r="N23" s="126"/>
+      <c r="O23" s="126"/>
+      <c r="P23" s="95"/>
+      <c r="Q23" s="99"/>
+      <c r="R23" s="68"/>
+      <c r="S23" s="68"/>
+      <c r="T23" s="91"/>
+      <c r="U23" s="90"/>
     </row>
     <row r="24" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="44"/>
-      <c r="B24" s="44"/>
+      <c r="A24" s="65"/>
+      <c r="B24" s="65"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="48" t="s">
+      <c r="D24" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="E24" s="54" t="s">
+      <c r="E24" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="58"/>
-      <c r="P24" s="78" t="s">
+      <c r="F24" s="126"/>
+      <c r="G24" s="126"/>
+      <c r="H24" s="126"/>
+      <c r="I24" s="126"/>
+      <c r="J24" s="126"/>
+      <c r="K24" s="126"/>
+      <c r="L24" s="126"/>
+      <c r="M24" s="126"/>
+      <c r="N24" s="126"/>
+      <c r="O24" s="126"/>
+      <c r="P24" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="Q24" s="61" t="s">
+      <c r="Q24" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="R24" s="62" t="s">
+      <c r="R24" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="S24" s="62" t="s">
+      <c r="S24" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="T24" s="63" t="s">
+      <c r="T24" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="U24" s="64" t="s">
+      <c r="U24" s="101" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="44"/>
-      <c r="B25" s="44"/>
+      <c r="A25" s="65"/>
+      <c r="B25" s="65"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
-      <c r="P25" s="78"/>
-      <c r="Q25" s="61"/>
-      <c r="R25" s="62"/>
-      <c r="S25" s="62"/>
-      <c r="T25" s="63"/>
-      <c r="U25" s="64"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="126"/>
+      <c r="H25" s="126"/>
+      <c r="I25" s="126"/>
+      <c r="J25" s="126"/>
+      <c r="K25" s="126"/>
+      <c r="L25" s="126"/>
+      <c r="M25" s="126"/>
+      <c r="N25" s="126"/>
+      <c r="O25" s="126"/>
+      <c r="P25" s="88"/>
+      <c r="Q25" s="89"/>
+      <c r="R25" s="69"/>
+      <c r="S25" s="69"/>
+      <c r="T25" s="100"/>
+      <c r="U25" s="101"/>
     </row>
     <row r="26" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="44"/>
-      <c r="B26" s="44"/>
+      <c r="A26" s="65"/>
+      <c r="B26" s="65"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
-      <c r="P26" s="78"/>
-      <c r="Q26" s="61"/>
-      <c r="R26" s="62"/>
-      <c r="S26" s="62"/>
-      <c r="T26" s="63"/>
-      <c r="U26" s="64"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="126"/>
+      <c r="G26" s="126"/>
+      <c r="H26" s="126"/>
+      <c r="I26" s="126"/>
+      <c r="J26" s="126"/>
+      <c r="K26" s="126"/>
+      <c r="L26" s="126"/>
+      <c r="M26" s="126"/>
+      <c r="N26" s="126"/>
+      <c r="O26" s="126"/>
+      <c r="P26" s="88"/>
+      <c r="Q26" s="89"/>
+      <c r="R26" s="69"/>
+      <c r="S26" s="69"/>
+      <c r="T26" s="100"/>
+      <c r="U26" s="101"/>
     </row>
     <row r="27" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="44"/>
-      <c r="B27" s="44"/>
+      <c r="A27" s="65"/>
+      <c r="B27" s="65"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="45" t="s">
+      <c r="D27" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="E27" s="51" t="s">
+      <c r="E27" s="61" t="s">
         <v>125</v>
       </c>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
-      <c r="P27" s="93" t="s">
+      <c r="F27" s="126"/>
+      <c r="G27" s="126"/>
+      <c r="H27" s="126"/>
+      <c r="I27" s="126"/>
+      <c r="J27" s="126"/>
+      <c r="K27" s="126"/>
+      <c r="L27" s="126"/>
+      <c r="M27" s="126"/>
+      <c r="N27" s="126"/>
+      <c r="O27" s="126"/>
+      <c r="P27" s="95" t="s">
         <v>168</v>
       </c>
-      <c r="Q27" s="91" t="s">
+      <c r="Q27" s="99" t="s">
         <v>176</v>
       </c>
-      <c r="R27" s="46" t="s">
+      <c r="R27" s="68" t="s">
         <v>178</v>
       </c>
-      <c r="S27" s="46" t="s">
+      <c r="S27" s="68" t="s">
         <v>185</v>
       </c>
-      <c r="T27" s="67" t="s">
+      <c r="T27" s="91" t="s">
         <v>198</v>
       </c>
-      <c r="U27" s="68" t="s">
+      <c r="U27" s="90" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="44"/>
-      <c r="B28" s="44"/>
+      <c r="A28" s="65"/>
+      <c r="B28" s="65"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
-      <c r="P28" s="93"/>
-      <c r="Q28" s="91"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="67"/>
-      <c r="U28" s="68"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="126"/>
+      <c r="G28" s="126"/>
+      <c r="H28" s="126"/>
+      <c r="I28" s="126"/>
+      <c r="J28" s="126"/>
+      <c r="K28" s="126"/>
+      <c r="L28" s="126"/>
+      <c r="M28" s="126"/>
+      <c r="N28" s="126"/>
+      <c r="O28" s="126"/>
+      <c r="P28" s="95"/>
+      <c r="Q28" s="99"/>
+      <c r="R28" s="68"/>
+      <c r="S28" s="68"/>
+      <c r="T28" s="91"/>
+      <c r="U28" s="90"/>
     </row>
     <row r="29" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="44"/>
-      <c r="B29" s="44"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="65"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="56">
+      <c r="D29" s="74">
         <v>22.99</v>
       </c>
-      <c r="E29" s="52">
+      <c r="E29" s="63">
         <v>24.305</v>
       </c>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
-      <c r="P29" s="42">
+      <c r="F29" s="126"/>
+      <c r="G29" s="126"/>
+      <c r="H29" s="126"/>
+      <c r="I29" s="126"/>
+      <c r="J29" s="126"/>
+      <c r="K29" s="126"/>
+      <c r="L29" s="126"/>
+      <c r="M29" s="126"/>
+      <c r="N29" s="126"/>
+      <c r="O29" s="126"/>
+      <c r="P29" s="96">
         <v>26.981999999999999</v>
       </c>
-      <c r="Q29" s="74">
+      <c r="Q29" s="92">
         <v>28.085000000000001</v>
       </c>
-      <c r="R29" s="76">
+      <c r="R29" s="70">
         <v>30.974</v>
       </c>
-      <c r="S29" s="76">
+      <c r="S29" s="70">
         <v>32.06</v>
       </c>
-      <c r="T29" s="69">
+      <c r="T29" s="102">
         <v>35.450000000000003</v>
       </c>
-      <c r="U29" s="71">
+      <c r="U29" s="104">
         <v>39.950000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="44"/>
-      <c r="B30" s="44"/>
+      <c r="A30" s="65"/>
+      <c r="B30" s="65"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="58"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="58"/>
-      <c r="O30" s="58"/>
-      <c r="P30" s="43"/>
-      <c r="Q30" s="75"/>
-      <c r="R30" s="77"/>
-      <c r="S30" s="77"/>
-      <c r="T30" s="70"/>
-      <c r="U30" s="72"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="126"/>
+      <c r="G30" s="126"/>
+      <c r="H30" s="126"/>
+      <c r="I30" s="126"/>
+      <c r="J30" s="126"/>
+      <c r="K30" s="126"/>
+      <c r="L30" s="126"/>
+      <c r="M30" s="126"/>
+      <c r="N30" s="126"/>
+      <c r="O30" s="126"/>
+      <c r="P30" s="97"/>
+      <c r="Q30" s="93"/>
+      <c r="R30" s="71"/>
+      <c r="S30" s="71"/>
+      <c r="T30" s="103"/>
+      <c r="U30" s="105"/>
     </row>
     <row r="31" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="44"/>
-      <c r="B31" s="44">
+      <c r="A31" s="65"/>
+      <c r="B31" s="65">
         <v>4</v>
       </c>
       <c r="C31" s="7"/>
-      <c r="D31" s="47">
+      <c r="D31" s="72">
         <v>19</v>
       </c>
-      <c r="E31" s="55">
+      <c r="E31" s="76">
         <v>20</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="77">
         <v>21</v>
       </c>
-      <c r="G31" s="37">
+      <c r="G31" s="77">
         <v>22</v>
       </c>
-      <c r="H31" s="37">
+      <c r="H31" s="77">
         <v>23</v>
       </c>
-      <c r="I31" s="37">
+      <c r="I31" s="77">
         <v>24</v>
       </c>
-      <c r="J31" s="37">
+      <c r="J31" s="77">
         <v>25</v>
       </c>
-      <c r="K31" s="37">
+      <c r="K31" s="77">
         <v>26</v>
       </c>
-      <c r="L31" s="37">
+      <c r="L31" s="77">
         <v>27</v>
       </c>
-      <c r="M31" s="37">
+      <c r="M31" s="77">
         <v>28</v>
       </c>
-      <c r="N31" s="37">
+      <c r="N31" s="77">
         <v>29</v>
       </c>
-      <c r="O31" s="37">
+      <c r="O31" s="77">
         <v>30</v>
       </c>
-      <c r="P31" s="92">
+      <c r="P31" s="94">
         <v>31</v>
       </c>
-      <c r="Q31" s="90">
+      <c r="Q31" s="98">
         <v>32</v>
       </c>
-      <c r="R31" s="90">
+      <c r="R31" s="98">
         <v>33</v>
       </c>
-      <c r="S31" s="65">
+      <c r="S31" s="67">
         <v>34</v>
       </c>
-      <c r="T31" s="66">
+      <c r="T31" s="106">
         <v>35</v>
       </c>
-      <c r="U31" s="73">
+      <c r="U31" s="107">
         <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="44"/>
-      <c r="B32" s="44"/>
+      <c r="A32" s="65"/>
+      <c r="B32" s="65"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="38"/>
-      <c r="J32" s="38"/>
-      <c r="K32" s="38"/>
-      <c r="L32" s="38"/>
-      <c r="M32" s="38"/>
-      <c r="N32" s="37"/>
-      <c r="O32" s="37"/>
-      <c r="P32" s="93"/>
-      <c r="Q32" s="91"/>
-      <c r="R32" s="91"/>
-      <c r="S32" s="46"/>
-      <c r="T32" s="67"/>
-      <c r="U32" s="68"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="78"/>
+      <c r="J32" s="78"/>
+      <c r="K32" s="78"/>
+      <c r="L32" s="78"/>
+      <c r="M32" s="78"/>
+      <c r="N32" s="77"/>
+      <c r="O32" s="77"/>
+      <c r="P32" s="95"/>
+      <c r="Q32" s="99"/>
+      <c r="R32" s="99"/>
+      <c r="S32" s="68"/>
+      <c r="T32" s="91"/>
+      <c r="U32" s="90"/>
     </row>
     <row r="33" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="44"/>
-      <c r="B33" s="44"/>
+      <c r="A33" s="65"/>
+      <c r="B33" s="65"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="48" t="s">
+      <c r="D33" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="E33" s="54" t="s">
+      <c r="E33" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="36" t="s">
+      <c r="F33" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="36" t="s">
+      <c r="G33" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H33" s="36" t="s">
+      <c r="H33" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="I33" s="36" t="s">
+      <c r="I33" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="J33" s="36" t="s">
+      <c r="J33" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="K33" s="36" t="s">
+      <c r="K33" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="L33" s="36" t="s">
+      <c r="L33" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="M33" s="36" t="s">
+      <c r="M33" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="N33" s="36" t="s">
+      <c r="N33" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="O33" s="36" t="s">
+      <c r="O33" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="P33" s="78" t="s">
+      <c r="P33" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="Q33" s="61" t="s">
+      <c r="Q33" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="R33" s="61" t="s">
+      <c r="R33" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="S33" s="62" t="s">
+      <c r="S33" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="T33" s="63" t="s">
+      <c r="T33" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="U33" s="64" t="s">
+      <c r="U33" s="101" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="44"/>
-      <c r="B34" s="44"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="65"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="78"/>
-      <c r="Q34" s="61"/>
-      <c r="R34" s="61"/>
-      <c r="S34" s="62"/>
-      <c r="T34" s="63"/>
-      <c r="U34" s="64"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="79"/>
+      <c r="L34" s="79"/>
+      <c r="M34" s="79"/>
+      <c r="N34" s="79"/>
+      <c r="O34" s="79"/>
+      <c r="P34" s="88"/>
+      <c r="Q34" s="89"/>
+      <c r="R34" s="89"/>
+      <c r="S34" s="69"/>
+      <c r="T34" s="100"/>
+      <c r="U34" s="101"/>
     </row>
     <row r="35" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="44"/>
-      <c r="B35" s="44"/>
+      <c r="A35" s="65"/>
+      <c r="B35" s="65"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="54"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="36"/>
-      <c r="N35" s="36"/>
-      <c r="O35" s="36"/>
-      <c r="P35" s="78"/>
-      <c r="Q35" s="61"/>
-      <c r="R35" s="61"/>
-      <c r="S35" s="62"/>
-      <c r="T35" s="63"/>
-      <c r="U35" s="64"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="79"/>
+      <c r="J35" s="79"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="79"/>
+      <c r="M35" s="79"/>
+      <c r="N35" s="79"/>
+      <c r="O35" s="79"/>
+      <c r="P35" s="88"/>
+      <c r="Q35" s="89"/>
+      <c r="R35" s="89"/>
+      <c r="S35" s="69"/>
+      <c r="T35" s="100"/>
+      <c r="U35" s="101"/>
     </row>
     <row r="36" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="44"/>
-      <c r="B36" s="44"/>
+      <c r="A36" s="65"/>
+      <c r="B36" s="65"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="45" t="s">
+      <c r="D36" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="E36" s="51" t="s">
+      <c r="E36" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="F36" s="38" t="s">
+      <c r="F36" s="78" t="s">
         <v>238</v>
       </c>
-      <c r="G36" s="38" t="s">
+      <c r="G36" s="78" t="s">
         <v>134</v>
       </c>
-      <c r="H36" s="38" t="s">
+      <c r="H36" s="78" t="s">
         <v>140</v>
       </c>
-      <c r="I36" s="38" t="s">
+      <c r="I36" s="78" t="s">
         <v>229</v>
       </c>
-      <c r="J36" s="38" t="s">
+      <c r="J36" s="78" t="s">
         <v>147</v>
       </c>
-      <c r="K36" s="38" t="s">
+      <c r="K36" s="78" t="s">
         <v>148</v>
       </c>
-      <c r="L36" s="38" t="s">
+      <c r="L36" s="78" t="s">
         <v>151</v>
       </c>
-      <c r="M36" s="38" t="s">
+      <c r="M36" s="78" t="s">
         <v>155</v>
       </c>
-      <c r="N36" s="38" t="s">
+      <c r="N36" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="O36" s="38" t="s">
+      <c r="O36" s="78" t="s">
         <v>163</v>
       </c>
-      <c r="P36" s="93" t="s">
+      <c r="P36" s="95" t="s">
         <v>169</v>
       </c>
-      <c r="Q36" s="91" t="s">
+      <c r="Q36" s="99" t="s">
         <v>175</v>
       </c>
-      <c r="R36" s="91" t="s">
+      <c r="R36" s="99" t="s">
         <v>180</v>
       </c>
-      <c r="S36" s="46" t="s">
+      <c r="S36" s="68" t="s">
         <v>186</v>
       </c>
-      <c r="T36" s="67" t="s">
+      <c r="T36" s="91" t="s">
         <v>199</v>
       </c>
-      <c r="U36" s="68" t="s">
+      <c r="U36" s="90" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="37" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="44"/>
-      <c r="B37" s="44"/>
+      <c r="A37" s="65"/>
+      <c r="B37" s="65"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="38"/>
-      <c r="L37" s="38"/>
-      <c r="M37" s="38"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="38"/>
-      <c r="P37" s="93"/>
-      <c r="Q37" s="91"/>
-      <c r="R37" s="91"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="67"/>
-      <c r="U37" s="68"/>
+      <c r="D37" s="62"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="78"/>
+      <c r="G37" s="78"/>
+      <c r="H37" s="78"/>
+      <c r="I37" s="78"/>
+      <c r="J37" s="78"/>
+      <c r="K37" s="78"/>
+      <c r="L37" s="78"/>
+      <c r="M37" s="78"/>
+      <c r="N37" s="78"/>
+      <c r="O37" s="78"/>
+      <c r="P37" s="95"/>
+      <c r="Q37" s="99"/>
+      <c r="R37" s="99"/>
+      <c r="S37" s="68"/>
+      <c r="T37" s="91"/>
+      <c r="U37" s="90"/>
     </row>
     <row r="38" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="44"/>
-      <c r="B38" s="44"/>
+      <c r="A38" s="65"/>
+      <c r="B38" s="65"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="56">
+      <c r="D38" s="74">
         <v>39.097999999999999</v>
       </c>
-      <c r="E38" s="52">
+      <c r="E38" s="63">
         <v>40.078000000000003</v>
       </c>
-      <c r="F38" s="40">
+      <c r="F38" s="80">
         <v>44.956000000000003</v>
       </c>
-      <c r="G38" s="40">
+      <c r="G38" s="80">
         <v>47.866999999999997</v>
       </c>
-      <c r="H38" s="40">
+      <c r="H38" s="80">
         <v>50.942</v>
       </c>
-      <c r="I38" s="40">
+      <c r="I38" s="80">
         <v>51.996000000000002</v>
       </c>
-      <c r="J38" s="40">
+      <c r="J38" s="80">
         <v>54.938000000000002</v>
       </c>
-      <c r="K38" s="40">
+      <c r="K38" s="80">
         <v>55.844999999999999</v>
       </c>
-      <c r="L38" s="40">
+      <c r="L38" s="80">
         <v>58.933</v>
       </c>
-      <c r="M38" s="40">
+      <c r="M38" s="80">
         <v>58.692999999999998</v>
       </c>
-      <c r="N38" s="40">
+      <c r="N38" s="80">
         <v>63.545999999999999</v>
       </c>
-      <c r="O38" s="40">
+      <c r="O38" s="80">
         <v>65.38</v>
       </c>
-      <c r="P38" s="42">
+      <c r="P38" s="96">
         <v>69.722999999999999</v>
       </c>
-      <c r="Q38" s="74">
+      <c r="Q38" s="92">
         <v>72.63</v>
       </c>
-      <c r="R38" s="74">
+      <c r="R38" s="92">
         <v>74.921999999999997</v>
       </c>
-      <c r="S38" s="76">
+      <c r="S38" s="70">
         <v>78.971000000000004</v>
       </c>
-      <c r="T38" s="69">
+      <c r="T38" s="102">
         <v>79.903999999999996</v>
       </c>
-      <c r="U38" s="71">
+      <c r="U38" s="104">
         <v>83.798000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="44"/>
-      <c r="B39" s="44"/>
+      <c r="A39" s="65"/>
+      <c r="B39" s="65"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="57"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="40"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="41"/>
-      <c r="M39" s="41"/>
-      <c r="N39" s="41"/>
-      <c r="O39" s="41"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="75"/>
-      <c r="R39" s="75"/>
-      <c r="S39" s="77"/>
-      <c r="T39" s="70"/>
-      <c r="U39" s="72"/>
+      <c r="D39" s="75"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="81"/>
+      <c r="J39" s="81"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="81"/>
+      <c r="M39" s="81"/>
+      <c r="N39" s="81"/>
+      <c r="O39" s="81"/>
+      <c r="P39" s="97"/>
+      <c r="Q39" s="93"/>
+      <c r="R39" s="93"/>
+      <c r="S39" s="71"/>
+      <c r="T39" s="103"/>
+      <c r="U39" s="105"/>
     </row>
     <row r="40" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="44"/>
-      <c r="B40" s="44">
+      <c r="A40" s="65"/>
+      <c r="B40" s="65">
         <v>5</v>
       </c>
       <c r="C40" s="7"/>
-      <c r="D40" s="47">
+      <c r="D40" s="72">
         <v>37</v>
       </c>
-      <c r="E40" s="55">
+      <c r="E40" s="76">
         <v>38</v>
       </c>
-      <c r="F40" s="37">
+      <c r="F40" s="77">
         <v>39</v>
       </c>
-      <c r="G40" s="37">
+      <c r="G40" s="77">
         <v>40</v>
       </c>
-      <c r="H40" s="37">
+      <c r="H40" s="77">
         <v>41</v>
       </c>
-      <c r="I40" s="37">
+      <c r="I40" s="77">
         <v>42</v>
       </c>
-      <c r="J40" s="37">
+      <c r="J40" s="77">
         <v>43</v>
       </c>
-      <c r="K40" s="37">
+      <c r="K40" s="77">
         <v>44</v>
       </c>
-      <c r="L40" s="37">
+      <c r="L40" s="77">
         <v>45</v>
       </c>
-      <c r="M40" s="37">
+      <c r="M40" s="77">
         <v>46</v>
       </c>
-      <c r="N40" s="37">
+      <c r="N40" s="77">
         <v>47</v>
       </c>
-      <c r="O40" s="37">
+      <c r="O40" s="77">
         <v>48</v>
       </c>
-      <c r="P40" s="92">
+      <c r="P40" s="94">
         <v>49</v>
       </c>
-      <c r="Q40" s="92">
+      <c r="Q40" s="94">
         <v>50</v>
       </c>
-      <c r="R40" s="90">
+      <c r="R40" s="98">
         <v>51</v>
       </c>
-      <c r="S40" s="90">
+      <c r="S40" s="98">
         <v>52</v>
       </c>
-      <c r="T40" s="66">
+      <c r="T40" s="106">
         <v>53</v>
       </c>
-      <c r="U40" s="73">
+      <c r="U40" s="107">
         <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="44"/>
-      <c r="B41" s="44"/>
+      <c r="A41" s="65"/>
+      <c r="B41" s="65"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38"/>
-      <c r="J41" s="38"/>
-      <c r="K41" s="38"/>
-      <c r="L41" s="38"/>
-      <c r="M41" s="38"/>
-      <c r="N41" s="38"/>
-      <c r="O41" s="38"/>
-      <c r="P41" s="93"/>
-      <c r="Q41" s="93"/>
-      <c r="R41" s="91"/>
-      <c r="S41" s="91"/>
-      <c r="T41" s="67"/>
-      <c r="U41" s="68"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="78"/>
+      <c r="G41" s="78"/>
+      <c r="H41" s="78"/>
+      <c r="I41" s="78"/>
+      <c r="J41" s="78"/>
+      <c r="K41" s="78"/>
+      <c r="L41" s="78"/>
+      <c r="M41" s="78"/>
+      <c r="N41" s="78"/>
+      <c r="O41" s="78"/>
+      <c r="P41" s="95"/>
+      <c r="Q41" s="95"/>
+      <c r="R41" s="99"/>
+      <c r="S41" s="99"/>
+      <c r="T41" s="91"/>
+      <c r="U41" s="90"/>
     </row>
     <row r="42" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="44"/>
-      <c r="B42" s="44"/>
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="48" t="s">
+      <c r="D42" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="54" t="s">
+      <c r="E42" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="F42" s="36" t="s">
+      <c r="F42" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="G42" s="36" t="s">
+      <c r="G42" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="H42" s="36" t="s">
+      <c r="H42" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="I42" s="36" t="s">
+      <c r="I42" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="J42" s="36" t="s">
+      <c r="J42" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="K42" s="36" t="s">
+      <c r="K42" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="L42" s="36" t="s">
+      <c r="L42" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="M42" s="36" t="s">
+      <c r="M42" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="N42" s="36" t="s">
+      <c r="N42" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="O42" s="36" t="s">
+      <c r="O42" s="79" t="s">
         <v>51</v>
       </c>
-      <c r="P42" s="78" t="s">
+      <c r="P42" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="Q42" s="78" t="s">
+      <c r="Q42" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="R42" s="61" t="s">
+      <c r="R42" s="89" t="s">
         <v>75</v>
       </c>
-      <c r="S42" s="61" t="s">
+      <c r="S42" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="T42" s="63" t="s">
+      <c r="T42" s="100" t="s">
         <v>77</v>
       </c>
-      <c r="U42" s="64" t="s">
+      <c r="U42" s="101" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="44"/>
-      <c r="B43" s="44"/>
+      <c r="A43" s="65"/>
+      <c r="B43" s="65"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="54"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
-      <c r="J43" s="36"/>
-      <c r="K43" s="36"/>
-      <c r="L43" s="36"/>
-      <c r="M43" s="36"/>
-      <c r="N43" s="36"/>
-      <c r="O43" s="36"/>
-      <c r="P43" s="78"/>
-      <c r="Q43" s="78"/>
-      <c r="R43" s="61"/>
-      <c r="S43" s="61"/>
-      <c r="T43" s="63"/>
-      <c r="U43" s="64"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="79"/>
+      <c r="G43" s="79"/>
+      <c r="H43" s="79"/>
+      <c r="I43" s="79"/>
+      <c r="J43" s="79"/>
+      <c r="K43" s="79"/>
+      <c r="L43" s="79"/>
+      <c r="M43" s="79"/>
+      <c r="N43" s="79"/>
+      <c r="O43" s="79"/>
+      <c r="P43" s="88"/>
+      <c r="Q43" s="88"/>
+      <c r="R43" s="89"/>
+      <c r="S43" s="89"/>
+      <c r="T43" s="100"/>
+      <c r="U43" s="101"/>
     </row>
     <row r="44" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="44"/>
-      <c r="B44" s="44"/>
+      <c r="A44" s="65"/>
+      <c r="B44" s="65"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="54"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="36"/>
-      <c r="M44" s="36"/>
-      <c r="N44" s="36"/>
-      <c r="O44" s="36"/>
-      <c r="P44" s="78"/>
-      <c r="Q44" s="78"/>
-      <c r="R44" s="61"/>
-      <c r="S44" s="61"/>
-      <c r="T44" s="63"/>
-      <c r="U44" s="64"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="66"/>
+      <c r="F44" s="79"/>
+      <c r="G44" s="79"/>
+      <c r="H44" s="79"/>
+      <c r="I44" s="79"/>
+      <c r="J44" s="79"/>
+      <c r="K44" s="79"/>
+      <c r="L44" s="79"/>
+      <c r="M44" s="79"/>
+      <c r="N44" s="79"/>
+      <c r="O44" s="79"/>
+      <c r="P44" s="88"/>
+      <c r="Q44" s="88"/>
+      <c r="R44" s="89"/>
+      <c r="S44" s="89"/>
+      <c r="T44" s="100"/>
+      <c r="U44" s="101"/>
     </row>
     <row r="45" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="44"/>
-      <c r="B45" s="44"/>
+      <c r="A45" s="65"/>
+      <c r="B45" s="65"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="45" t="s">
+      <c r="D45" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="E45" s="51" t="s">
+      <c r="E45" s="61" t="s">
         <v>230</v>
       </c>
-      <c r="F45" s="38" t="s">
+      <c r="F45" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="G45" s="38" t="s">
+      <c r="G45" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="H45" s="38" t="s">
+      <c r="H45" s="78" t="s">
         <v>139</v>
       </c>
-      <c r="I45" s="38" t="s">
+      <c r="I45" s="78" t="s">
         <v>141</v>
       </c>
-      <c r="J45" s="38" t="s">
+      <c r="J45" s="78" t="s">
         <v>146</v>
       </c>
-      <c r="K45" s="38" t="s">
+      <c r="K45" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="L45" s="38" t="s">
+      <c r="L45" s="78" t="s">
         <v>152</v>
       </c>
-      <c r="M45" s="38" t="s">
+      <c r="M45" s="78" t="s">
         <v>157</v>
       </c>
-      <c r="N45" s="38" t="s">
+      <c r="N45" s="78" t="s">
         <v>160</v>
       </c>
-      <c r="O45" s="38" t="s">
+      <c r="O45" s="78" t="s">
         <v>164</v>
       </c>
-      <c r="P45" s="93" t="s">
+      <c r="P45" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="Q45" s="93" t="s">
+      <c r="Q45" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="R45" s="91" t="s">
+      <c r="R45" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="S45" s="91" t="s">
+      <c r="S45" s="99" t="s">
         <v>187</v>
       </c>
-      <c r="T45" s="67" t="s">
+      <c r="T45" s="91" t="s">
         <v>190</v>
       </c>
-      <c r="U45" s="68" t="s">
+      <c r="U45" s="90" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="44"/>
-      <c r="B46" s="44"/>
+      <c r="A46" s="65"/>
+      <c r="B46" s="65"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
-      <c r="J46" s="38"/>
-      <c r="K46" s="38"/>
-      <c r="L46" s="38"/>
-      <c r="M46" s="38"/>
-      <c r="N46" s="38"/>
-      <c r="O46" s="38"/>
-      <c r="P46" s="93"/>
-      <c r="Q46" s="93"/>
-      <c r="R46" s="91"/>
-      <c r="S46" s="91"/>
-      <c r="T46" s="67"/>
-      <c r="U46" s="68"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="78"/>
+      <c r="G46" s="78"/>
+      <c r="H46" s="78"/>
+      <c r="I46" s="78"/>
+      <c r="J46" s="78"/>
+      <c r="K46" s="78"/>
+      <c r="L46" s="78"/>
+      <c r="M46" s="78"/>
+      <c r="N46" s="78"/>
+      <c r="O46" s="78"/>
+      <c r="P46" s="95"/>
+      <c r="Q46" s="95"/>
+      <c r="R46" s="99"/>
+      <c r="S46" s="99"/>
+      <c r="T46" s="91"/>
+      <c r="U46" s="90"/>
     </row>
     <row r="47" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="44"/>
-      <c r="B47" s="44"/>
+      <c r="A47" s="65"/>
+      <c r="B47" s="65"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="56">
+      <c r="D47" s="74">
         <v>85.468000000000004</v>
       </c>
-      <c r="E47" s="52">
+      <c r="E47" s="63">
         <v>87.62</v>
       </c>
-      <c r="F47" s="40">
+      <c r="F47" s="80">
         <v>88.906000000000006</v>
       </c>
-      <c r="G47" s="40">
+      <c r="G47" s="80">
         <v>91.224000000000004</v>
       </c>
-      <c r="H47" s="40">
+      <c r="H47" s="80">
         <v>92.906000000000006</v>
       </c>
-      <c r="I47" s="40">
+      <c r="I47" s="80">
         <v>95.95</v>
       </c>
-      <c r="J47" s="40">
+      <c r="J47" s="80">
         <v>97</v>
       </c>
-      <c r="K47" s="40">
+      <c r="K47" s="80">
         <v>101.07</v>
       </c>
-      <c r="L47" s="40">
+      <c r="L47" s="80">
         <v>102.91</v>
       </c>
-      <c r="M47" s="40">
+      <c r="M47" s="80">
         <v>106.42</v>
       </c>
-      <c r="N47" s="40">
+      <c r="N47" s="80">
         <v>107.87</v>
       </c>
-      <c r="O47" s="40">
+      <c r="O47" s="80">
         <v>112.41</v>
       </c>
-      <c r="P47" s="42">
+      <c r="P47" s="96">
         <v>114.82</v>
       </c>
-      <c r="Q47" s="42">
+      <c r="Q47" s="96">
         <v>118.71</v>
       </c>
-      <c r="R47" s="74">
+      <c r="R47" s="92">
         <v>121.76</v>
       </c>
-      <c r="S47" s="74">
+      <c r="S47" s="92">
         <v>127.6</v>
       </c>
-      <c r="T47" s="69">
+      <c r="T47" s="102">
         <v>126.9</v>
       </c>
-      <c r="U47" s="71">
+      <c r="U47" s="104">
         <v>131.29</v>
       </c>
     </row>
     <row r="48" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="44"/>
-      <c r="B48" s="44"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="65"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="57"/>
-      <c r="E48" s="53"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="41"/>
-      <c r="J48" s="41"/>
-      <c r="K48" s="41"/>
-      <c r="L48" s="41"/>
-      <c r="M48" s="41"/>
-      <c r="N48" s="41"/>
-      <c r="O48" s="41"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="75"/>
-      <c r="S48" s="75"/>
-      <c r="T48" s="70"/>
-      <c r="U48" s="72"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="64"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="81"/>
+      <c r="H48" s="81"/>
+      <c r="I48" s="81"/>
+      <c r="J48" s="81"/>
+      <c r="K48" s="81"/>
+      <c r="L48" s="81"/>
+      <c r="M48" s="81"/>
+      <c r="N48" s="81"/>
+      <c r="O48" s="81"/>
+      <c r="P48" s="97"/>
+      <c r="Q48" s="97"/>
+      <c r="R48" s="93"/>
+      <c r="S48" s="93"/>
+      <c r="T48" s="103"/>
+      <c r="U48" s="105"/>
     </row>
     <row r="49" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="44"/>
-      <c r="B49" s="44">
+      <c r="A49" s="65"/>
+      <c r="B49" s="65">
         <v>6</v>
       </c>
       <c r="C49" s="7"/>
-      <c r="D49" s="47">
+      <c r="D49" s="72">
         <v>55</v>
       </c>
-      <c r="E49" s="55">
+      <c r="E49" s="76">
         <v>56</v>
       </c>
-      <c r="F49" s="94" t="s">
+      <c r="F49" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="G49" s="37">
+      <c r="G49" s="77">
         <v>72</v>
       </c>
-      <c r="H49" s="37">
+      <c r="H49" s="77">
         <v>73</v>
       </c>
-      <c r="I49" s="37">
+      <c r="I49" s="77">
         <v>74</v>
       </c>
-      <c r="J49" s="37">
+      <c r="J49" s="77">
         <v>75</v>
       </c>
-      <c r="K49" s="37">
+      <c r="K49" s="77">
         <v>76</v>
       </c>
-      <c r="L49" s="37">
+      <c r="L49" s="77">
         <v>77</v>
       </c>
-      <c r="M49" s="37">
+      <c r="M49" s="77">
         <v>78</v>
       </c>
-      <c r="N49" s="37">
+      <c r="N49" s="77">
         <v>79</v>
       </c>
-      <c r="O49" s="37">
+      <c r="O49" s="77">
         <v>80</v>
       </c>
-      <c r="P49" s="92">
+      <c r="P49" s="94">
         <v>81</v>
       </c>
-      <c r="Q49" s="92">
+      <c r="Q49" s="94">
         <v>82</v>
       </c>
-      <c r="R49" s="92">
+      <c r="R49" s="94">
         <v>83</v>
       </c>
-      <c r="S49" s="90">
+      <c r="S49" s="98">
         <v>84</v>
       </c>
-      <c r="T49" s="66">
+      <c r="T49" s="106">
         <v>85</v>
       </c>
-      <c r="U49" s="73">
+      <c r="U49" s="107">
         <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="44"/>
-      <c r="B50" s="44"/>
+      <c r="A50" s="65"/>
+      <c r="B50" s="65"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="95"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="38"/>
-      <c r="K50" s="38"/>
-      <c r="L50" s="38"/>
-      <c r="M50" s="38"/>
-      <c r="N50" s="38"/>
-      <c r="O50" s="38"/>
-      <c r="P50" s="93"/>
-      <c r="Q50" s="93"/>
-      <c r="R50" s="93"/>
-      <c r="S50" s="91"/>
-      <c r="T50" s="67"/>
-      <c r="U50" s="68"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="61"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="78"/>
+      <c r="H50" s="78"/>
+      <c r="I50" s="78"/>
+      <c r="J50" s="78"/>
+      <c r="K50" s="78"/>
+      <c r="L50" s="78"/>
+      <c r="M50" s="78"/>
+      <c r="N50" s="78"/>
+      <c r="O50" s="78"/>
+      <c r="P50" s="95"/>
+      <c r="Q50" s="95"/>
+      <c r="R50" s="95"/>
+      <c r="S50" s="99"/>
+      <c r="T50" s="91"/>
+      <c r="U50" s="90"/>
     </row>
     <row r="51" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="44"/>
-      <c r="B51" s="44"/>
+      <c r="A51" s="65"/>
+      <c r="B51" s="65"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="48" t="s">
+      <c r="D51" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="95"/>
-      <c r="G51" s="36" t="s">
+      <c r="F51" s="83"/>
+      <c r="G51" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="H51" s="36" t="s">
+      <c r="H51" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="I51" s="36" t="s">
+      <c r="I51" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="J51" s="36" t="s">
+      <c r="J51" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="K51" s="36" t="s">
+      <c r="K51" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="L51" s="36" t="s">
+      <c r="L51" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="M51" s="36" t="s">
+      <c r="M51" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="N51" s="36" t="s">
+      <c r="N51" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="O51" s="36" t="s">
+      <c r="O51" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="P51" s="78" t="s">
+      <c r="P51" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="Q51" s="78" t="s">
+      <c r="Q51" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="R51" s="78" t="s">
+      <c r="R51" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="S51" s="61" t="s">
+      <c r="S51" s="89" t="s">
         <v>82</v>
       </c>
-      <c r="T51" s="63" t="s">
+      <c r="T51" s="100" t="s">
         <v>83</v>
       </c>
-      <c r="U51" s="64" t="s">
+      <c r="U51" s="101" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="44"/>
-      <c r="B52" s="44"/>
+      <c r="A52" s="65"/>
+      <c r="B52" s="65"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="54"/>
-      <c r="F52" s="95"/>
-      <c r="G52" s="36"/>
-      <c r="H52" s="36"/>
-      <c r="I52" s="36"/>
-      <c r="J52" s="36"/>
-      <c r="K52" s="36"/>
-      <c r="L52" s="36"/>
-      <c r="M52" s="36"/>
-      <c r="N52" s="36"/>
-      <c r="O52" s="36"/>
-      <c r="P52" s="78"/>
-      <c r="Q52" s="78"/>
-      <c r="R52" s="78"/>
-      <c r="S52" s="61"/>
-      <c r="T52" s="63"/>
-      <c r="U52" s="64"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="66"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="79"/>
+      <c r="H52" s="79"/>
+      <c r="I52" s="79"/>
+      <c r="J52" s="79"/>
+      <c r="K52" s="79"/>
+      <c r="L52" s="79"/>
+      <c r="M52" s="79"/>
+      <c r="N52" s="79"/>
+      <c r="O52" s="79"/>
+      <c r="P52" s="88"/>
+      <c r="Q52" s="88"/>
+      <c r="R52" s="88"/>
+      <c r="S52" s="89"/>
+      <c r="T52" s="100"/>
+      <c r="U52" s="101"/>
     </row>
     <row r="53" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="44"/>
-      <c r="B53" s="44"/>
+      <c r="A53" s="65"/>
+      <c r="B53" s="65"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="54"/>
-      <c r="F53" s="95"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="36"/>
-      <c r="I53" s="36"/>
-      <c r="J53" s="36"/>
-      <c r="K53" s="36"/>
-      <c r="L53" s="36"/>
-      <c r="M53" s="36"/>
-      <c r="N53" s="36"/>
-      <c r="O53" s="36"/>
-      <c r="P53" s="78"/>
-      <c r="Q53" s="78"/>
-      <c r="R53" s="78"/>
-      <c r="S53" s="61"/>
-      <c r="T53" s="63"/>
-      <c r="U53" s="64"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="66"/>
+      <c r="F53" s="83"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="79"/>
+      <c r="I53" s="79"/>
+      <c r="J53" s="79"/>
+      <c r="K53" s="79"/>
+      <c r="L53" s="79"/>
+      <c r="M53" s="79"/>
+      <c r="N53" s="79"/>
+      <c r="O53" s="79"/>
+      <c r="P53" s="88"/>
+      <c r="Q53" s="88"/>
+      <c r="R53" s="88"/>
+      <c r="S53" s="89"/>
+      <c r="T53" s="100"/>
+      <c r="U53" s="101"/>
     </row>
     <row r="54" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="44"/>
-      <c r="B54" s="44"/>
+      <c r="A54" s="65"/>
+      <c r="B54" s="65"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="45" t="s">
+      <c r="D54" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="E54" s="51" t="s">
+      <c r="E54" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="F54" s="95"/>
-      <c r="G54" s="38" t="s">
+      <c r="F54" s="83"/>
+      <c r="G54" s="78" t="s">
         <v>136</v>
       </c>
-      <c r="H54" s="38" t="s">
+      <c r="H54" s="78" t="s">
         <v>138</v>
       </c>
-      <c r="I54" s="38" t="s">
+      <c r="I54" s="78" t="s">
         <v>142</v>
       </c>
-      <c r="J54" s="38" t="s">
+      <c r="J54" s="78" t="s">
         <v>145</v>
       </c>
-      <c r="K54" s="38" t="s">
+      <c r="K54" s="78" t="s">
         <v>231</v>
       </c>
-      <c r="L54" s="38" t="s">
+      <c r="L54" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="M54" s="38" t="s">
+      <c r="M54" s="78" t="s">
         <v>156</v>
       </c>
-      <c r="N54" s="38" t="s">
+      <c r="N54" s="78" t="s">
         <v>161</v>
       </c>
-      <c r="O54" s="38" t="s">
+      <c r="O54" s="78" t="s">
         <v>165</v>
       </c>
-      <c r="P54" s="93" t="s">
+      <c r="P54" s="95" t="s">
         <v>171</v>
       </c>
-      <c r="Q54" s="93" t="s">
+      <c r="Q54" s="95" t="s">
         <v>173</v>
       </c>
-      <c r="R54" s="93" t="s">
+      <c r="R54" s="95" t="s">
         <v>182</v>
       </c>
-      <c r="S54" s="91" t="s">
+      <c r="S54" s="99" t="s">
         <v>188</v>
       </c>
-      <c r="T54" s="67" t="s">
+      <c r="T54" s="91" t="s">
         <v>179</v>
       </c>
-      <c r="U54" s="68" t="s">
+      <c r="U54" s="90" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="44"/>
-      <c r="B55" s="44"/>
+      <c r="A55" s="65"/>
+      <c r="B55" s="65"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="95"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="38"/>
-      <c r="I55" s="38"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="38"/>
-      <c r="L55" s="38"/>
-      <c r="M55" s="38"/>
-      <c r="N55" s="38"/>
-      <c r="O55" s="38"/>
-      <c r="P55" s="93"/>
-      <c r="Q55" s="93"/>
-      <c r="R55" s="93"/>
-      <c r="S55" s="91"/>
-      <c r="T55" s="67"/>
-      <c r="U55" s="68"/>
+      <c r="D55" s="62"/>
+      <c r="E55" s="61"/>
+      <c r="F55" s="83"/>
+      <c r="G55" s="78"/>
+      <c r="H55" s="78"/>
+      <c r="I55" s="78"/>
+      <c r="J55" s="78"/>
+      <c r="K55" s="78"/>
+      <c r="L55" s="78"/>
+      <c r="M55" s="78"/>
+      <c r="N55" s="78"/>
+      <c r="O55" s="78"/>
+      <c r="P55" s="95"/>
+      <c r="Q55" s="95"/>
+      <c r="R55" s="95"/>
+      <c r="S55" s="99"/>
+      <c r="T55" s="91"/>
+      <c r="U55" s="90"/>
     </row>
     <row r="56" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="44"/>
-      <c r="B56" s="44"/>
+      <c r="A56" s="65"/>
+      <c r="B56" s="65"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="56">
+      <c r="D56" s="74">
         <v>132.91</v>
       </c>
-      <c r="E56" s="52">
+      <c r="E56" s="63">
         <v>137.33000000000001</v>
       </c>
-      <c r="F56" s="95"/>
-      <c r="G56" s="40">
+      <c r="F56" s="83"/>
+      <c r="G56" s="80">
         <v>178.49</v>
       </c>
-      <c r="H56" s="40">
+      <c r="H56" s="80">
         <v>180.95</v>
       </c>
-      <c r="I56" s="40">
+      <c r="I56" s="80">
         <v>183.84</v>
       </c>
-      <c r="J56" s="40">
+      <c r="J56" s="80">
         <v>186.21</v>
       </c>
-      <c r="K56" s="40">
+      <c r="K56" s="80">
         <v>190.23</v>
       </c>
-      <c r="L56" s="40">
+      <c r="L56" s="80">
         <v>192.22</v>
       </c>
-      <c r="M56" s="40">
+      <c r="M56" s="80">
         <v>195.08</v>
       </c>
-      <c r="N56" s="40">
+      <c r="N56" s="80">
         <v>196.97</v>
       </c>
-      <c r="O56" s="40">
+      <c r="O56" s="80">
         <v>200.59</v>
       </c>
-      <c r="P56" s="42">
+      <c r="P56" s="96">
         <v>204.38</v>
       </c>
-      <c r="Q56" s="42">
+      <c r="Q56" s="96">
         <v>207.2</v>
       </c>
-      <c r="R56" s="42">
+      <c r="R56" s="96">
         <v>208.98</v>
       </c>
-      <c r="S56" s="74">
+      <c r="S56" s="92">
         <v>209</v>
       </c>
-      <c r="T56" s="69">
+      <c r="T56" s="102">
         <v>210</v>
       </c>
-      <c r="U56" s="71">
+      <c r="U56" s="104">
         <v>222</v>
       </c>
     </row>
     <row r="57" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="44"/>
-      <c r="B57" s="44"/>
+      <c r="A57" s="65"/>
+      <c r="B57" s="65"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="56"/>
-      <c r="E57" s="53"/>
-      <c r="F57" s="96"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="41"/>
-      <c r="J57" s="41"/>
-      <c r="K57" s="41"/>
-      <c r="L57" s="41"/>
-      <c r="M57" s="41"/>
-      <c r="N57" s="41"/>
-      <c r="O57" s="41"/>
-      <c r="P57" s="43"/>
-      <c r="Q57" s="43"/>
-      <c r="R57" s="43"/>
-      <c r="S57" s="75"/>
-      <c r="T57" s="70"/>
-      <c r="U57" s="72"/>
+      <c r="D57" s="74"/>
+      <c r="E57" s="64"/>
+      <c r="F57" s="84"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="81"/>
+      <c r="I57" s="81"/>
+      <c r="J57" s="81"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="81"/>
+      <c r="M57" s="81"/>
+      <c r="N57" s="81"/>
+      <c r="O57" s="81"/>
+      <c r="P57" s="97"/>
+      <c r="Q57" s="97"/>
+      <c r="R57" s="97"/>
+      <c r="S57" s="93"/>
+      <c r="T57" s="103"/>
+      <c r="U57" s="105"/>
     </row>
     <row r="58" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="44"/>
-      <c r="B58" s="44">
+      <c r="A58" s="65"/>
+      <c r="B58" s="65">
         <v>7</v>
       </c>
       <c r="C58" s="7"/>
-      <c r="D58" s="47">
+      <c r="D58" s="72">
         <v>102</v>
       </c>
-      <c r="E58" s="55">
+      <c r="E58" s="76">
         <v>102</v>
       </c>
-      <c r="F58" s="97" t="s">
+      <c r="F58" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="G58" s="37">
+      <c r="G58" s="77">
         <v>104</v>
       </c>
-      <c r="H58" s="37">
+      <c r="H58" s="77">
         <v>105</v>
       </c>
-      <c r="I58" s="37">
+      <c r="I58" s="77">
         <v>106</v>
       </c>
-      <c r="J58" s="37">
+      <c r="J58" s="77">
         <v>107</v>
       </c>
-      <c r="K58" s="37">
+      <c r="K58" s="77">
         <v>108</v>
       </c>
-      <c r="L58" s="37">
+      <c r="L58" s="77">
         <v>109</v>
       </c>
-      <c r="M58" s="37">
+      <c r="M58" s="77">
         <v>110</v>
       </c>
-      <c r="N58" s="37">
+      <c r="N58" s="77">
         <v>111</v>
       </c>
-      <c r="O58" s="37">
+      <c r="O58" s="77">
         <v>112</v>
       </c>
-      <c r="P58" s="92">
+      <c r="P58" s="94">
         <v>113</v>
       </c>
-      <c r="Q58" s="92">
+      <c r="Q58" s="94">
         <v>114</v>
       </c>
-      <c r="R58" s="92">
+      <c r="R58" s="94">
         <v>115</v>
       </c>
-      <c r="S58" s="92">
+      <c r="S58" s="94">
         <v>116</v>
       </c>
-      <c r="T58" s="92">
+      <c r="T58" s="94">
         <v>117</v>
       </c>
-      <c r="U58" s="92">
+      <c r="U58" s="94">
         <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="44"/>
-      <c r="B59" s="44"/>
+      <c r="A59" s="65"/>
+      <c r="B59" s="65"/>
       <c r="C59" s="7"/>
-      <c r="D59" s="45"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="98"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="38"/>
-      <c r="K59" s="38"/>
-      <c r="L59" s="38"/>
-      <c r="M59" s="38"/>
-      <c r="N59" s="38"/>
-      <c r="O59" s="38"/>
-      <c r="P59" s="93"/>
-      <c r="Q59" s="93"/>
-      <c r="R59" s="93"/>
-      <c r="S59" s="93"/>
-      <c r="T59" s="93"/>
-      <c r="U59" s="93"/>
+      <c r="D59" s="62"/>
+      <c r="E59" s="61"/>
+      <c r="F59" s="86"/>
+      <c r="G59" s="78"/>
+      <c r="H59" s="78"/>
+      <c r="I59" s="78"/>
+      <c r="J59" s="78"/>
+      <c r="K59" s="78"/>
+      <c r="L59" s="78"/>
+      <c r="M59" s="78"/>
+      <c r="N59" s="78"/>
+      <c r="O59" s="78"/>
+      <c r="P59" s="95"/>
+      <c r="Q59" s="95"/>
+      <c r="R59" s="95"/>
+      <c r="S59" s="95"/>
+      <c r="T59" s="95"/>
+      <c r="U59" s="95"/>
     </row>
     <row r="60" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="44"/>
-      <c r="B60" s="44"/>
+      <c r="A60" s="65"/>
+      <c r="B60" s="65"/>
       <c r="C60" s="7"/>
-      <c r="D60" s="48" t="s">
+      <c r="D60" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="54" t="s">
+      <c r="E60" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="F60" s="98"/>
-      <c r="G60" s="36" t="s">
+      <c r="F60" s="86"/>
+      <c r="G60" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="H60" s="36" t="s">
+      <c r="H60" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="I60" s="36" t="s">
+      <c r="I60" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="J60" s="36" t="s">
+      <c r="J60" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="K60" s="36" t="s">
+      <c r="K60" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="L60" s="36" t="s">
+      <c r="L60" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="M60" s="36" t="s">
+      <c r="M60" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="N60" s="36" t="s">
+      <c r="N60" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="O60" s="36" t="s">
+      <c r="O60" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="P60" s="78" t="s">
+      <c r="P60" s="88" t="s">
         <v>85</v>
       </c>
-      <c r="Q60" s="78" t="s">
+      <c r="Q60" s="88" t="s">
         <v>86</v>
       </c>
-      <c r="R60" s="78" t="s">
+      <c r="R60" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="S60" s="78" t="s">
+      <c r="S60" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="T60" s="78" t="s">
+      <c r="T60" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="U60" s="78" t="s">
+      <c r="U60" s="88" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="44"/>
-      <c r="B61" s="44"/>
+      <c r="A61" s="65"/>
+      <c r="B61" s="65"/>
       <c r="C61" s="7"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="54"/>
-      <c r="F61" s="98"/>
-      <c r="G61" s="36"/>
-      <c r="H61" s="36"/>
-      <c r="I61" s="36"/>
-      <c r="J61" s="36"/>
-      <c r="K61" s="36"/>
-      <c r="L61" s="36"/>
-      <c r="M61" s="36"/>
-      <c r="N61" s="36"/>
-      <c r="O61" s="36"/>
-      <c r="P61" s="78"/>
-      <c r="Q61" s="78"/>
-      <c r="R61" s="78"/>
-      <c r="S61" s="78"/>
-      <c r="T61" s="78"/>
-      <c r="U61" s="78"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="66"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="79"/>
+      <c r="H61" s="79"/>
+      <c r="I61" s="79"/>
+      <c r="J61" s="79"/>
+      <c r="K61" s="79"/>
+      <c r="L61" s="79"/>
+      <c r="M61" s="79"/>
+      <c r="N61" s="79"/>
+      <c r="O61" s="79"/>
+      <c r="P61" s="88"/>
+      <c r="Q61" s="88"/>
+      <c r="R61" s="88"/>
+      <c r="S61" s="88"/>
+      <c r="T61" s="88"/>
+      <c r="U61" s="88"/>
     </row>
     <row r="62" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="44"/>
-      <c r="B62" s="44"/>
+      <c r="A62" s="65"/>
+      <c r="B62" s="65"/>
       <c r="C62" s="7"/>
-      <c r="D62" s="48"/>
-      <c r="E62" s="54"/>
-      <c r="F62" s="98"/>
-      <c r="G62" s="36"/>
-      <c r="H62" s="36"/>
-      <c r="I62" s="36"/>
-      <c r="J62" s="36"/>
-      <c r="K62" s="36"/>
-      <c r="L62" s="36"/>
-      <c r="M62" s="36"/>
-      <c r="N62" s="36"/>
-      <c r="O62" s="36"/>
-      <c r="P62" s="78"/>
-      <c r="Q62" s="78"/>
-      <c r="R62" s="78"/>
-      <c r="S62" s="78"/>
-      <c r="T62" s="78"/>
-      <c r="U62" s="78"/>
+      <c r="D62" s="73"/>
+      <c r="E62" s="66"/>
+      <c r="F62" s="86"/>
+      <c r="G62" s="79"/>
+      <c r="H62" s="79"/>
+      <c r="I62" s="79"/>
+      <c r="J62" s="79"/>
+      <c r="K62" s="79"/>
+      <c r="L62" s="79"/>
+      <c r="M62" s="79"/>
+      <c r="N62" s="79"/>
+      <c r="O62" s="79"/>
+      <c r="P62" s="88"/>
+      <c r="Q62" s="88"/>
+      <c r="R62" s="88"/>
+      <c r="S62" s="88"/>
+      <c r="T62" s="88"/>
+      <c r="U62" s="88"/>
     </row>
     <row r="63" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="44"/>
-      <c r="B63" s="44"/>
+      <c r="A63" s="65"/>
+      <c r="B63" s="65"/>
       <c r="C63" s="7"/>
-      <c r="D63" s="45" t="s">
+      <c r="D63" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="E63" s="51" t="s">
+      <c r="E63" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="F63" s="98"/>
-      <c r="G63" s="38" t="s">
+      <c r="F63" s="86"/>
+      <c r="G63" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="H63" s="38" t="s">
+      <c r="H63" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="I63" s="38" t="s">
+      <c r="I63" s="78" t="s">
         <v>143</v>
       </c>
-      <c r="J63" s="38" t="s">
+      <c r="J63" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="K63" s="38" t="s">
+      <c r="K63" s="78" t="s">
         <v>150</v>
       </c>
-      <c r="L63" s="38" t="s">
+      <c r="L63" s="78" t="s">
         <v>154</v>
       </c>
-      <c r="M63" s="38" t="s">
+      <c r="M63" s="78" t="s">
         <v>158</v>
       </c>
-      <c r="N63" s="38" t="s">
+      <c r="N63" s="78" t="s">
         <v>162</v>
       </c>
-      <c r="O63" s="38" t="s">
+      <c r="O63" s="78" t="s">
         <v>232</v>
       </c>
-      <c r="P63" s="93" t="s">
+      <c r="P63" s="95" t="s">
         <v>233</v>
       </c>
-      <c r="Q63" s="93" t="s">
+      <c r="Q63" s="95" t="s">
         <v>172</v>
       </c>
-      <c r="R63" s="93" t="s">
+      <c r="R63" s="95" t="s">
         <v>183</v>
       </c>
-      <c r="S63" s="93" t="s">
+      <c r="S63" s="95" t="s">
         <v>189</v>
       </c>
-      <c r="T63" s="93" t="s">
+      <c r="T63" s="95" t="s">
         <v>234</v>
       </c>
-      <c r="U63" s="93" t="s">
+      <c r="U63" s="95" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="64" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="44"/>
-      <c r="B64" s="44"/>
+      <c r="A64" s="65"/>
+      <c r="B64" s="65"/>
       <c r="C64" s="7"/>
-      <c r="D64" s="45"/>
-      <c r="E64" s="51"/>
-      <c r="F64" s="98"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="38"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="38"/>
-      <c r="L64" s="38"/>
-      <c r="M64" s="38"/>
-      <c r="N64" s="38"/>
-      <c r="O64" s="38"/>
-      <c r="P64" s="93"/>
-      <c r="Q64" s="93"/>
-      <c r="R64" s="93"/>
-      <c r="S64" s="93"/>
-      <c r="T64" s="93"/>
-      <c r="U64" s="93"/>
+      <c r="D64" s="62"/>
+      <c r="E64" s="61"/>
+      <c r="F64" s="86"/>
+      <c r="G64" s="78"/>
+      <c r="H64" s="78"/>
+      <c r="I64" s="78"/>
+      <c r="J64" s="78"/>
+      <c r="K64" s="78"/>
+      <c r="L64" s="78"/>
+      <c r="M64" s="78"/>
+      <c r="N64" s="78"/>
+      <c r="O64" s="78"/>
+      <c r="P64" s="95"/>
+      <c r="Q64" s="95"/>
+      <c r="R64" s="95"/>
+      <c r="S64" s="95"/>
+      <c r="T64" s="95"/>
+      <c r="U64" s="95"/>
     </row>
     <row r="65" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="44"/>
-      <c r="B65" s="44"/>
+      <c r="A65" s="65"/>
+      <c r="B65" s="65"/>
       <c r="C65" s="7"/>
-      <c r="D65" s="56">
+      <c r="D65" s="74">
         <v>223</v>
       </c>
-      <c r="E65" s="52">
+      <c r="E65" s="63">
         <v>226</v>
       </c>
-      <c r="F65" s="98"/>
-      <c r="G65" s="40">
+      <c r="F65" s="86"/>
+      <c r="G65" s="80">
         <v>267</v>
       </c>
-      <c r="H65" s="40">
+      <c r="H65" s="80">
         <v>268</v>
       </c>
-      <c r="I65" s="40">
+      <c r="I65" s="80">
         <v>269</v>
       </c>
-      <c r="J65" s="40">
+      <c r="J65" s="80">
         <v>270</v>
       </c>
-      <c r="K65" s="40">
+      <c r="K65" s="80">
         <v>269</v>
       </c>
-      <c r="L65" s="40">
+      <c r="L65" s="80">
         <v>277</v>
       </c>
-      <c r="M65" s="40">
+      <c r="M65" s="80">
         <v>281</v>
       </c>
-      <c r="N65" s="40">
+      <c r="N65" s="80">
         <v>282</v>
       </c>
-      <c r="O65" s="40">
+      <c r="O65" s="80">
         <v>285</v>
       </c>
-      <c r="P65" s="42">
+      <c r="P65" s="96">
         <v>286</v>
       </c>
-      <c r="Q65" s="42">
+      <c r="Q65" s="96">
         <v>290</v>
       </c>
-      <c r="R65" s="42">
+      <c r="R65" s="96">
         <v>290</v>
       </c>
-      <c r="S65" s="42">
+      <c r="S65" s="96">
         <v>293</v>
       </c>
-      <c r="T65" s="42">
+      <c r="T65" s="96">
         <v>294</v>
       </c>
-      <c r="U65" s="42">
+      <c r="U65" s="96">
         <v>294</v>
       </c>
     </row>
     <row r="66" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="44"/>
-      <c r="B66" s="44"/>
+      <c r="A66" s="65"/>
+      <c r="B66" s="65"/>
       <c r="C66" s="7"/>
-      <c r="D66" s="57"/>
-      <c r="E66" s="53"/>
-      <c r="F66" s="99"/>
-      <c r="G66" s="41"/>
-      <c r="H66" s="41"/>
-      <c r="I66" s="41"/>
-      <c r="J66" s="41"/>
-      <c r="K66" s="41"/>
-      <c r="L66" s="41"/>
-      <c r="M66" s="41"/>
-      <c r="N66" s="41"/>
-      <c r="O66" s="41"/>
-      <c r="P66" s="43"/>
-      <c r="Q66" s="43"/>
-      <c r="R66" s="43"/>
-      <c r="S66" s="43"/>
-      <c r="T66" s="43"/>
-      <c r="U66" s="43"/>
+      <c r="D66" s="75"/>
+      <c r="E66" s="64"/>
+      <c r="F66" s="87"/>
+      <c r="G66" s="81"/>
+      <c r="H66" s="81"/>
+      <c r="I66" s="81"/>
+      <c r="J66" s="81"/>
+      <c r="K66" s="81"/>
+      <c r="L66" s="81"/>
+      <c r="M66" s="81"/>
+      <c r="N66" s="81"/>
+      <c r="O66" s="81"/>
+      <c r="P66" s="97"/>
+      <c r="Q66" s="97"/>
+      <c r="R66" s="97"/>
+      <c r="S66" s="97"/>
+      <c r="T66" s="97"/>
+      <c r="U66" s="97"/>
     </row>
     <row r="67" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="12"/>
@@ -4475,207 +4475,207 @@
     </row>
     <row r="69" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E69" s="8"/>
-      <c r="F69" s="49" t="s">
+      <c r="F69" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="G69" s="34">
+      <c r="G69" s="121">
         <v>57</v>
       </c>
-      <c r="H69" s="34">
+      <c r="H69" s="121">
         <v>58</v>
       </c>
-      <c r="I69" s="34">
+      <c r="I69" s="121">
         <v>59</v>
       </c>
-      <c r="J69" s="34">
+      <c r="J69" s="121">
         <v>60</v>
       </c>
-      <c r="K69" s="34">
+      <c r="K69" s="121">
         <v>61</v>
       </c>
-      <c r="L69" s="34">
+      <c r="L69" s="121">
         <v>62</v>
       </c>
-      <c r="M69" s="34">
+      <c r="M69" s="121">
         <v>63</v>
       </c>
-      <c r="N69" s="34">
+      <c r="N69" s="121">
         <v>64</v>
       </c>
-      <c r="O69" s="34">
+      <c r="O69" s="121">
         <v>65</v>
       </c>
-      <c r="P69" s="34">
+      <c r="P69" s="121">
         <v>66</v>
       </c>
-      <c r="Q69" s="34">
+      <c r="Q69" s="121">
         <v>67</v>
       </c>
-      <c r="R69" s="34">
+      <c r="R69" s="121">
         <v>68</v>
       </c>
-      <c r="S69" s="34">
+      <c r="S69" s="121">
         <v>69</v>
       </c>
-      <c r="T69" s="34">
+      <c r="T69" s="121">
         <v>70</v>
       </c>
-      <c r="U69" s="34">
+      <c r="U69" s="121">
         <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E70" s="8"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="34"/>
-      <c r="J70" s="34"/>
-      <c r="K70" s="34"/>
-      <c r="L70" s="34"/>
-      <c r="M70" s="34"/>
-      <c r="N70" s="34"/>
-      <c r="O70" s="35"/>
-      <c r="P70" s="35"/>
-      <c r="Q70" s="35"/>
-      <c r="R70" s="35"/>
-      <c r="S70" s="35"/>
-      <c r="T70" s="35"/>
-      <c r="U70" s="34"/>
+      <c r="F70" s="128"/>
+      <c r="G70" s="120"/>
+      <c r="H70" s="120"/>
+      <c r="I70" s="121"/>
+      <c r="J70" s="121"/>
+      <c r="K70" s="121"/>
+      <c r="L70" s="121"/>
+      <c r="M70" s="121"/>
+      <c r="N70" s="121"/>
+      <c r="O70" s="120"/>
+      <c r="P70" s="120"/>
+      <c r="Q70" s="120"/>
+      <c r="R70" s="120"/>
+      <c r="S70" s="120"/>
+      <c r="T70" s="120"/>
+      <c r="U70" s="121"/>
     </row>
     <row r="71" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E71" s="8"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="33" t="s">
+      <c r="F71" s="128"/>
+      <c r="G71" s="122" t="s">
         <v>91</v>
       </c>
-      <c r="H71" s="33" t="s">
+      <c r="H71" s="122" t="s">
         <v>92</v>
       </c>
-      <c r="I71" s="33" t="s">
+      <c r="I71" s="122" t="s">
         <v>93</v>
       </c>
-      <c r="J71" s="33" t="s">
+      <c r="J71" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="K71" s="33" t="s">
+      <c r="K71" s="122" t="s">
         <v>95</v>
       </c>
-      <c r="L71" s="33" t="s">
+      <c r="L71" s="122" t="s">
         <v>96</v>
       </c>
-      <c r="M71" s="33" t="s">
+      <c r="M71" s="122" t="s">
         <v>97</v>
       </c>
-      <c r="N71" s="33" t="s">
+      <c r="N71" s="122" t="s">
         <v>98</v>
       </c>
-      <c r="O71" s="33" t="s">
+      <c r="O71" s="122" t="s">
         <v>99</v>
       </c>
-      <c r="P71" s="33" t="s">
+      <c r="P71" s="122" t="s">
         <v>100</v>
       </c>
-      <c r="Q71" s="33" t="s">
+      <c r="Q71" s="122" t="s">
         <v>101</v>
       </c>
-      <c r="R71" s="33" t="s">
+      <c r="R71" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="S71" s="33" t="s">
+      <c r="S71" s="122" t="s">
         <v>103</v>
       </c>
-      <c r="T71" s="33" t="s">
+      <c r="T71" s="122" t="s">
         <v>104</v>
       </c>
-      <c r="U71" s="33" t="s">
+      <c r="U71" s="122" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E72" s="8"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="33"/>
-      <c r="J72" s="33"/>
-      <c r="K72" s="33"/>
-      <c r="L72" s="33"/>
-      <c r="M72" s="33"/>
-      <c r="N72" s="33"/>
-      <c r="O72" s="33"/>
-      <c r="P72" s="33"/>
-      <c r="Q72" s="33"/>
-      <c r="R72" s="33"/>
-      <c r="S72" s="33"/>
-      <c r="T72" s="33"/>
-      <c r="U72" s="33"/>
+      <c r="F72" s="128"/>
+      <c r="G72" s="122"/>
+      <c r="H72" s="122"/>
+      <c r="I72" s="122"/>
+      <c r="J72" s="122"/>
+      <c r="K72" s="122"/>
+      <c r="L72" s="122"/>
+      <c r="M72" s="122"/>
+      <c r="N72" s="122"/>
+      <c r="O72" s="122"/>
+      <c r="P72" s="122"/>
+      <c r="Q72" s="122"/>
+      <c r="R72" s="122"/>
+      <c r="S72" s="122"/>
+      <c r="T72" s="122"/>
+      <c r="U72" s="122"/>
     </row>
     <row r="73" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E73" s="8"/>
-      <c r="F73" s="50"/>
-      <c r="G73" s="33"/>
-      <c r="H73" s="33"/>
-      <c r="I73" s="33"/>
-      <c r="J73" s="33"/>
-      <c r="K73" s="33"/>
-      <c r="L73" s="33"/>
-      <c r="M73" s="33"/>
-      <c r="N73" s="33"/>
-      <c r="O73" s="33"/>
-      <c r="P73" s="33"/>
-      <c r="Q73" s="33"/>
-      <c r="R73" s="33"/>
-      <c r="S73" s="33"/>
-      <c r="T73" s="33"/>
-      <c r="U73" s="33"/>
+      <c r="F73" s="128"/>
+      <c r="G73" s="122"/>
+      <c r="H73" s="122"/>
+      <c r="I73" s="122"/>
+      <c r="J73" s="122"/>
+      <c r="K73" s="122"/>
+      <c r="L73" s="122"/>
+      <c r="M73" s="122"/>
+      <c r="N73" s="122"/>
+      <c r="O73" s="122"/>
+      <c r="P73" s="122"/>
+      <c r="Q73" s="122"/>
+      <c r="R73" s="122"/>
+      <c r="S73" s="122"/>
+      <c r="T73" s="122"/>
+      <c r="U73" s="122"/>
     </row>
     <row r="74" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E74" s="8"/>
-      <c r="F74" s="50"/>
-      <c r="G74" s="35" t="s">
+      <c r="F74" s="128"/>
+      <c r="G74" s="120" t="s">
         <v>200</v>
       </c>
-      <c r="H74" s="35" t="s">
+      <c r="H74" s="120" t="s">
         <v>201</v>
       </c>
-      <c r="I74" s="35" t="s">
+      <c r="I74" s="120" t="s">
         <v>202</v>
       </c>
-      <c r="J74" s="35" t="s">
+      <c r="J74" s="120" t="s">
         <v>203</v>
       </c>
-      <c r="K74" s="35" t="s">
+      <c r="K74" s="120" t="s">
         <v>205</v>
       </c>
-      <c r="L74" s="35" t="s">
+      <c r="L74" s="120" t="s">
         <v>204</v>
       </c>
-      <c r="M74" s="35" t="s">
+      <c r="M74" s="120" t="s">
         <v>206</v>
       </c>
-      <c r="N74" s="35" t="s">
+      <c r="N74" s="120" t="s">
         <v>207</v>
       </c>
-      <c r="O74" s="35" t="s">
+      <c r="O74" s="120" t="s">
         <v>208</v>
       </c>
-      <c r="P74" s="35" t="s">
+      <c r="P74" s="120" t="s">
         <v>209</v>
       </c>
-      <c r="Q74" s="35" t="s">
+      <c r="Q74" s="120" t="s">
         <v>210</v>
       </c>
-      <c r="R74" s="35" t="s">
+      <c r="R74" s="120" t="s">
         <v>211</v>
       </c>
-      <c r="S74" s="35" t="s">
+      <c r="S74" s="120" t="s">
         <v>212</v>
       </c>
-      <c r="T74" s="35" t="s">
+      <c r="T74" s="120" t="s">
         <v>213</v>
       </c>
-      <c r="U74" s="35" t="s">
+      <c r="U74" s="120" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4683,71 +4683,71 @@
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="E75" s="8"/>
-      <c r="F75" s="50"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
-      <c r="J75" s="35"/>
-      <c r="K75" s="35"/>
-      <c r="L75" s="35"/>
-      <c r="M75" s="35"/>
-      <c r="N75" s="35"/>
-      <c r="O75" s="35"/>
-      <c r="P75" s="35"/>
-      <c r="Q75" s="35"/>
-      <c r="R75" s="35"/>
-      <c r="S75" s="35"/>
-      <c r="T75" s="35"/>
-      <c r="U75" s="35"/>
+      <c r="F75" s="128"/>
+      <c r="G75" s="120"/>
+      <c r="H75" s="120"/>
+      <c r="I75" s="120"/>
+      <c r="J75" s="120"/>
+      <c r="K75" s="120"/>
+      <c r="L75" s="120"/>
+      <c r="M75" s="120"/>
+      <c r="N75" s="120"/>
+      <c r="O75" s="120"/>
+      <c r="P75" s="120"/>
+      <c r="Q75" s="120"/>
+      <c r="R75" s="120"/>
+      <c r="S75" s="120"/>
+      <c r="T75" s="120"/>
+      <c r="U75" s="120"/>
     </row>
     <row r="76" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="E76" s="8"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="32">
+      <c r="F76" s="128"/>
+      <c r="G76" s="124">
         <v>138.91</v>
       </c>
-      <c r="H76" s="32">
+      <c r="H76" s="124">
         <v>140.12</v>
       </c>
-      <c r="I76" s="32">
+      <c r="I76" s="124">
         <v>140.91</v>
       </c>
-      <c r="J76" s="32">
+      <c r="J76" s="124">
         <v>144.24</v>
       </c>
-      <c r="K76" s="32">
+      <c r="K76" s="124">
         <v>145</v>
       </c>
-      <c r="L76" s="32">
+      <c r="L76" s="124">
         <v>150.36000000000001</v>
       </c>
-      <c r="M76" s="32">
+      <c r="M76" s="124">
         <v>151.96</v>
       </c>
-      <c r="N76" s="32">
+      <c r="N76" s="124">
         <v>157.25</v>
       </c>
-      <c r="O76" s="32">
+      <c r="O76" s="124">
         <v>158.93</v>
       </c>
-      <c r="P76" s="32">
+      <c r="P76" s="124">
         <v>162.5</v>
       </c>
-      <c r="Q76" s="32">
+      <c r="Q76" s="124">
         <v>164.93</v>
       </c>
-      <c r="R76" s="32">
+      <c r="R76" s="124">
         <v>167.26</v>
       </c>
-      <c r="S76" s="32">
+      <c r="S76" s="124">
         <v>168.93</v>
       </c>
-      <c r="T76" s="32">
+      <c r="T76" s="124">
         <v>173.05</v>
       </c>
-      <c r="U76" s="32">
+      <c r="U76" s="124">
         <v>174.97</v>
       </c>
     </row>
@@ -4755,338 +4755,338 @@
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="E77" s="8"/>
-      <c r="F77" s="50"/>
-      <c r="G77" s="39"/>
-      <c r="H77" s="39"/>
-      <c r="I77" s="39"/>
-      <c r="J77" s="39"/>
-      <c r="K77" s="39"/>
-      <c r="L77" s="39"/>
-      <c r="M77" s="39"/>
-      <c r="N77" s="39"/>
-      <c r="O77" s="32"/>
-      <c r="P77" s="32"/>
-      <c r="Q77" s="32"/>
-      <c r="R77" s="32"/>
-      <c r="S77" s="32"/>
-      <c r="T77" s="32"/>
-      <c r="U77" s="32"/>
+      <c r="F77" s="128"/>
+      <c r="G77" s="125"/>
+      <c r="H77" s="125"/>
+      <c r="I77" s="125"/>
+      <c r="J77" s="125"/>
+      <c r="K77" s="125"/>
+      <c r="L77" s="125"/>
+      <c r="M77" s="125"/>
+      <c r="N77" s="125"/>
+      <c r="O77" s="124"/>
+      <c r="P77" s="124"/>
+      <c r="Q77" s="124"/>
+      <c r="R77" s="124"/>
+      <c r="S77" s="124"/>
+      <c r="T77" s="124"/>
+      <c r="U77" s="124"/>
     </row>
     <row r="78" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D78" s="105" t="s">
+      <c r="D78" s="39" t="s">
         <v>248</v>
       </c>
-      <c r="E78" s="117"/>
-      <c r="F78" s="120" t="s">
+      <c r="E78" s="51"/>
+      <c r="F78" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="G78" s="31">
+      <c r="G78" s="55">
         <v>89</v>
       </c>
-      <c r="H78" s="31">
+      <c r="H78" s="55">
         <v>90</v>
       </c>
-      <c r="I78" s="31">
+      <c r="I78" s="55">
         <v>91</v>
       </c>
-      <c r="J78" s="31">
+      <c r="J78" s="55">
         <v>92</v>
       </c>
-      <c r="K78" s="31">
+      <c r="K78" s="55">
         <v>93</v>
       </c>
-      <c r="L78" s="31">
+      <c r="L78" s="55">
         <v>94</v>
       </c>
-      <c r="M78" s="31">
+      <c r="M78" s="55">
         <v>95</v>
       </c>
-      <c r="N78" s="31">
+      <c r="N78" s="55">
         <v>96</v>
       </c>
-      <c r="O78" s="31">
+      <c r="O78" s="55">
         <v>97</v>
       </c>
-      <c r="P78" s="31">
+      <c r="P78" s="55">
         <v>98</v>
       </c>
-      <c r="Q78" s="31">
+      <c r="Q78" s="55">
         <v>99</v>
       </c>
-      <c r="R78" s="31">
+      <c r="R78" s="55">
         <v>100</v>
       </c>
-      <c r="S78" s="31">
+      <c r="S78" s="55">
         <v>101</v>
       </c>
-      <c r="T78" s="31">
+      <c r="T78" s="55">
         <v>102</v>
       </c>
-      <c r="U78" s="31">
+      <c r="U78" s="55">
         <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D79" s="105"/>
-      <c r="E79" s="117"/>
-      <c r="F79" s="120"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
-      <c r="J79" s="31"/>
-      <c r="K79" s="31"/>
-      <c r="L79" s="31"/>
-      <c r="M79" s="31"/>
-      <c r="N79" s="31"/>
-      <c r="O79" s="31"/>
-      <c r="P79" s="31"/>
-      <c r="Q79" s="31"/>
-      <c r="R79" s="31"/>
-      <c r="S79" s="31"/>
-      <c r="T79" s="31"/>
-      <c r="U79" s="31"/>
+      <c r="D79" s="39"/>
+      <c r="E79" s="51"/>
+      <c r="F79" s="54"/>
+      <c r="G79" s="55"/>
+      <c r="H79" s="55"/>
+      <c r="I79" s="55"/>
+      <c r="J79" s="55"/>
+      <c r="K79" s="55"/>
+      <c r="L79" s="55"/>
+      <c r="M79" s="55"/>
+      <c r="N79" s="55"/>
+      <c r="O79" s="55"/>
+      <c r="P79" s="55"/>
+      <c r="Q79" s="55"/>
+      <c r="R79" s="55"/>
+      <c r="S79" s="55"/>
+      <c r="T79" s="55"/>
+      <c r="U79" s="55"/>
     </row>
     <row r="80" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D80" s="106" t="s">
+      <c r="D80" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="E80" s="118"/>
-      <c r="F80" s="120"/>
-      <c r="G80" s="116" t="s">
+      <c r="E80" s="52"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="H80" s="59" t="s">
+      <c r="H80" s="108" t="s">
         <v>107</v>
       </c>
-      <c r="I80" s="60" t="s">
+      <c r="I80" s="123" t="s">
         <v>108</v>
       </c>
-      <c r="J80" s="59" t="s">
+      <c r="J80" s="108" t="s">
         <v>109</v>
       </c>
-      <c r="K80" s="83" t="s">
+      <c r="K80" s="112" t="s">
         <v>110</v>
       </c>
-      <c r="L80" s="59" t="s">
+      <c r="L80" s="108" t="s">
         <v>111</v>
       </c>
-      <c r="M80" s="59" t="s">
+      <c r="M80" s="108" t="s">
         <v>112</v>
       </c>
-      <c r="N80" s="59" t="s">
+      <c r="N80" s="108" t="s">
         <v>113</v>
       </c>
-      <c r="O80" s="59" t="s">
+      <c r="O80" s="108" t="s">
         <v>114</v>
       </c>
-      <c r="P80" s="59" t="s">
+      <c r="P80" s="108" t="s">
         <v>115</v>
       </c>
-      <c r="Q80" s="59" t="s">
+      <c r="Q80" s="108" t="s">
         <v>116</v>
       </c>
-      <c r="R80" s="59" t="s">
+      <c r="R80" s="108" t="s">
         <v>117</v>
       </c>
-      <c r="S80" s="59" t="s">
+      <c r="S80" s="108" t="s">
         <v>118</v>
       </c>
-      <c r="T80" s="59" t="s">
+      <c r="T80" s="108" t="s">
         <v>119</v>
       </c>
-      <c r="U80" s="59" t="s">
+      <c r="U80" s="108" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D81" s="106"/>
-      <c r="E81" s="118"/>
-      <c r="F81" s="120"/>
-      <c r="G81" s="116"/>
-      <c r="H81" s="59"/>
-      <c r="I81" s="60"/>
-      <c r="J81" s="59"/>
-      <c r="K81" s="83"/>
-      <c r="L81" s="59"/>
-      <c r="M81" s="59"/>
-      <c r="N81" s="59"/>
-      <c r="O81" s="59"/>
-      <c r="P81" s="59"/>
-      <c r="Q81" s="59"/>
-      <c r="R81" s="59"/>
-      <c r="S81" s="59"/>
-      <c r="T81" s="59"/>
-      <c r="U81" s="59"/>
+      <c r="D81" s="40"/>
+      <c r="E81" s="52"/>
+      <c r="F81" s="54"/>
+      <c r="G81" s="50"/>
+      <c r="H81" s="108"/>
+      <c r="I81" s="123"/>
+      <c r="J81" s="108"/>
+      <c r="K81" s="112"/>
+      <c r="L81" s="108"/>
+      <c r="M81" s="108"/>
+      <c r="N81" s="108"/>
+      <c r="O81" s="108"/>
+      <c r="P81" s="108"/>
+      <c r="Q81" s="108"/>
+      <c r="R81" s="108"/>
+      <c r="S81" s="108"/>
+      <c r="T81" s="108"/>
+      <c r="U81" s="108"/>
     </row>
     <row r="82" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D82" s="106"/>
-      <c r="E82" s="118"/>
-      <c r="F82" s="120"/>
-      <c r="G82" s="116"/>
-      <c r="H82" s="59"/>
-      <c r="I82" s="60"/>
-      <c r="J82" s="59"/>
-      <c r="K82" s="83"/>
-      <c r="L82" s="59"/>
-      <c r="M82" s="59"/>
-      <c r="N82" s="59"/>
-      <c r="O82" s="59"/>
-      <c r="P82" s="59"/>
-      <c r="Q82" s="59"/>
-      <c r="R82" s="59"/>
-      <c r="S82" s="59"/>
-      <c r="T82" s="59"/>
-      <c r="U82" s="59"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="52"/>
+      <c r="F82" s="54"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="108"/>
+      <c r="I82" s="123"/>
+      <c r="J82" s="108"/>
+      <c r="K82" s="112"/>
+      <c r="L82" s="108"/>
+      <c r="M82" s="108"/>
+      <c r="N82" s="108"/>
+      <c r="O82" s="108"/>
+      <c r="P82" s="108"/>
+      <c r="Q82" s="108"/>
+      <c r="R82" s="108"/>
+      <c r="S82" s="108"/>
+      <c r="T82" s="108"/>
+      <c r="U82" s="108"/>
     </row>
     <row r="83" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D83" s="105" t="s">
+      <c r="D83" s="39" t="s">
         <v>250</v>
       </c>
-      <c r="E83" s="117"/>
-      <c r="F83" s="120"/>
-      <c r="G83" s="79" t="s">
+      <c r="E83" s="51"/>
+      <c r="F83" s="54"/>
+      <c r="G83" s="119" t="s">
         <v>215</v>
       </c>
-      <c r="H83" s="82" t="s">
+      <c r="H83" s="109" t="s">
         <v>216</v>
       </c>
-      <c r="I83" s="84" t="s">
+      <c r="I83" s="113" t="s">
         <v>217</v>
       </c>
-      <c r="J83" s="82" t="s">
+      <c r="J83" s="109" t="s">
         <v>218</v>
       </c>
-      <c r="K83" s="85" t="s">
+      <c r="K83" s="114" t="s">
         <v>236</v>
       </c>
-      <c r="L83" s="82" t="s">
+      <c r="L83" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="M83" s="82" t="s">
+      <c r="M83" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="N83" s="82" t="s">
+      <c r="N83" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="O83" s="82" t="s">
+      <c r="O83" s="109" t="s">
         <v>222</v>
       </c>
-      <c r="P83" s="82" t="s">
+      <c r="P83" s="109" t="s">
         <v>223</v>
       </c>
-      <c r="Q83" s="82" t="s">
+      <c r="Q83" s="109" t="s">
         <v>224</v>
       </c>
-      <c r="R83" s="82" t="s">
+      <c r="R83" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="S83" s="82" t="s">
+      <c r="S83" s="109" t="s">
         <v>237</v>
       </c>
-      <c r="T83" s="82" t="s">
+      <c r="T83" s="109" t="s">
         <v>226</v>
       </c>
-      <c r="U83" s="82" t="s">
+      <c r="U83" s="109" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="84" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
-      <c r="D84" s="105"/>
-      <c r="E84" s="117"/>
-      <c r="F84" s="120"/>
-      <c r="G84" s="79"/>
-      <c r="H84" s="82"/>
-      <c r="I84" s="84"/>
-      <c r="J84" s="82"/>
-      <c r="K84" s="85"/>
-      <c r="L84" s="82"/>
-      <c r="M84" s="82"/>
-      <c r="N84" s="82"/>
-      <c r="O84" s="82"/>
-      <c r="P84" s="82"/>
-      <c r="Q84" s="82"/>
-      <c r="R84" s="82"/>
-      <c r="S84" s="82"/>
-      <c r="T84" s="82"/>
-      <c r="U84" s="82"/>
+      <c r="D84" s="39"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="54"/>
+      <c r="G84" s="119"/>
+      <c r="H84" s="109"/>
+      <c r="I84" s="113"/>
+      <c r="J84" s="109"/>
+      <c r="K84" s="114"/>
+      <c r="L84" s="109"/>
+      <c r="M84" s="109"/>
+      <c r="N84" s="109"/>
+      <c r="O84" s="109"/>
+      <c r="P84" s="109"/>
+      <c r="Q84" s="109"/>
+      <c r="R84" s="109"/>
+      <c r="S84" s="109"/>
+      <c r="T84" s="109"/>
+      <c r="U84" s="109"/>
     </row>
     <row r="85" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
-      <c r="D85" s="107" t="s">
+      <c r="D85" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="E85" s="119"/>
-      <c r="F85" s="120"/>
-      <c r="G85" s="114">
+      <c r="E85" s="53"/>
+      <c r="F85" s="54"/>
+      <c r="G85" s="48">
         <v>227</v>
       </c>
-      <c r="H85" s="80">
+      <c r="H85" s="110">
         <v>232.04</v>
       </c>
-      <c r="I85" s="86">
+      <c r="I85" s="115">
         <v>231.04</v>
       </c>
-      <c r="J85" s="80">
+      <c r="J85" s="110">
         <v>238.03</v>
       </c>
-      <c r="K85" s="88">
+      <c r="K85" s="117">
         <v>237</v>
       </c>
-      <c r="L85" s="80">
+      <c r="L85" s="110">
         <v>244</v>
       </c>
-      <c r="M85" s="80">
+      <c r="M85" s="110">
         <v>243</v>
       </c>
-      <c r="N85" s="80">
+      <c r="N85" s="110">
         <v>247</v>
       </c>
-      <c r="O85" s="80">
+      <c r="O85" s="110">
         <v>247</v>
       </c>
-      <c r="P85" s="80">
+      <c r="P85" s="110">
         <v>251</v>
       </c>
-      <c r="Q85" s="80">
+      <c r="Q85" s="110">
         <v>252</v>
       </c>
-      <c r="R85" s="80">
+      <c r="R85" s="110">
         <v>257</v>
       </c>
-      <c r="S85" s="80">
+      <c r="S85" s="110">
         <v>258</v>
       </c>
-      <c r="T85" s="80">
+      <c r="T85" s="110">
         <v>259</v>
       </c>
-      <c r="U85" s="80">
+      <c r="U85" s="110">
         <v>266</v>
       </c>
     </row>
     <row r="86" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
-      <c r="D86" s="107"/>
-      <c r="E86" s="119"/>
-      <c r="F86" s="120"/>
-      <c r="G86" s="115"/>
-      <c r="H86" s="81"/>
-      <c r="I86" s="87"/>
-      <c r="J86" s="81"/>
-      <c r="K86" s="89"/>
-      <c r="L86" s="81"/>
-      <c r="M86" s="81"/>
-      <c r="N86" s="81"/>
-      <c r="O86" s="81"/>
-      <c r="P86" s="81"/>
-      <c r="Q86" s="81"/>
-      <c r="R86" s="81"/>
-      <c r="S86" s="81"/>
-      <c r="T86" s="81"/>
-      <c r="U86" s="81"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="53"/>
+      <c r="F86" s="54"/>
+      <c r="G86" s="49"/>
+      <c r="H86" s="111"/>
+      <c r="I86" s="116"/>
+      <c r="J86" s="111"/>
+      <c r="K86" s="118"/>
+      <c r="L86" s="111"/>
+      <c r="M86" s="111"/>
+      <c r="N86" s="111"/>
+      <c r="O86" s="111"/>
+      <c r="P86" s="111"/>
+      <c r="Q86" s="111"/>
+      <c r="R86" s="111"/>
+      <c r="S86" s="111"/>
+      <c r="T86" s="111"/>
+      <c r="U86" s="111"/>
     </row>
     <row r="87" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
@@ -5137,50 +5137,50 @@
       <c r="B89" s="3"/>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
-      <c r="H89" s="108" t="s">
+      <c r="H89" s="42" t="s">
         <v>240</v>
       </c>
-      <c r="I89" s="108"/>
+      <c r="I89" s="42"/>
       <c r="J89" s="16"/>
-      <c r="K89" s="110" t="s">
+      <c r="K89" s="44" t="s">
         <v>252</v>
       </c>
-      <c r="L89" s="110"/>
+      <c r="L89" s="44"/>
       <c r="M89" s="15"/>
-      <c r="N89" s="112" t="s">
+      <c r="N89" s="46" t="s">
         <v>244</v>
       </c>
-      <c r="O89" s="112"/>
+      <c r="O89" s="46"/>
       <c r="P89" s="15"/>
-      <c r="Q89" s="100" t="s">
+      <c r="Q89" s="56" t="s">
         <v>242</v>
       </c>
-      <c r="R89" s="100"/>
+      <c r="R89" s="56"/>
       <c r="S89" s="16"/>
-      <c r="T89" s="102" t="s">
+      <c r="T89" s="58" t="s">
         <v>246</v>
       </c>
-      <c r="U89" s="102"/>
+      <c r="U89" s="58"/>
     </row>
     <row r="90" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="E90" s="11"/>
       <c r="F90" s="11"/>
-      <c r="H90" s="108"/>
-      <c r="I90" s="108"/>
+      <c r="H90" s="42"/>
+      <c r="I90" s="42"/>
       <c r="J90" s="16"/>
-      <c r="K90" s="110"/>
-      <c r="L90" s="110"/>
+      <c r="K90" s="44"/>
+      <c r="L90" s="44"/>
       <c r="M90" s="15"/>
-      <c r="N90" s="112"/>
-      <c r="O90" s="112"/>
+      <c r="N90" s="46"/>
+      <c r="O90" s="46"/>
       <c r="P90" s="15"/>
-      <c r="Q90" s="100"/>
-      <c r="R90" s="100"/>
+      <c r="Q90" s="56"/>
+      <c r="R90" s="56"/>
       <c r="S90" s="16"/>
-      <c r="T90" s="102"/>
-      <c r="U90" s="102"/>
+      <c r="T90" s="58"/>
+      <c r="U90" s="58"/>
     </row>
     <row r="91" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
@@ -5227,48 +5227,48 @@
       <c r="B93" s="3"/>
       <c r="E93" s="11"/>
       <c r="F93" s="11"/>
-      <c r="H93" s="109" t="s">
+      <c r="H93" s="43" t="s">
         <v>239</v>
       </c>
-      <c r="I93" s="109"/>
+      <c r="I93" s="43"/>
       <c r="J93" s="16"/>
-      <c r="K93" s="111" t="s">
+      <c r="K93" s="45" t="s">
         <v>247</v>
       </c>
-      <c r="L93" s="111"/>
+      <c r="L93" s="45"/>
       <c r="M93" s="15"/>
-      <c r="N93" s="113" t="s">
+      <c r="N93" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="O93" s="113"/>
+      <c r="O93" s="47"/>
       <c r="P93" s="15"/>
-      <c r="Q93" s="101" t="s">
+      <c r="Q93" s="57" t="s">
         <v>241</v>
       </c>
-      <c r="R93" s="101"/>
+      <c r="R93" s="57"/>
       <c r="S93" s="16"/>
-      <c r="T93" s="103" t="s">
+      <c r="T93" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="U93" s="103"/>
+      <c r="U93" s="59"/>
     </row>
     <row r="94" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E94" s="11"/>
       <c r="F94" s="11"/>
-      <c r="H94" s="109"/>
-      <c r="I94" s="109"/>
+      <c r="H94" s="43"/>
+      <c r="I94" s="43"/>
       <c r="J94" s="16"/>
-      <c r="K94" s="111"/>
-      <c r="L94" s="111"/>
+      <c r="K94" s="45"/>
+      <c r="L94" s="45"/>
       <c r="M94" s="15"/>
-      <c r="N94" s="113"/>
-      <c r="O94" s="113"/>
+      <c r="N94" s="47"/>
+      <c r="O94" s="47"/>
       <c r="P94" s="15"/>
-      <c r="Q94" s="101"/>
-      <c r="R94" s="101"/>
+      <c r="Q94" s="57"/>
+      <c r="R94" s="57"/>
       <c r="S94" s="16"/>
-      <c r="T94" s="103"/>
-      <c r="U94" s="103"/>
+      <c r="T94" s="59"/>
+      <c r="U94" s="59"/>
     </row>
     <row r="95" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4"/>
@@ -5596,27 +5596,27 @@
       <c r="U112" s="10"/>
     </row>
     <row r="113" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="104"/>
-      <c r="B113" s="104"/>
-      <c r="C113" s="104"/>
-      <c r="D113" s="104"/>
-      <c r="E113" s="104"/>
-      <c r="F113" s="104"/>
-      <c r="G113" s="104"/>
-      <c r="H113" s="104"/>
-      <c r="I113" s="104"/>
-      <c r="J113" s="104"/>
-      <c r="K113" s="104"/>
-      <c r="L113" s="104"/>
-      <c r="M113" s="104"/>
-      <c r="N113" s="104"/>
-      <c r="O113" s="104"/>
-      <c r="P113" s="104"/>
-      <c r="Q113" s="104"/>
-      <c r="R113" s="104"/>
-      <c r="S113" s="104"/>
-      <c r="T113" s="104"/>
-      <c r="U113" s="104"/>
+      <c r="A113" s="60"/>
+      <c r="B113" s="60"/>
+      <c r="C113" s="60"/>
+      <c r="D113" s="60"/>
+      <c r="E113" s="60"/>
+      <c r="F113" s="60"/>
+      <c r="G113" s="60"/>
+      <c r="H113" s="60"/>
+      <c r="I113" s="60"/>
+      <c r="J113" s="60"/>
+      <c r="K113" s="60"/>
+      <c r="L113" s="60"/>
+      <c r="M113" s="60"/>
+      <c r="N113" s="60"/>
+      <c r="O113" s="60"/>
+      <c r="P113" s="60"/>
+      <c r="Q113" s="60"/>
+      <c r="R113" s="60"/>
+      <c r="S113" s="60"/>
+      <c r="T113" s="60"/>
+      <c r="U113" s="60"/>
     </row>
     <row r="114" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="115" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5626,24 +5626,492 @@
     <row r="119" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="528">
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="D80:D82"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="H89:I90"/>
-    <mergeCell ref="H93:I94"/>
-    <mergeCell ref="K89:L90"/>
-    <mergeCell ref="K93:L94"/>
-    <mergeCell ref="N89:O90"/>
-    <mergeCell ref="N93:O94"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="G80:G82"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="E80:E82"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F78:F86"/>
-    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="U78:U79"/>
+    <mergeCell ref="U76:U77"/>
+    <mergeCell ref="U71:U73"/>
+    <mergeCell ref="U69:U70"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="R74:R75"/>
+    <mergeCell ref="S74:S75"/>
+    <mergeCell ref="T74:T75"/>
+    <mergeCell ref="U74:U75"/>
+    <mergeCell ref="R78:R79"/>
+    <mergeCell ref="T76:T77"/>
+    <mergeCell ref="S76:S77"/>
+    <mergeCell ref="T78:T79"/>
+    <mergeCell ref="S78:S79"/>
+    <mergeCell ref="Q71:Q73"/>
+    <mergeCell ref="R71:R73"/>
+    <mergeCell ref="S71:S73"/>
+    <mergeCell ref="O42:O44"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="Q78:Q79"/>
+    <mergeCell ref="P78:P79"/>
+    <mergeCell ref="O78:O79"/>
+    <mergeCell ref="R76:R77"/>
+    <mergeCell ref="Q76:Q77"/>
+    <mergeCell ref="P76:P77"/>
+    <mergeCell ref="O76:O77"/>
+    <mergeCell ref="L78:L79"/>
+    <mergeCell ref="K78:K79"/>
+    <mergeCell ref="K76:K77"/>
+    <mergeCell ref="L76:L77"/>
+    <mergeCell ref="M76:M77"/>
+    <mergeCell ref="N76:N77"/>
+    <mergeCell ref="K69:K70"/>
+    <mergeCell ref="N69:N70"/>
+    <mergeCell ref="M69:M70"/>
+    <mergeCell ref="M78:M79"/>
+    <mergeCell ref="O65:O66"/>
+    <mergeCell ref="O74:O75"/>
+    <mergeCell ref="P65:P66"/>
+    <mergeCell ref="L60:L62"/>
+    <mergeCell ref="A58:A66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F69:F77"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="H76:H77"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="G60:G62"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="B4:B12"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="N54:N55"/>
+    <mergeCell ref="B13:B21"/>
+    <mergeCell ref="B22:B30"/>
+    <mergeCell ref="B31:B39"/>
+    <mergeCell ref="B40:B48"/>
+    <mergeCell ref="B49:B57"/>
+    <mergeCell ref="B58:B66"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="N31:N32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="H33:H35"/>
+    <mergeCell ref="J60:J62"/>
+    <mergeCell ref="K60:K62"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="D60:D62"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F4:O30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="O36:O37"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="N56:N57"/>
+    <mergeCell ref="O56:O57"/>
+    <mergeCell ref="N33:N35"/>
+    <mergeCell ref="O33:O35"/>
+    <mergeCell ref="N38:N39"/>
+    <mergeCell ref="O38:O39"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="J65:J66"/>
+    <mergeCell ref="K65:K66"/>
+    <mergeCell ref="L65:L66"/>
+    <mergeCell ref="H80:H82"/>
+    <mergeCell ref="I80:I82"/>
+    <mergeCell ref="J80:J82"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="L69:L70"/>
+    <mergeCell ref="N78:N79"/>
+    <mergeCell ref="J78:J79"/>
+    <mergeCell ref="I78:I79"/>
+    <mergeCell ref="H78:H79"/>
+    <mergeCell ref="I76:I77"/>
+    <mergeCell ref="J76:J77"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="I74:I75"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="K71:K73"/>
+    <mergeCell ref="L71:L73"/>
+    <mergeCell ref="M71:M73"/>
+    <mergeCell ref="M60:M62"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="N60:N62"/>
+    <mergeCell ref="O69:O70"/>
+    <mergeCell ref="P69:P70"/>
+    <mergeCell ref="N74:N75"/>
+    <mergeCell ref="M65:M66"/>
+    <mergeCell ref="N63:N64"/>
+    <mergeCell ref="M63:M64"/>
+    <mergeCell ref="L63:L64"/>
+    <mergeCell ref="O60:O62"/>
+    <mergeCell ref="N71:N73"/>
+    <mergeCell ref="O71:O73"/>
+    <mergeCell ref="P71:P73"/>
+    <mergeCell ref="M74:M75"/>
+    <mergeCell ref="K74:K75"/>
+    <mergeCell ref="L74:L75"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="O63:O64"/>
+    <mergeCell ref="N65:N66"/>
+    <mergeCell ref="G71:G73"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="K63:K64"/>
+    <mergeCell ref="J63:J64"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="U1:U2"/>
+    <mergeCell ref="T71:T73"/>
+    <mergeCell ref="S69:S70"/>
+    <mergeCell ref="T69:T70"/>
+    <mergeCell ref="Q69:Q70"/>
+    <mergeCell ref="R69:R70"/>
+    <mergeCell ref="Q24:Q26"/>
+    <mergeCell ref="R24:R26"/>
+    <mergeCell ref="S24:S26"/>
+    <mergeCell ref="T24:T26"/>
+    <mergeCell ref="U24:U26"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="U36:U37"/>
+    <mergeCell ref="T36:T37"/>
+    <mergeCell ref="T51:T53"/>
+    <mergeCell ref="U51:U53"/>
+    <mergeCell ref="T47:T48"/>
+    <mergeCell ref="U47:U48"/>
+    <mergeCell ref="T40:T41"/>
+    <mergeCell ref="U40:U41"/>
+    <mergeCell ref="S31:S32"/>
+    <mergeCell ref="T31:T32"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="S29:S30"/>
+    <mergeCell ref="T29:T30"/>
+    <mergeCell ref="U29:U30"/>
+    <mergeCell ref="P24:P26"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="U18:U19"/>
+    <mergeCell ref="T18:T19"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="R15:R17"/>
+    <mergeCell ref="S15:S17"/>
+    <mergeCell ref="T15:T17"/>
+    <mergeCell ref="U15:U17"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="T85:T86"/>
+    <mergeCell ref="U80:U82"/>
+    <mergeCell ref="U85:U86"/>
+    <mergeCell ref="M85:M86"/>
+    <mergeCell ref="N85:N86"/>
+    <mergeCell ref="O85:O86"/>
+    <mergeCell ref="P85:P86"/>
+    <mergeCell ref="Q85:Q86"/>
+    <mergeCell ref="R85:R86"/>
+    <mergeCell ref="R80:R82"/>
+    <mergeCell ref="S80:S82"/>
+    <mergeCell ref="T80:T82"/>
+    <mergeCell ref="O80:O82"/>
+    <mergeCell ref="P83:P84"/>
+    <mergeCell ref="O83:O84"/>
+    <mergeCell ref="U83:U84"/>
+    <mergeCell ref="T83:T84"/>
+    <mergeCell ref="S83:S84"/>
+    <mergeCell ref="R83:R84"/>
+    <mergeCell ref="Q83:Q84"/>
+    <mergeCell ref="Q80:Q82"/>
+    <mergeCell ref="M83:M84"/>
+    <mergeCell ref="N83:N84"/>
+    <mergeCell ref="S85:S86"/>
+    <mergeCell ref="K80:K82"/>
+    <mergeCell ref="L80:L82"/>
+    <mergeCell ref="M80:M82"/>
+    <mergeCell ref="N80:N82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="J83:J84"/>
+    <mergeCell ref="K83:K84"/>
+    <mergeCell ref="L83:L84"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="K85:K86"/>
+    <mergeCell ref="L85:L86"/>
+    <mergeCell ref="P80:P82"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="Q20:Q21"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="T20:T21"/>
+    <mergeCell ref="U20:U21"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="Q15:Q17"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="T33:T35"/>
+    <mergeCell ref="U33:U35"/>
+    <mergeCell ref="P31:P32"/>
+    <mergeCell ref="Q31:Q32"/>
+    <mergeCell ref="R31:R32"/>
+    <mergeCell ref="P27:P28"/>
+    <mergeCell ref="T65:T66"/>
+    <mergeCell ref="U65:U66"/>
+    <mergeCell ref="U63:U64"/>
+    <mergeCell ref="T63:T64"/>
+    <mergeCell ref="P38:P39"/>
+    <mergeCell ref="Q38:Q39"/>
+    <mergeCell ref="R38:R39"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:T39"/>
+    <mergeCell ref="U38:U39"/>
+    <mergeCell ref="S54:S55"/>
+    <mergeCell ref="R54:R55"/>
+    <mergeCell ref="Q54:Q55"/>
+    <mergeCell ref="U45:U46"/>
+    <mergeCell ref="T45:T46"/>
+    <mergeCell ref="S45:S46"/>
+    <mergeCell ref="T58:T59"/>
+    <mergeCell ref="U58:U59"/>
+    <mergeCell ref="P60:P62"/>
+    <mergeCell ref="P36:P37"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="T60:T62"/>
+    <mergeCell ref="U60:U62"/>
+    <mergeCell ref="T42:T44"/>
+    <mergeCell ref="U42:U44"/>
+    <mergeCell ref="R40:R41"/>
+    <mergeCell ref="S40:S41"/>
+    <mergeCell ref="T56:T57"/>
+    <mergeCell ref="U56:U57"/>
+    <mergeCell ref="T49:T50"/>
+    <mergeCell ref="U49:U50"/>
+    <mergeCell ref="U31:U32"/>
+    <mergeCell ref="Q27:Q28"/>
+    <mergeCell ref="R33:R35"/>
+    <mergeCell ref="S33:S35"/>
+    <mergeCell ref="S36:S37"/>
+    <mergeCell ref="R36:R37"/>
+    <mergeCell ref="Q36:Q37"/>
+    <mergeCell ref="N58:N59"/>
+    <mergeCell ref="O58:O59"/>
+    <mergeCell ref="P58:P59"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="R58:R59"/>
+    <mergeCell ref="S58:S59"/>
+    <mergeCell ref="P33:P35"/>
+    <mergeCell ref="Q33:Q35"/>
+    <mergeCell ref="P54:P55"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="O54:O55"/>
+    <mergeCell ref="P56:P57"/>
+    <mergeCell ref="Q56:Q57"/>
+    <mergeCell ref="R56:R57"/>
+    <mergeCell ref="S56:S57"/>
+    <mergeCell ref="R42:R44"/>
+    <mergeCell ref="S42:S44"/>
+    <mergeCell ref="P42:P44"/>
+    <mergeCell ref="Q42:Q44"/>
+    <mergeCell ref="N40:N41"/>
+    <mergeCell ref="O40:O41"/>
+    <mergeCell ref="P40:P41"/>
+    <mergeCell ref="Q40:Q41"/>
+    <mergeCell ref="Q65:Q66"/>
+    <mergeCell ref="R65:R66"/>
+    <mergeCell ref="S65:S66"/>
+    <mergeCell ref="R49:R50"/>
+    <mergeCell ref="S49:S50"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="Q47:Q48"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="Q60:Q62"/>
+    <mergeCell ref="R60:R62"/>
+    <mergeCell ref="S60:S62"/>
+    <mergeCell ref="P63:P64"/>
+    <mergeCell ref="S63:S64"/>
+    <mergeCell ref="R63:R64"/>
+    <mergeCell ref="Q63:Q64"/>
+    <mergeCell ref="R45:R46"/>
+    <mergeCell ref="Q45:Q46"/>
+    <mergeCell ref="N51:N53"/>
+    <mergeCell ref="O51:O53"/>
+    <mergeCell ref="P51:P53"/>
+    <mergeCell ref="Q51:Q53"/>
+    <mergeCell ref="R51:R53"/>
+    <mergeCell ref="S51:S53"/>
+    <mergeCell ref="U54:U55"/>
+    <mergeCell ref="T54:T55"/>
+    <mergeCell ref="S47:S48"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P49:P50"/>
+    <mergeCell ref="Q49:Q50"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="L56:L57"/>
+    <mergeCell ref="M56:M57"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="J51:J53"/>
+    <mergeCell ref="K51:K53"/>
+    <mergeCell ref="L51:L53"/>
+    <mergeCell ref="M51:M53"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="M54:M55"/>
+    <mergeCell ref="L54:L55"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I35"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="J33:J35"/>
+    <mergeCell ref="K33:K35"/>
+    <mergeCell ref="L33:L35"/>
+    <mergeCell ref="M33:M35"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="K40:K41"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="J42:J44"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="M45:M46"/>
+    <mergeCell ref="L45:L46"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H42:H44"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="L42:L44"/>
+    <mergeCell ref="M42:M44"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="L38:L39"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="E60:E62"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="I51:I53"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="I60:I62"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="H60:H62"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="F49:F57"/>
+    <mergeCell ref="F58:F66"/>
     <mergeCell ref="Q89:R90"/>
     <mergeCell ref="Q93:R94"/>
     <mergeCell ref="T89:U90"/>
@@ -5668,492 +6136,24 @@
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E40:E41"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="E60:E62"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="I51:I53"/>
-    <mergeCell ref="I56:I57"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="I60:I62"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="H51:H53"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="H60:H62"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="F49:F57"/>
-    <mergeCell ref="F58:F66"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H42:H44"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="L42:L44"/>
-    <mergeCell ref="M42:M44"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="L38:L39"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I42:I44"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="K40:K41"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="J42:J44"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="M45:M46"/>
-    <mergeCell ref="L45:L46"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I35"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="J33:J35"/>
-    <mergeCell ref="K33:K35"/>
-    <mergeCell ref="L33:L35"/>
-    <mergeCell ref="M33:M35"/>
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="L56:L57"/>
-    <mergeCell ref="M56:M57"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="K49:K50"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="J51:J53"/>
-    <mergeCell ref="K51:K53"/>
-    <mergeCell ref="L51:L53"/>
-    <mergeCell ref="M51:M53"/>
-    <mergeCell ref="J56:J57"/>
-    <mergeCell ref="K56:K57"/>
-    <mergeCell ref="M54:M55"/>
-    <mergeCell ref="L54:L55"/>
-    <mergeCell ref="N51:N53"/>
-    <mergeCell ref="O51:O53"/>
-    <mergeCell ref="P51:P53"/>
-    <mergeCell ref="Q51:Q53"/>
-    <mergeCell ref="R51:R53"/>
-    <mergeCell ref="S51:S53"/>
-    <mergeCell ref="U54:U55"/>
-    <mergeCell ref="T54:T55"/>
-    <mergeCell ref="S47:S48"/>
-    <mergeCell ref="N49:N50"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P49:P50"/>
-    <mergeCell ref="Q49:Q50"/>
-    <mergeCell ref="Q65:Q66"/>
-    <mergeCell ref="R65:R66"/>
-    <mergeCell ref="S65:S66"/>
-    <mergeCell ref="R49:R50"/>
-    <mergeCell ref="S49:S50"/>
-    <mergeCell ref="P47:P48"/>
-    <mergeCell ref="Q47:Q48"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="P45:P46"/>
-    <mergeCell ref="Q60:Q62"/>
-    <mergeCell ref="R60:R62"/>
-    <mergeCell ref="S60:S62"/>
-    <mergeCell ref="P63:P64"/>
-    <mergeCell ref="S63:S64"/>
-    <mergeCell ref="R63:R64"/>
-    <mergeCell ref="Q63:Q64"/>
-    <mergeCell ref="R45:R46"/>
-    <mergeCell ref="Q45:Q46"/>
-    <mergeCell ref="N58:N59"/>
-    <mergeCell ref="O58:O59"/>
-    <mergeCell ref="P58:P59"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="R58:R59"/>
-    <mergeCell ref="S58:S59"/>
-    <mergeCell ref="P33:P35"/>
-    <mergeCell ref="Q33:Q35"/>
-    <mergeCell ref="P54:P55"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="O54:O55"/>
-    <mergeCell ref="P56:P57"/>
-    <mergeCell ref="Q56:Q57"/>
-    <mergeCell ref="R56:R57"/>
-    <mergeCell ref="S56:S57"/>
-    <mergeCell ref="R42:R44"/>
-    <mergeCell ref="S42:S44"/>
-    <mergeCell ref="P42:P44"/>
-    <mergeCell ref="Q42:Q44"/>
-    <mergeCell ref="N40:N41"/>
-    <mergeCell ref="O40:O41"/>
-    <mergeCell ref="P40:P41"/>
-    <mergeCell ref="Q40:Q41"/>
-    <mergeCell ref="T58:T59"/>
-    <mergeCell ref="U58:U59"/>
-    <mergeCell ref="P60:P62"/>
-    <mergeCell ref="P36:P37"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="T60:T62"/>
-    <mergeCell ref="U60:U62"/>
-    <mergeCell ref="T42:T44"/>
-    <mergeCell ref="U42:U44"/>
-    <mergeCell ref="R40:R41"/>
-    <mergeCell ref="S40:S41"/>
-    <mergeCell ref="T56:T57"/>
-    <mergeCell ref="U56:U57"/>
-    <mergeCell ref="T49:T50"/>
-    <mergeCell ref="U49:U50"/>
-    <mergeCell ref="U31:U32"/>
-    <mergeCell ref="Q27:Q28"/>
-    <mergeCell ref="R33:R35"/>
-    <mergeCell ref="S33:S35"/>
-    <mergeCell ref="S36:S37"/>
-    <mergeCell ref="R36:R37"/>
-    <mergeCell ref="Q36:Q37"/>
-    <mergeCell ref="P22:P23"/>
-    <mergeCell ref="Q22:Q23"/>
-    <mergeCell ref="T33:T35"/>
-    <mergeCell ref="U33:U35"/>
-    <mergeCell ref="P31:P32"/>
-    <mergeCell ref="Q31:Q32"/>
-    <mergeCell ref="R31:R32"/>
-    <mergeCell ref="P27:P28"/>
-    <mergeCell ref="T65:T66"/>
-    <mergeCell ref="U65:U66"/>
-    <mergeCell ref="U63:U64"/>
-    <mergeCell ref="T63:T64"/>
-    <mergeCell ref="P38:P39"/>
-    <mergeCell ref="Q38:Q39"/>
-    <mergeCell ref="R38:R39"/>
-    <mergeCell ref="S38:S39"/>
-    <mergeCell ref="T38:T39"/>
-    <mergeCell ref="U38:U39"/>
-    <mergeCell ref="S54:S55"/>
-    <mergeCell ref="R54:R55"/>
-    <mergeCell ref="Q54:Q55"/>
-    <mergeCell ref="U45:U46"/>
-    <mergeCell ref="T45:T46"/>
-    <mergeCell ref="S45:S46"/>
-    <mergeCell ref="P20:P21"/>
-    <mergeCell ref="Q20:Q21"/>
-    <mergeCell ref="R20:R21"/>
-    <mergeCell ref="S20:S21"/>
-    <mergeCell ref="T20:T21"/>
-    <mergeCell ref="U20:U21"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="Q15:Q17"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="Q80:Q82"/>
-    <mergeCell ref="M83:M84"/>
-    <mergeCell ref="N83:N84"/>
-    <mergeCell ref="S85:S86"/>
-    <mergeCell ref="K80:K82"/>
-    <mergeCell ref="L80:L82"/>
-    <mergeCell ref="M80:M82"/>
-    <mergeCell ref="N80:N82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="J83:J84"/>
-    <mergeCell ref="K83:K84"/>
-    <mergeCell ref="L83:L84"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="K85:K86"/>
-    <mergeCell ref="L85:L86"/>
-    <mergeCell ref="P80:P82"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="T85:T86"/>
-    <mergeCell ref="U80:U82"/>
-    <mergeCell ref="U85:U86"/>
-    <mergeCell ref="M85:M86"/>
-    <mergeCell ref="N85:N86"/>
-    <mergeCell ref="O85:O86"/>
-    <mergeCell ref="P85:P86"/>
-    <mergeCell ref="Q85:Q86"/>
-    <mergeCell ref="R85:R86"/>
-    <mergeCell ref="R80:R82"/>
-    <mergeCell ref="S80:S82"/>
-    <mergeCell ref="T80:T82"/>
-    <mergeCell ref="O80:O82"/>
-    <mergeCell ref="P83:P84"/>
-    <mergeCell ref="O83:O84"/>
-    <mergeCell ref="U83:U84"/>
-    <mergeCell ref="T83:T84"/>
-    <mergeCell ref="S83:S84"/>
-    <mergeCell ref="R83:R84"/>
-    <mergeCell ref="Q83:Q84"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="P29:P30"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="S29:S30"/>
-    <mergeCell ref="T29:T30"/>
-    <mergeCell ref="U29:U30"/>
-    <mergeCell ref="P24:P26"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="U18:U19"/>
-    <mergeCell ref="T18:T19"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="R18:R19"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="U22:U23"/>
-    <mergeCell ref="R15:R17"/>
-    <mergeCell ref="S15:S17"/>
-    <mergeCell ref="T15:T17"/>
-    <mergeCell ref="U15:U17"/>
-    <mergeCell ref="T27:T28"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="U1:U2"/>
-    <mergeCell ref="T71:T73"/>
-    <mergeCell ref="S69:S70"/>
-    <mergeCell ref="T69:T70"/>
-    <mergeCell ref="Q69:Q70"/>
-    <mergeCell ref="R69:R70"/>
-    <mergeCell ref="Q24:Q26"/>
-    <mergeCell ref="R24:R26"/>
-    <mergeCell ref="S24:S26"/>
-    <mergeCell ref="T24:T26"/>
-    <mergeCell ref="U24:U26"/>
-    <mergeCell ref="R22:R23"/>
-    <mergeCell ref="S22:S23"/>
-    <mergeCell ref="T22:T23"/>
-    <mergeCell ref="U36:U37"/>
-    <mergeCell ref="T36:T37"/>
-    <mergeCell ref="T51:T53"/>
-    <mergeCell ref="U51:U53"/>
-    <mergeCell ref="T47:T48"/>
-    <mergeCell ref="U47:U48"/>
-    <mergeCell ref="T40:T41"/>
-    <mergeCell ref="U40:U41"/>
-    <mergeCell ref="S31:S32"/>
-    <mergeCell ref="T31:T32"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="J54:J55"/>
-    <mergeCell ref="K54:K55"/>
-    <mergeCell ref="K63:K64"/>
-    <mergeCell ref="J63:J64"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="G63:G64"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="M60:M62"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="N60:N62"/>
-    <mergeCell ref="O69:O70"/>
-    <mergeCell ref="P69:P70"/>
-    <mergeCell ref="N74:N75"/>
-    <mergeCell ref="M65:M66"/>
-    <mergeCell ref="N63:N64"/>
-    <mergeCell ref="M63:M64"/>
-    <mergeCell ref="L63:L64"/>
-    <mergeCell ref="O60:O62"/>
-    <mergeCell ref="N71:N73"/>
-    <mergeCell ref="O71:O73"/>
-    <mergeCell ref="P71:P73"/>
-    <mergeCell ref="M74:M75"/>
-    <mergeCell ref="K74:K75"/>
-    <mergeCell ref="L74:L75"/>
-    <mergeCell ref="P74:P75"/>
-    <mergeCell ref="O63:O64"/>
-    <mergeCell ref="N65:N66"/>
-    <mergeCell ref="G71:G73"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="J65:J66"/>
-    <mergeCell ref="K65:K66"/>
-    <mergeCell ref="L65:L66"/>
-    <mergeCell ref="H80:H82"/>
-    <mergeCell ref="I80:I82"/>
-    <mergeCell ref="J80:J82"/>
-    <mergeCell ref="H74:H75"/>
-    <mergeCell ref="L69:L70"/>
-    <mergeCell ref="N78:N79"/>
-    <mergeCell ref="J78:J79"/>
-    <mergeCell ref="I78:I79"/>
-    <mergeCell ref="H78:H79"/>
-    <mergeCell ref="I76:I77"/>
-    <mergeCell ref="J76:J77"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="J74:J75"/>
-    <mergeCell ref="I74:I75"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="K71:K73"/>
-    <mergeCell ref="L71:L73"/>
-    <mergeCell ref="M71:M73"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="D60:D62"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F4:O30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="F33:F35"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="O36:O37"/>
-    <mergeCell ref="N36:N37"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="N56:N57"/>
-    <mergeCell ref="O56:O57"/>
-    <mergeCell ref="N33:N35"/>
-    <mergeCell ref="O33:O35"/>
-    <mergeCell ref="N38:N39"/>
-    <mergeCell ref="O38:O39"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="E65:E66"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="N45:N46"/>
-    <mergeCell ref="N54:N55"/>
-    <mergeCell ref="B13:B21"/>
-    <mergeCell ref="B22:B30"/>
-    <mergeCell ref="B31:B39"/>
-    <mergeCell ref="B40:B48"/>
-    <mergeCell ref="B49:B57"/>
-    <mergeCell ref="B58:B66"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="N31:N32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="H33:H35"/>
-    <mergeCell ref="J60:J62"/>
-    <mergeCell ref="K60:K62"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="K36:K37"/>
-    <mergeCell ref="A58:A66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="F69:F77"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="H76:H77"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="G60:G62"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="B4:B12"/>
-    <mergeCell ref="O42:O44"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="L58:L59"/>
-    <mergeCell ref="Q78:Q79"/>
-    <mergeCell ref="P78:P79"/>
-    <mergeCell ref="O78:O79"/>
-    <mergeCell ref="R76:R77"/>
-    <mergeCell ref="Q76:Q77"/>
-    <mergeCell ref="P76:P77"/>
-    <mergeCell ref="O76:O77"/>
-    <mergeCell ref="L78:L79"/>
-    <mergeCell ref="K78:K79"/>
-    <mergeCell ref="K76:K77"/>
-    <mergeCell ref="L76:L77"/>
-    <mergeCell ref="M76:M77"/>
-    <mergeCell ref="N76:N77"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="N69:N70"/>
-    <mergeCell ref="M69:M70"/>
-    <mergeCell ref="M78:M79"/>
-    <mergeCell ref="O65:O66"/>
-    <mergeCell ref="O74:O75"/>
-    <mergeCell ref="P65:P66"/>
-    <mergeCell ref="L60:L62"/>
-    <mergeCell ref="U78:U79"/>
-    <mergeCell ref="U76:U77"/>
-    <mergeCell ref="U71:U73"/>
-    <mergeCell ref="U69:U70"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="R74:R75"/>
-    <mergeCell ref="S74:S75"/>
-    <mergeCell ref="T74:T75"/>
-    <mergeCell ref="U74:U75"/>
-    <mergeCell ref="R78:R79"/>
-    <mergeCell ref="T76:T77"/>
-    <mergeCell ref="S76:S77"/>
-    <mergeCell ref="T78:T79"/>
-    <mergeCell ref="S78:S79"/>
-    <mergeCell ref="Q71:Q73"/>
-    <mergeCell ref="R71:R73"/>
-    <mergeCell ref="S71:S73"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="H89:I90"/>
+    <mergeCell ref="H93:I94"/>
+    <mergeCell ref="K89:L90"/>
+    <mergeCell ref="K93:L94"/>
+    <mergeCell ref="N89:O90"/>
+    <mergeCell ref="N93:O94"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="G80:G82"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F78:F86"/>
+    <mergeCell ref="G78:G79"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="27" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -6176,22 +6176,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="I2" s="122" t="s">
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="I2" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="122"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
     </row>
     <row r="3" spans="2:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="20"/>
@@ -6211,17 +6211,17 @@
       <c r="B4" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="D4" s="29"/>
+      <c r="D4" s="32"/>
       <c r="E4" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="G4" s="30"/>
+      <c r="G4" s="33"/>
       <c r="I4" s="24" t="s">
         <v>253</v>
       </c>
@@ -6232,10 +6232,10 @@
       <c r="L4" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="M4" s="123" t="s">
+      <c r="M4" s="35" t="s">
         <v>256</v>
       </c>
-      <c r="N4" s="124"/>
+      <c r="N4" s="36"/>
     </row>
     <row r="5" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
@@ -6310,25 +6310,25 @@
       <c r="P6" s="18"/>
     </row>
     <row r="7" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="33" t="s">
         <v>277</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
       <c r="F7" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="G7" s="128">
+      <c r="G7" s="29">
         <f>SUM(G5:G6)</f>
         <v>44.009</v>
       </c>
-      <c r="I7" s="125" t="s">
+      <c r="I7" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="J7" s="125"/>
-      <c r="K7" s="125"/>
-      <c r="L7" s="125"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
       <c r="M7" s="26" t="s">
         <v>257</v>
       </c>
@@ -6355,22 +6355,22 @@
       <c r="G9" s="23"/>
     </row>
     <row r="10" spans="2:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="B10" s="121" t="s">
+      <c r="B10" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="I10" s="122" t="s">
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="I10" s="30" t="s">
         <v>273</v>
       </c>
-      <c r="J10" s="122"/>
-      <c r="K10" s="122"/>
-      <c r="L10" s="122"/>
-      <c r="M10" s="122"/>
-      <c r="N10" s="122"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
     </row>
     <row r="11" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="20"/>
@@ -6390,17 +6390,17 @@
       <c r="B12" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="D12" s="29"/>
+      <c r="D12" s="32"/>
       <c r="E12" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="G12" s="30"/>
+      <c r="G12" s="33"/>
       <c r="I12" s="24" t="s">
         <v>253</v>
       </c>
@@ -6411,10 +6411,10 @@
       <c r="L12" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="M12" s="123" t="s">
+      <c r="M12" s="35" t="s">
         <v>256</v>
       </c>
-      <c r="N12" s="124"/>
+      <c r="N12" s="36"/>
     </row>
     <row r="13" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
@@ -6495,44 +6495,44 @@
       <c r="N15" s="26"/>
     </row>
     <row r="16" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="33" t="s">
         <v>278</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
       <c r="F16" s="22" t="s">
         <v>257</v>
       </c>
       <c r="G16" s="19"/>
-      <c r="I16" s="125" t="s">
+      <c r="I16" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="J16" s="125"/>
-      <c r="K16" s="125"/>
-      <c r="L16" s="125"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
       <c r="M16" s="26" t="s">
         <v>257</v>
       </c>
       <c r="N16" s="28"/>
     </row>
     <row r="19" spans="2:14" ht="21" x14ac:dyDescent="0.35">
-      <c r="B19" s="122" t="s">
+      <c r="B19" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="C19" s="122"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
-      <c r="I19" s="122" t="s">
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="I19" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="J19" s="122"/>
-      <c r="K19" s="122"/>
-      <c r="L19" s="122"/>
-      <c r="M19" s="122"/>
-      <c r="N19" s="122"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
     </row>
     <row r="20" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B20" s="20"/>
@@ -6559,10 +6559,10 @@
       <c r="E21" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="F21" s="126" t="s">
+      <c r="F21" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="G21" s="127"/>
+      <c r="G21" s="38"/>
       <c r="I21" s="24" t="s">
         <v>253</v>
       </c>
@@ -6657,22 +6657,22 @@
       <c r="N24" s="26"/>
     </row>
     <row r="25" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="125" t="s">
+      <c r="B25" s="31" t="s">
         <v>280</v>
       </c>
-      <c r="C25" s="125"/>
-      <c r="D25" s="125"/>
-      <c r="E25" s="125"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
       <c r="F25" s="26" t="s">
         <v>257</v>
       </c>
       <c r="G25" s="28"/>
-      <c r="I25" s="125" t="s">
+      <c r="I25" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="J25" s="125"/>
-      <c r="K25" s="125"/>
-      <c r="L25" s="125"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
       <c r="M25" s="26" t="s">
         <v>257</v>
       </c>
@@ -6680,13 +6680,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="I2:N2"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="M4:N4"/>
     <mergeCell ref="I25:L25"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B10:G10"/>
@@ -6699,6 +6692,13 @@
     <mergeCell ref="I19:N19"/>
     <mergeCell ref="M12:N12"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="I2:N2"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Exercícios/tabela_periodica_color.xlsx
+++ b/Exercícios/tabela_periodica_color.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\4. Projetos TIC - Química\ptic_quimica\Exercícios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48629E5-9004-417F-B4F6-B26B91412AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989283EA-A1A4-4A77-A977-3C1B7E32938E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabela_periodica" sheetId="1" r:id="rId1"/>
@@ -1607,21 +1607,291 @@
     <xf numFmtId="0" fontId="26" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1633,276 +1903,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2213,80 +2213,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="65">
+      <c r="D1" s="43">
         <v>1</v>
       </c>
-      <c r="E1" s="65">
+      <c r="E1" s="43">
         <v>2</v>
       </c>
-      <c r="F1" s="65">
+      <c r="F1" s="43">
         <v>3</v>
       </c>
-      <c r="G1" s="65">
+      <c r="G1" s="43">
         <v>4</v>
       </c>
-      <c r="H1" s="65">
+      <c r="H1" s="43">
         <v>5</v>
       </c>
-      <c r="I1" s="65">
+      <c r="I1" s="43">
         <v>6</v>
       </c>
-      <c r="J1" s="65">
+      <c r="J1" s="43">
         <v>7</v>
       </c>
-      <c r="K1" s="65">
+      <c r="K1" s="43">
         <v>8</v>
       </c>
-      <c r="L1" s="65">
+      <c r="L1" s="43">
         <v>9</v>
       </c>
-      <c r="M1" s="65">
+      <c r="M1" s="43">
         <v>10</v>
       </c>
-      <c r="N1" s="65">
+      <c r="N1" s="43">
         <v>11</v>
       </c>
-      <c r="O1" s="65">
+      <c r="O1" s="43">
         <v>12</v>
       </c>
-      <c r="P1" s="65">
+      <c r="P1" s="43">
         <v>13</v>
       </c>
-      <c r="Q1" s="65">
+      <c r="Q1" s="43">
         <v>14</v>
       </c>
-      <c r="R1" s="65">
+      <c r="R1" s="43">
         <v>15</v>
       </c>
-      <c r="S1" s="65">
+      <c r="S1" s="43">
         <v>16</v>
       </c>
-      <c r="T1" s="65">
+      <c r="T1" s="43">
         <v>17</v>
       </c>
-      <c r="U1" s="65">
+      <c r="U1" s="43">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
     </row>
     <row r="3" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="6"/>
@@ -2309,2123 +2309,2123 @@
       <c r="U3" s="6"/>
     </row>
     <row r="4" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
-      <c r="B4" s="65">
+      <c r="A4" s="43"/>
+      <c r="B4" s="43">
         <v>1</v>
       </c>
       <c r="C4" s="7"/>
-      <c r="D4" s="67">
+      <c r="D4" s="64">
         <v>1</v>
       </c>
-      <c r="F4" s="126" t="s">
+      <c r="F4" s="57" t="s">
         <v>228</v>
       </c>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="126"/>
-      <c r="K4" s="126"/>
-      <c r="L4" s="126"/>
-      <c r="M4" s="126"/>
-      <c r="N4" s="126"/>
-      <c r="O4" s="126"/>
-      <c r="U4" s="107">
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="U4" s="72">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="65"/>
-      <c r="B5" s="65"/>
+      <c r="A5" s="43"/>
+      <c r="B5" s="43"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="68"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
-      <c r="L5" s="126"/>
-      <c r="M5" s="126"/>
-      <c r="N5" s="126"/>
-      <c r="O5" s="126"/>
-      <c r="U5" s="90"/>
+      <c r="D5" s="45"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="U5" s="67"/>
     </row>
     <row r="6" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
-      <c r="B6" s="65"/>
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="126"/>
-      <c r="G6" s="126"/>
-      <c r="H6" s="126"/>
-      <c r="I6" s="126"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="126"/>
-      <c r="L6" s="126"/>
-      <c r="M6" s="126"/>
-      <c r="N6" s="126"/>
-      <c r="O6" s="126"/>
-      <c r="U6" s="101" t="s">
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
+      <c r="U6" s="63" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="65"/>
-      <c r="B7" s="65"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="69"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="126"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="126"/>
-      <c r="K7" s="126"/>
-      <c r="L7" s="126"/>
-      <c r="M7" s="126"/>
-      <c r="N7" s="126"/>
-      <c r="O7" s="126"/>
-      <c r="U7" s="101"/>
+      <c r="D7" s="61"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="57"/>
+      <c r="U7" s="63"/>
     </row>
     <row r="8" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="65"/>
-      <c r="B8" s="65"/>
+      <c r="A8" s="43"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="69"/>
-      <c r="F8" s="126"/>
-      <c r="G8" s="126"/>
-      <c r="H8" s="126"/>
-      <c r="I8" s="126"/>
-      <c r="J8" s="126"/>
-      <c r="K8" s="126"/>
-      <c r="L8" s="126"/>
-      <c r="M8" s="126"/>
-      <c r="N8" s="126"/>
-      <c r="O8" s="126"/>
-      <c r="U8" s="101"/>
+      <c r="D8" s="61"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
+      <c r="N8" s="57"/>
+      <c r="O8" s="57"/>
+      <c r="U8" s="63"/>
     </row>
     <row r="9" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="65"/>
-      <c r="B9" s="65"/>
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="68" t="s">
+      <c r="D9" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
-      <c r="M9" s="126"/>
-      <c r="N9" s="126"/>
-      <c r="O9" s="126"/>
-      <c r="U9" s="90" t="s">
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="57"/>
+      <c r="U9" s="67" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="65"/>
-      <c r="B10" s="65"/>
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="68"/>
-      <c r="F10" s="126"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="126"/>
-      <c r="I10" s="126"/>
-      <c r="J10" s="126"/>
-      <c r="K10" s="126"/>
-      <c r="L10" s="126"/>
-      <c r="M10" s="126"/>
-      <c r="N10" s="126"/>
-      <c r="O10" s="126"/>
-      <c r="U10" s="90"/>
+      <c r="D10" s="45"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+      <c r="N10" s="57"/>
+      <c r="O10" s="57"/>
+      <c r="U10" s="67"/>
     </row>
     <row r="11" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="65"/>
-      <c r="B11" s="65"/>
+      <c r="A11" s="43"/>
+      <c r="B11" s="43"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="70">
+      <c r="D11" s="75">
         <v>1.008</v>
       </c>
-      <c r="F11" s="126"/>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="126"/>
-      <c r="K11" s="126"/>
-      <c r="L11" s="126"/>
-      <c r="M11" s="126"/>
-      <c r="N11" s="126"/>
-      <c r="O11" s="126"/>
-      <c r="U11" s="104">
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="57"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="57"/>
+      <c r="U11" s="70">
         <v>4.0026000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="65"/>
-      <c r="B12" s="65"/>
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="71"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="126"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="126"/>
-      <c r="K12" s="126"/>
-      <c r="L12" s="126"/>
-      <c r="M12" s="126"/>
-      <c r="N12" s="126"/>
-      <c r="O12" s="126"/>
-      <c r="U12" s="105"/>
+      <c r="D12" s="76"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="57"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="57"/>
+      <c r="U12" s="71"/>
     </row>
     <row r="13" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="65"/>
-      <c r="B13" s="65">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43">
         <v>2</v>
       </c>
       <c r="C13" s="7"/>
-      <c r="D13" s="72">
+      <c r="D13" s="46">
         <v>3</v>
       </c>
-      <c r="E13" s="76">
+      <c r="E13" s="54">
         <v>4</v>
       </c>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="126"/>
-      <c r="L13" s="126"/>
-      <c r="M13" s="126"/>
-      <c r="N13" s="126"/>
-      <c r="O13" s="126"/>
-      <c r="P13" s="98">
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="57"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="57"/>
+      <c r="P13" s="89">
         <v>5</v>
       </c>
-      <c r="Q13" s="67">
+      <c r="Q13" s="64">
         <v>6</v>
       </c>
-      <c r="R13" s="67">
+      <c r="R13" s="64">
         <v>7</v>
       </c>
-      <c r="S13" s="67">
+      <c r="S13" s="64">
         <v>8</v>
       </c>
-      <c r="T13" s="106">
+      <c r="T13" s="65">
         <v>9</v>
       </c>
-      <c r="U13" s="107">
+      <c r="U13" s="72">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="65"/>
-      <c r="B14" s="65"/>
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="126"/>
-      <c r="H14" s="126"/>
-      <c r="I14" s="126"/>
-      <c r="J14" s="126"/>
-      <c r="K14" s="126"/>
-      <c r="L14" s="126"/>
-      <c r="M14" s="126"/>
-      <c r="N14" s="126"/>
-      <c r="O14" s="126"/>
-      <c r="P14" s="99"/>
-      <c r="Q14" s="68"/>
-      <c r="R14" s="68"/>
-      <c r="S14" s="68"/>
-      <c r="T14" s="91"/>
-      <c r="U14" s="90"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="57"/>
+      <c r="P14" s="90"/>
+      <c r="Q14" s="45"/>
+      <c r="R14" s="45"/>
+      <c r="S14" s="45"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="67"/>
     </row>
     <row r="15" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="65"/>
-      <c r="B15" s="65"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="43"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="73" t="s">
+      <c r="D15" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="66" t="s">
+      <c r="E15" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="126"/>
-      <c r="J15" s="126"/>
-      <c r="K15" s="126"/>
-      <c r="L15" s="126"/>
-      <c r="M15" s="126"/>
-      <c r="N15" s="126"/>
-      <c r="O15" s="126"/>
-      <c r="P15" s="89" t="s">
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="57"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="Q15" s="69" t="s">
+      <c r="Q15" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="R15" s="69" t="s">
+      <c r="R15" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="S15" s="69" t="s">
+      <c r="S15" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="T15" s="100" t="s">
+      <c r="T15" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="U15" s="101" t="s">
+      <c r="U15" s="63" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="65"/>
-      <c r="B16" s="65"/>
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="126"/>
-      <c r="H16" s="126"/>
-      <c r="I16" s="126"/>
-      <c r="J16" s="126"/>
-      <c r="K16" s="126"/>
-      <c r="L16" s="126"/>
-      <c r="M16" s="126"/>
-      <c r="N16" s="126"/>
-      <c r="O16" s="126"/>
-      <c r="P16" s="89"/>
-      <c r="Q16" s="69"/>
-      <c r="R16" s="69"/>
-      <c r="S16" s="69"/>
-      <c r="T16" s="100"/>
-      <c r="U16" s="101"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="57"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="57"/>
+      <c r="P16" s="60"/>
+      <c r="Q16" s="61"/>
+      <c r="R16" s="61"/>
+      <c r="S16" s="61"/>
+      <c r="T16" s="62"/>
+      <c r="U16" s="63"/>
     </row>
     <row r="17" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="65"/>
-      <c r="B17" s="65"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="126"/>
-      <c r="G17" s="126"/>
-      <c r="H17" s="126"/>
-      <c r="I17" s="126"/>
-      <c r="J17" s="126"/>
-      <c r="K17" s="126"/>
-      <c r="L17" s="126"/>
-      <c r="M17" s="126"/>
-      <c r="N17" s="126"/>
-      <c r="O17" s="126"/>
-      <c r="P17" s="89"/>
-      <c r="Q17" s="69"/>
-      <c r="R17" s="69"/>
-      <c r="S17" s="69"/>
-      <c r="T17" s="100"/>
-      <c r="U17" s="101"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="60"/>
+      <c r="Q17" s="61"/>
+      <c r="R17" s="61"/>
+      <c r="S17" s="61"/>
+      <c r="T17" s="62"/>
+      <c r="U17" s="63"/>
     </row>
     <row r="18" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="65"/>
-      <c r="B18" s="65"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="62" t="s">
+      <c r="D18" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="E18" s="61" t="s">
+      <c r="E18" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="F18" s="126"/>
-      <c r="G18" s="126"/>
-      <c r="H18" s="126"/>
-      <c r="I18" s="126"/>
-      <c r="J18" s="126"/>
-      <c r="K18" s="126"/>
-      <c r="L18" s="126"/>
-      <c r="M18" s="126"/>
-      <c r="N18" s="126"/>
-      <c r="O18" s="126"/>
-      <c r="P18" s="99" t="s">
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="57"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="90" t="s">
         <v>166</v>
       </c>
-      <c r="Q18" s="68" t="s">
+      <c r="Q18" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="R18" s="68" t="s">
+      <c r="R18" s="45" t="s">
         <v>177</v>
       </c>
-      <c r="S18" s="68" t="s">
+      <c r="S18" s="45" t="s">
         <v>184</v>
       </c>
-      <c r="T18" s="91" t="s">
+      <c r="T18" s="66" t="s">
         <v>197</v>
       </c>
-      <c r="U18" s="90" t="s">
+      <c r="U18" s="67" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="65"/>
-      <c r="B19" s="65"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="126"/>
-      <c r="H19" s="126"/>
-      <c r="I19" s="126"/>
-      <c r="J19" s="126"/>
-      <c r="K19" s="126"/>
-      <c r="L19" s="126"/>
-      <c r="M19" s="126"/>
-      <c r="N19" s="126"/>
-      <c r="O19" s="126"/>
-      <c r="P19" s="99"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="68"/>
-      <c r="T19" s="91"/>
-      <c r="U19" s="90"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="90"/>
+      <c r="Q19" s="45"/>
+      <c r="R19" s="45"/>
+      <c r="S19" s="45"/>
+      <c r="T19" s="66"/>
+      <c r="U19" s="67"/>
     </row>
     <row r="20" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="65"/>
-      <c r="B20" s="65"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="74">
+      <c r="D20" s="55">
         <v>6.94</v>
       </c>
-      <c r="E20" s="63">
+      <c r="E20" s="51">
         <v>9.0122</v>
       </c>
-      <c r="F20" s="126"/>
-      <c r="G20" s="126"/>
-      <c r="H20" s="126"/>
-      <c r="I20" s="126"/>
-      <c r="J20" s="126"/>
-      <c r="K20" s="126"/>
-      <c r="L20" s="126"/>
-      <c r="M20" s="126"/>
-      <c r="N20" s="126"/>
-      <c r="O20" s="126"/>
-      <c r="P20" s="92">
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="57"/>
+      <c r="P20" s="73">
         <v>10.81</v>
       </c>
-      <c r="Q20" s="70">
+      <c r="Q20" s="75">
         <v>12.010999999999999</v>
       </c>
-      <c r="R20" s="70">
+      <c r="R20" s="75">
         <v>14.007</v>
       </c>
-      <c r="S20" s="70">
+      <c r="S20" s="75">
         <v>15.999000000000001</v>
       </c>
-      <c r="T20" s="102">
+      <c r="T20" s="68">
         <v>18.998000000000001</v>
       </c>
-      <c r="U20" s="104">
+      <c r="U20" s="70">
         <v>20.18</v>
       </c>
     </row>
     <row r="21" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="65"/>
-      <c r="B21" s="65"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="75"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="126"/>
-      <c r="H21" s="126"/>
-      <c r="I21" s="126"/>
-      <c r="J21" s="126"/>
-      <c r="K21" s="126"/>
-      <c r="L21" s="126"/>
-      <c r="M21" s="126"/>
-      <c r="N21" s="126"/>
-      <c r="O21" s="126"/>
-      <c r="P21" s="93"/>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="71"/>
-      <c r="S21" s="71"/>
-      <c r="T21" s="103"/>
-      <c r="U21" s="105"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="74"/>
+      <c r="Q21" s="76"/>
+      <c r="R21" s="76"/>
+      <c r="S21" s="76"/>
+      <c r="T21" s="69"/>
+      <c r="U21" s="71"/>
     </row>
     <row r="22" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="65"/>
-      <c r="B22" s="65">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43">
         <v>3</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="72">
+      <c r="D22" s="46">
         <v>11</v>
       </c>
-      <c r="E22" s="76">
+      <c r="E22" s="54">
         <v>12</v>
       </c>
-      <c r="F22" s="126"/>
-      <c r="G22" s="126"/>
-      <c r="H22" s="126"/>
-      <c r="I22" s="126"/>
-      <c r="J22" s="126"/>
-      <c r="K22" s="126"/>
-      <c r="L22" s="126"/>
-      <c r="M22" s="126"/>
-      <c r="N22" s="126"/>
-      <c r="O22" s="126"/>
-      <c r="P22" s="94">
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="57"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="57"/>
+      <c r="P22" s="91">
         <v>13</v>
       </c>
-      <c r="Q22" s="98">
+      <c r="Q22" s="89">
         <v>14</v>
       </c>
-      <c r="R22" s="67">
+      <c r="R22" s="64">
         <v>15</v>
       </c>
-      <c r="S22" s="67">
+      <c r="S22" s="64">
         <v>16</v>
       </c>
-      <c r="T22" s="106">
+      <c r="T22" s="65">
         <v>17</v>
       </c>
-      <c r="U22" s="107">
+      <c r="U22" s="72">
         <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="65"/>
-      <c r="B23" s="65"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="126"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="126"/>
-      <c r="K23" s="126"/>
-      <c r="L23" s="126"/>
-      <c r="M23" s="126"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="126"/>
-      <c r="P23" s="95"/>
-      <c r="Q23" s="99"/>
-      <c r="R23" s="68"/>
-      <c r="S23" s="68"/>
-      <c r="T23" s="91"/>
-      <c r="U23" s="90"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="57"/>
+      <c r="P23" s="92"/>
+      <c r="Q23" s="90"/>
+      <c r="R23" s="45"/>
+      <c r="S23" s="45"/>
+      <c r="T23" s="66"/>
+      <c r="U23" s="67"/>
     </row>
     <row r="24" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="65"/>
-      <c r="B24" s="65"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="73" t="s">
+      <c r="D24" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="E24" s="66" t="s">
+      <c r="E24" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="126"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="126"/>
-      <c r="I24" s="126"/>
-      <c r="J24" s="126"/>
-      <c r="K24" s="126"/>
-      <c r="L24" s="126"/>
-      <c r="M24" s="126"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="126"/>
-      <c r="P24" s="88" t="s">
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="57"/>
+      <c r="P24" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="Q24" s="89" t="s">
+      <c r="Q24" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="R24" s="69" t="s">
+      <c r="R24" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="S24" s="69" t="s">
+      <c r="S24" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="T24" s="100" t="s">
+      <c r="T24" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="U24" s="101" t="s">
+      <c r="U24" s="63" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="65"/>
-      <c r="B25" s="65"/>
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="126"/>
-      <c r="G25" s="126"/>
-      <c r="H25" s="126"/>
-      <c r="I25" s="126"/>
-      <c r="J25" s="126"/>
-      <c r="K25" s="126"/>
-      <c r="L25" s="126"/>
-      <c r="M25" s="126"/>
-      <c r="N25" s="126"/>
-      <c r="O25" s="126"/>
-      <c r="P25" s="88"/>
-      <c r="Q25" s="89"/>
-      <c r="R25" s="69"/>
-      <c r="S25" s="69"/>
-      <c r="T25" s="100"/>
-      <c r="U25" s="101"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="57"/>
+      <c r="P25" s="77"/>
+      <c r="Q25" s="60"/>
+      <c r="R25" s="61"/>
+      <c r="S25" s="61"/>
+      <c r="T25" s="62"/>
+      <c r="U25" s="63"/>
     </row>
     <row r="26" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="65"/>
-      <c r="B26" s="65"/>
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="126"/>
-      <c r="G26" s="126"/>
-      <c r="H26" s="126"/>
-      <c r="I26" s="126"/>
-      <c r="J26" s="126"/>
-      <c r="K26" s="126"/>
-      <c r="L26" s="126"/>
-      <c r="M26" s="126"/>
-      <c r="N26" s="126"/>
-      <c r="O26" s="126"/>
-      <c r="P26" s="88"/>
-      <c r="Q26" s="89"/>
-      <c r="R26" s="69"/>
-      <c r="S26" s="69"/>
-      <c r="T26" s="100"/>
-      <c r="U26" s="101"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="57"/>
+      <c r="P26" s="77"/>
+      <c r="Q26" s="60"/>
+      <c r="R26" s="61"/>
+      <c r="S26" s="61"/>
+      <c r="T26" s="62"/>
+      <c r="U26" s="63"/>
     </row>
     <row r="27" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="65"/>
-      <c r="B27" s="65"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="62" t="s">
+      <c r="D27" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="E27" s="61" t="s">
+      <c r="E27" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="F27" s="126"/>
-      <c r="G27" s="126"/>
-      <c r="H27" s="126"/>
-      <c r="I27" s="126"/>
-      <c r="J27" s="126"/>
-      <c r="K27" s="126"/>
-      <c r="L27" s="126"/>
-      <c r="M27" s="126"/>
-      <c r="N27" s="126"/>
-      <c r="O27" s="126"/>
-      <c r="P27" s="95" t="s">
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="57"/>
+      <c r="P27" s="92" t="s">
         <v>168</v>
       </c>
-      <c r="Q27" s="99" t="s">
+      <c r="Q27" s="90" t="s">
         <v>176</v>
       </c>
-      <c r="R27" s="68" t="s">
+      <c r="R27" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="S27" s="68" t="s">
+      <c r="S27" s="45" t="s">
         <v>185</v>
       </c>
-      <c r="T27" s="91" t="s">
+      <c r="T27" s="66" t="s">
         <v>198</v>
       </c>
-      <c r="U27" s="90" t="s">
+      <c r="U27" s="67" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="65"/>
-      <c r="B28" s="65"/>
+      <c r="A28" s="43"/>
+      <c r="B28" s="43"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="61"/>
-      <c r="F28" s="126"/>
-      <c r="G28" s="126"/>
-      <c r="H28" s="126"/>
-      <c r="I28" s="126"/>
-      <c r="J28" s="126"/>
-      <c r="K28" s="126"/>
-      <c r="L28" s="126"/>
-      <c r="M28" s="126"/>
-      <c r="N28" s="126"/>
-      <c r="O28" s="126"/>
-      <c r="P28" s="95"/>
-      <c r="Q28" s="99"/>
-      <c r="R28" s="68"/>
-      <c r="S28" s="68"/>
-      <c r="T28" s="91"/>
-      <c r="U28" s="90"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="57"/>
+      <c r="P28" s="92"/>
+      <c r="Q28" s="90"/>
+      <c r="R28" s="45"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="66"/>
+      <c r="U28" s="67"/>
     </row>
     <row r="29" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="65"/>
-      <c r="B29" s="65"/>
+      <c r="A29" s="43"/>
+      <c r="B29" s="43"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="74">
+      <c r="D29" s="55">
         <v>22.99</v>
       </c>
-      <c r="E29" s="63">
+      <c r="E29" s="51">
         <v>24.305</v>
       </c>
-      <c r="F29" s="126"/>
-      <c r="G29" s="126"/>
-      <c r="H29" s="126"/>
-      <c r="I29" s="126"/>
-      <c r="J29" s="126"/>
-      <c r="K29" s="126"/>
-      <c r="L29" s="126"/>
-      <c r="M29" s="126"/>
-      <c r="N29" s="126"/>
-      <c r="O29" s="126"/>
-      <c r="P29" s="96">
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="41">
         <v>26.981999999999999</v>
       </c>
-      <c r="Q29" s="92">
+      <c r="Q29" s="73">
         <v>28.085000000000001</v>
       </c>
-      <c r="R29" s="70">
+      <c r="R29" s="75">
         <v>30.974</v>
       </c>
-      <c r="S29" s="70">
+      <c r="S29" s="75">
         <v>32.06</v>
       </c>
-      <c r="T29" s="102">
+      <c r="T29" s="68">
         <v>35.450000000000003</v>
       </c>
-      <c r="U29" s="104">
+      <c r="U29" s="70">
         <v>39.950000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="65"/>
-      <c r="B30" s="65"/>
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="75"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="126"/>
-      <c r="G30" s="126"/>
-      <c r="H30" s="126"/>
-      <c r="I30" s="126"/>
-      <c r="J30" s="126"/>
-      <c r="K30" s="126"/>
-      <c r="L30" s="126"/>
-      <c r="M30" s="126"/>
-      <c r="N30" s="126"/>
-      <c r="O30" s="126"/>
-      <c r="P30" s="97"/>
-      <c r="Q30" s="93"/>
-      <c r="R30" s="71"/>
-      <c r="S30" s="71"/>
-      <c r="T30" s="103"/>
-      <c r="U30" s="105"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="74"/>
+      <c r="R30" s="76"/>
+      <c r="S30" s="76"/>
+      <c r="T30" s="69"/>
+      <c r="U30" s="71"/>
     </row>
     <row r="31" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="65"/>
-      <c r="B31" s="65">
+      <c r="A31" s="43"/>
+      <c r="B31" s="43">
         <v>4</v>
       </c>
       <c r="C31" s="7"/>
-      <c r="D31" s="72">
+      <c r="D31" s="46">
         <v>19</v>
       </c>
-      <c r="E31" s="76">
+      <c r="E31" s="54">
         <v>20</v>
       </c>
-      <c r="F31" s="77">
+      <c r="F31" s="36">
         <v>21</v>
       </c>
-      <c r="G31" s="77">
+      <c r="G31" s="36">
         <v>22</v>
       </c>
-      <c r="H31" s="77">
+      <c r="H31" s="36">
         <v>23</v>
       </c>
-      <c r="I31" s="77">
+      <c r="I31" s="36">
         <v>24</v>
       </c>
-      <c r="J31" s="77">
+      <c r="J31" s="36">
         <v>25</v>
       </c>
-      <c r="K31" s="77">
+      <c r="K31" s="36">
         <v>26</v>
       </c>
-      <c r="L31" s="77">
+      <c r="L31" s="36">
         <v>27</v>
       </c>
-      <c r="M31" s="77">
+      <c r="M31" s="36">
         <v>28</v>
       </c>
-      <c r="N31" s="77">
+      <c r="N31" s="36">
         <v>29</v>
       </c>
-      <c r="O31" s="77">
+      <c r="O31" s="36">
         <v>30</v>
       </c>
-      <c r="P31" s="94">
+      <c r="P31" s="91">
         <v>31</v>
       </c>
-      <c r="Q31" s="98">
+      <c r="Q31" s="89">
         <v>32</v>
       </c>
-      <c r="R31" s="98">
+      <c r="R31" s="89">
         <v>33</v>
       </c>
-      <c r="S31" s="67">
+      <c r="S31" s="64">
         <v>34</v>
       </c>
-      <c r="T31" s="106">
+      <c r="T31" s="65">
         <v>35</v>
       </c>
-      <c r="U31" s="107">
+      <c r="U31" s="72">
         <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="65"/>
-      <c r="B32" s="65"/>
+      <c r="A32" s="43"/>
+      <c r="B32" s="43"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="76"/>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="78"/>
-      <c r="K32" s="78"/>
-      <c r="L32" s="78"/>
-      <c r="M32" s="78"/>
-      <c r="N32" s="77"/>
-      <c r="O32" s="77"/>
-      <c r="P32" s="95"/>
-      <c r="Q32" s="99"/>
-      <c r="R32" s="99"/>
-      <c r="S32" s="68"/>
-      <c r="T32" s="91"/>
-      <c r="U32" s="90"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="37"/>
+      <c r="M32" s="37"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="36"/>
+      <c r="P32" s="92"/>
+      <c r="Q32" s="90"/>
+      <c r="R32" s="90"/>
+      <c r="S32" s="45"/>
+      <c r="T32" s="66"/>
+      <c r="U32" s="67"/>
     </row>
     <row r="33" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="65"/>
-      <c r="B33" s="65"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="43"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="73" t="s">
+      <c r="D33" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E33" s="66" t="s">
+      <c r="E33" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="79" t="s">
+      <c r="F33" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="79" t="s">
+      <c r="G33" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="H33" s="79" t="s">
+      <c r="H33" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="I33" s="79" t="s">
+      <c r="I33" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="J33" s="79" t="s">
+      <c r="J33" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="K33" s="79" t="s">
+      <c r="K33" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="L33" s="79" t="s">
+      <c r="L33" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="M33" s="79" t="s">
+      <c r="M33" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="N33" s="79" t="s">
+      <c r="N33" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="O33" s="79" t="s">
+      <c r="O33" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="P33" s="88" t="s">
+      <c r="P33" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="Q33" s="89" t="s">
+      <c r="Q33" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="R33" s="89" t="s">
+      <c r="R33" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="S33" s="69" t="s">
+      <c r="S33" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="T33" s="100" t="s">
+      <c r="T33" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="U33" s="101" t="s">
+      <c r="U33" s="63" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="65"/>
-      <c r="B34" s="65"/>
+      <c r="A34" s="43"/>
+      <c r="B34" s="43"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="66"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
-      <c r="I34" s="79"/>
-      <c r="J34" s="79"/>
-      <c r="K34" s="79"/>
-      <c r="L34" s="79"/>
-      <c r="M34" s="79"/>
-      <c r="N34" s="79"/>
-      <c r="O34" s="79"/>
-      <c r="P34" s="88"/>
-      <c r="Q34" s="89"/>
-      <c r="R34" s="89"/>
-      <c r="S34" s="69"/>
-      <c r="T34" s="100"/>
-      <c r="U34" s="101"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="77"/>
+      <c r="Q34" s="60"/>
+      <c r="R34" s="60"/>
+      <c r="S34" s="61"/>
+      <c r="T34" s="62"/>
+      <c r="U34" s="63"/>
     </row>
     <row r="35" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="65"/>
-      <c r="B35" s="65"/>
+      <c r="A35" s="43"/>
+      <c r="B35" s="43"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
-      <c r="I35" s="79"/>
-      <c r="J35" s="79"/>
-      <c r="K35" s="79"/>
-      <c r="L35" s="79"/>
-      <c r="M35" s="79"/>
-      <c r="N35" s="79"/>
-      <c r="O35" s="79"/>
-      <c r="P35" s="88"/>
-      <c r="Q35" s="89"/>
-      <c r="R35" s="89"/>
-      <c r="S35" s="69"/>
-      <c r="T35" s="100"/>
-      <c r="U35" s="101"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="77"/>
+      <c r="Q35" s="60"/>
+      <c r="R35" s="60"/>
+      <c r="S35" s="61"/>
+      <c r="T35" s="62"/>
+      <c r="U35" s="63"/>
     </row>
     <row r="36" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="65"/>
-      <c r="B36" s="65"/>
+      <c r="A36" s="43"/>
+      <c r="B36" s="43"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="62" t="s">
+      <c r="D36" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E36" s="61" t="s">
+      <c r="E36" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="F36" s="78" t="s">
+      <c r="F36" s="37" t="s">
         <v>238</v>
       </c>
-      <c r="G36" s="78" t="s">
+      <c r="G36" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H36" s="78" t="s">
+      <c r="H36" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="I36" s="78" t="s">
+      <c r="I36" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="J36" s="78" t="s">
+      <c r="J36" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="K36" s="78" t="s">
+      <c r="K36" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="L36" s="78" t="s">
+      <c r="L36" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="M36" s="78" t="s">
+      <c r="M36" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="N36" s="78" t="s">
+      <c r="N36" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="O36" s="78" t="s">
+      <c r="O36" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="P36" s="95" t="s">
+      <c r="P36" s="92" t="s">
         <v>169</v>
       </c>
-      <c r="Q36" s="99" t="s">
+      <c r="Q36" s="90" t="s">
         <v>175</v>
       </c>
-      <c r="R36" s="99" t="s">
+      <c r="R36" s="90" t="s">
         <v>180</v>
       </c>
-      <c r="S36" s="68" t="s">
+      <c r="S36" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="T36" s="91" t="s">
+      <c r="T36" s="66" t="s">
         <v>199</v>
       </c>
-      <c r="U36" s="90" t="s">
+      <c r="U36" s="67" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="37" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="65"/>
-      <c r="B37" s="65"/>
+      <c r="A37" s="43"/>
+      <c r="B37" s="43"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="62"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="78"/>
-      <c r="M37" s="78"/>
-      <c r="N37" s="78"/>
-      <c r="O37" s="78"/>
-      <c r="P37" s="95"/>
-      <c r="Q37" s="99"/>
-      <c r="R37" s="99"/>
-      <c r="S37" s="68"/>
-      <c r="T37" s="91"/>
-      <c r="U37" s="90"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="37"/>
+      <c r="M37" s="37"/>
+      <c r="N37" s="37"/>
+      <c r="O37" s="37"/>
+      <c r="P37" s="92"/>
+      <c r="Q37" s="90"/>
+      <c r="R37" s="90"/>
+      <c r="S37" s="45"/>
+      <c r="T37" s="66"/>
+      <c r="U37" s="67"/>
     </row>
     <row r="38" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="65"/>
-      <c r="B38" s="65"/>
+      <c r="A38" s="43"/>
+      <c r="B38" s="43"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="74">
+      <c r="D38" s="55">
         <v>39.097999999999999</v>
       </c>
-      <c r="E38" s="63">
+      <c r="E38" s="51">
         <v>40.078000000000003</v>
       </c>
-      <c r="F38" s="80">
+      <c r="F38" s="39">
         <v>44.956000000000003</v>
       </c>
-      <c r="G38" s="80">
+      <c r="G38" s="39">
         <v>47.866999999999997</v>
       </c>
-      <c r="H38" s="80">
+      <c r="H38" s="39">
         <v>50.942</v>
       </c>
-      <c r="I38" s="80">
+      <c r="I38" s="39">
         <v>51.996000000000002</v>
       </c>
-      <c r="J38" s="80">
+      <c r="J38" s="39">
         <v>54.938000000000002</v>
       </c>
-      <c r="K38" s="80">
+      <c r="K38" s="39">
         <v>55.844999999999999</v>
       </c>
-      <c r="L38" s="80">
+      <c r="L38" s="39">
         <v>58.933</v>
       </c>
-      <c r="M38" s="80">
+      <c r="M38" s="39">
         <v>58.692999999999998</v>
       </c>
-      <c r="N38" s="80">
+      <c r="N38" s="39">
         <v>63.545999999999999</v>
       </c>
-      <c r="O38" s="80">
+      <c r="O38" s="39">
         <v>65.38</v>
       </c>
-      <c r="P38" s="96">
+      <c r="P38" s="41">
         <v>69.722999999999999</v>
       </c>
-      <c r="Q38" s="92">
+      <c r="Q38" s="73">
         <v>72.63</v>
       </c>
-      <c r="R38" s="92">
+      <c r="R38" s="73">
         <v>74.921999999999997</v>
       </c>
-      <c r="S38" s="70">
+      <c r="S38" s="75">
         <v>78.971000000000004</v>
       </c>
-      <c r="T38" s="102">
+      <c r="T38" s="68">
         <v>79.903999999999996</v>
       </c>
-      <c r="U38" s="104">
+      <c r="U38" s="70">
         <v>83.798000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="65"/>
-      <c r="B39" s="65"/>
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="75"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="80"/>
-      <c r="G39" s="81"/>
-      <c r="H39" s="80"/>
-      <c r="I39" s="81"/>
-      <c r="J39" s="81"/>
-      <c r="K39" s="81"/>
-      <c r="L39" s="81"/>
-      <c r="M39" s="81"/>
-      <c r="N39" s="81"/>
-      <c r="O39" s="81"/>
-      <c r="P39" s="97"/>
-      <c r="Q39" s="93"/>
-      <c r="R39" s="93"/>
-      <c r="S39" s="71"/>
-      <c r="T39" s="103"/>
-      <c r="U39" s="105"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="40"/>
+      <c r="N39" s="40"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="74"/>
+      <c r="R39" s="74"/>
+      <c r="S39" s="76"/>
+      <c r="T39" s="69"/>
+      <c r="U39" s="71"/>
     </row>
     <row r="40" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="65"/>
-      <c r="B40" s="65">
+      <c r="A40" s="43"/>
+      <c r="B40" s="43">
         <v>5</v>
       </c>
       <c r="C40" s="7"/>
-      <c r="D40" s="72">
+      <c r="D40" s="46">
         <v>37</v>
       </c>
-      <c r="E40" s="76">
+      <c r="E40" s="54">
         <v>38</v>
       </c>
-      <c r="F40" s="77">
+      <c r="F40" s="36">
         <v>39</v>
       </c>
-      <c r="G40" s="77">
+      <c r="G40" s="36">
         <v>40</v>
       </c>
-      <c r="H40" s="77">
+      <c r="H40" s="36">
         <v>41</v>
       </c>
-      <c r="I40" s="77">
+      <c r="I40" s="36">
         <v>42</v>
       </c>
-      <c r="J40" s="77">
+      <c r="J40" s="36">
         <v>43</v>
       </c>
-      <c r="K40" s="77">
+      <c r="K40" s="36">
         <v>44</v>
       </c>
-      <c r="L40" s="77">
+      <c r="L40" s="36">
         <v>45</v>
       </c>
-      <c r="M40" s="77">
+      <c r="M40" s="36">
         <v>46</v>
       </c>
-      <c r="N40" s="77">
+      <c r="N40" s="36">
         <v>47</v>
       </c>
-      <c r="O40" s="77">
+      <c r="O40" s="36">
         <v>48</v>
       </c>
-      <c r="P40" s="94">
+      <c r="P40" s="91">
         <v>49</v>
       </c>
-      <c r="Q40" s="94">
+      <c r="Q40" s="91">
         <v>50</v>
       </c>
-      <c r="R40" s="98">
+      <c r="R40" s="89">
         <v>51</v>
       </c>
-      <c r="S40" s="98">
+      <c r="S40" s="89">
         <v>52</v>
       </c>
-      <c r="T40" s="106">
+      <c r="T40" s="65">
         <v>53</v>
       </c>
-      <c r="U40" s="107">
+      <c r="U40" s="72">
         <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="65"/>
-      <c r="B41" s="65"/>
+      <c r="A41" s="43"/>
+      <c r="B41" s="43"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="62"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="78"/>
-      <c r="G41" s="78"/>
-      <c r="H41" s="78"/>
-      <c r="I41" s="78"/>
-      <c r="J41" s="78"/>
-      <c r="K41" s="78"/>
-      <c r="L41" s="78"/>
-      <c r="M41" s="78"/>
-      <c r="N41" s="78"/>
-      <c r="O41" s="78"/>
-      <c r="P41" s="95"/>
-      <c r="Q41" s="95"/>
-      <c r="R41" s="99"/>
-      <c r="S41" s="99"/>
-      <c r="T41" s="91"/>
-      <c r="U41" s="90"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
+      <c r="J41" s="37"/>
+      <c r="K41" s="37"/>
+      <c r="L41" s="37"/>
+      <c r="M41" s="37"/>
+      <c r="N41" s="37"/>
+      <c r="O41" s="37"/>
+      <c r="P41" s="92"/>
+      <c r="Q41" s="92"/>
+      <c r="R41" s="90"/>
+      <c r="S41" s="90"/>
+      <c r="T41" s="66"/>
+      <c r="U41" s="67"/>
     </row>
     <row r="42" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="73" t="s">
+      <c r="D42" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="66" t="s">
+      <c r="E42" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="F42" s="79" t="s">
+      <c r="F42" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="G42" s="79" t="s">
+      <c r="G42" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="H42" s="79" t="s">
+      <c r="H42" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="I42" s="79" t="s">
+      <c r="I42" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="J42" s="79" t="s">
+      <c r="J42" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="K42" s="79" t="s">
+      <c r="K42" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="L42" s="79" t="s">
+      <c r="L42" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="M42" s="79" t="s">
+      <c r="M42" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N42" s="79" t="s">
+      <c r="N42" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="O42" s="79" t="s">
+      <c r="O42" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="P42" s="88" t="s">
+      <c r="P42" s="77" t="s">
         <v>73</v>
       </c>
-      <c r="Q42" s="88" t="s">
+      <c r="Q42" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="R42" s="89" t="s">
+      <c r="R42" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="S42" s="89" t="s">
+      <c r="S42" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="T42" s="100" t="s">
+      <c r="T42" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="U42" s="101" t="s">
+      <c r="U42" s="63" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="65"/>
-      <c r="B43" s="65"/>
+      <c r="A43" s="43"/>
+      <c r="B43" s="43"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="73"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="79"/>
-      <c r="G43" s="79"/>
-      <c r="H43" s="79"/>
-      <c r="I43" s="79"/>
-      <c r="J43" s="79"/>
-      <c r="K43" s="79"/>
-      <c r="L43" s="79"/>
-      <c r="M43" s="79"/>
-      <c r="N43" s="79"/>
-      <c r="O43" s="79"/>
-      <c r="P43" s="88"/>
-      <c r="Q43" s="88"/>
-      <c r="R43" s="89"/>
-      <c r="S43" s="89"/>
-      <c r="T43" s="100"/>
-      <c r="U43" s="101"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="35"/>
+      <c r="L43" s="35"/>
+      <c r="M43" s="35"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="35"/>
+      <c r="P43" s="77"/>
+      <c r="Q43" s="77"/>
+      <c r="R43" s="60"/>
+      <c r="S43" s="60"/>
+      <c r="T43" s="62"/>
+      <c r="U43" s="63"/>
     </row>
     <row r="44" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="65"/>
-      <c r="B44" s="65"/>
+      <c r="A44" s="43"/>
+      <c r="B44" s="43"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="73"/>
-      <c r="E44" s="66"/>
-      <c r="F44" s="79"/>
-      <c r="G44" s="79"/>
-      <c r="H44" s="79"/>
-      <c r="I44" s="79"/>
-      <c r="J44" s="79"/>
-      <c r="K44" s="79"/>
-      <c r="L44" s="79"/>
-      <c r="M44" s="79"/>
-      <c r="N44" s="79"/>
-      <c r="O44" s="79"/>
-      <c r="P44" s="88"/>
-      <c r="Q44" s="88"/>
-      <c r="R44" s="89"/>
-      <c r="S44" s="89"/>
-      <c r="T44" s="100"/>
-      <c r="U44" s="101"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="35"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="35"/>
+      <c r="L44" s="35"/>
+      <c r="M44" s="35"/>
+      <c r="N44" s="35"/>
+      <c r="O44" s="35"/>
+      <c r="P44" s="77"/>
+      <c r="Q44" s="77"/>
+      <c r="R44" s="60"/>
+      <c r="S44" s="60"/>
+      <c r="T44" s="62"/>
+      <c r="U44" s="63"/>
     </row>
     <row r="45" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="65"/>
-      <c r="B45" s="65"/>
+      <c r="A45" s="43"/>
+      <c r="B45" s="43"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="62" t="s">
+      <c r="D45" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="E45" s="61" t="s">
+      <c r="E45" s="50" t="s">
         <v>230</v>
       </c>
-      <c r="F45" s="78" t="s">
+      <c r="F45" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="G45" s="78" t="s">
+      <c r="G45" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="H45" s="78" t="s">
+      <c r="H45" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="I45" s="78" t="s">
+      <c r="I45" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="J45" s="78" t="s">
+      <c r="J45" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="K45" s="78" t="s">
+      <c r="K45" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="L45" s="78" t="s">
+      <c r="L45" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="M45" s="78" t="s">
+      <c r="M45" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="N45" s="78" t="s">
+      <c r="N45" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="O45" s="78" t="s">
+      <c r="O45" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="P45" s="95" t="s">
+      <c r="P45" s="92" t="s">
         <v>170</v>
       </c>
-      <c r="Q45" s="95" t="s">
+      <c r="Q45" s="92" t="s">
         <v>174</v>
       </c>
-      <c r="R45" s="99" t="s">
+      <c r="R45" s="90" t="s">
         <v>181</v>
       </c>
-      <c r="S45" s="99" t="s">
+      <c r="S45" s="90" t="s">
         <v>187</v>
       </c>
-      <c r="T45" s="91" t="s">
+      <c r="T45" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="U45" s="90" t="s">
+      <c r="U45" s="67" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="65"/>
-      <c r="B46" s="65"/>
+      <c r="A46" s="43"/>
+      <c r="B46" s="43"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="78"/>
-      <c r="G46" s="78"/>
-      <c r="H46" s="78"/>
-      <c r="I46" s="78"/>
-      <c r="J46" s="78"/>
-      <c r="K46" s="78"/>
-      <c r="L46" s="78"/>
-      <c r="M46" s="78"/>
-      <c r="N46" s="78"/>
-      <c r="O46" s="78"/>
-      <c r="P46" s="95"/>
-      <c r="Q46" s="95"/>
-      <c r="R46" s="99"/>
-      <c r="S46" s="99"/>
-      <c r="T46" s="91"/>
-      <c r="U46" s="90"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="37"/>
+      <c r="I46" s="37"/>
+      <c r="J46" s="37"/>
+      <c r="K46" s="37"/>
+      <c r="L46" s="37"/>
+      <c r="M46" s="37"/>
+      <c r="N46" s="37"/>
+      <c r="O46" s="37"/>
+      <c r="P46" s="92"/>
+      <c r="Q46" s="92"/>
+      <c r="R46" s="90"/>
+      <c r="S46" s="90"/>
+      <c r="T46" s="66"/>
+      <c r="U46" s="67"/>
     </row>
     <row r="47" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="65"/>
-      <c r="B47" s="65"/>
+      <c r="A47" s="43"/>
+      <c r="B47" s="43"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="74">
+      <c r="D47" s="55">
         <v>85.468000000000004</v>
       </c>
-      <c r="E47" s="63">
+      <c r="E47" s="51">
         <v>87.62</v>
       </c>
-      <c r="F47" s="80">
+      <c r="F47" s="39">
         <v>88.906000000000006</v>
       </c>
-      <c r="G47" s="80">
+      <c r="G47" s="39">
         <v>91.224000000000004</v>
       </c>
-      <c r="H47" s="80">
+      <c r="H47" s="39">
         <v>92.906000000000006</v>
       </c>
-      <c r="I47" s="80">
+      <c r="I47" s="39">
         <v>95.95</v>
       </c>
-      <c r="J47" s="80">
+      <c r="J47" s="39">
         <v>97</v>
       </c>
-      <c r="K47" s="80">
+      <c r="K47" s="39">
         <v>101.07</v>
       </c>
-      <c r="L47" s="80">
+      <c r="L47" s="39">
         <v>102.91</v>
       </c>
-      <c r="M47" s="80">
+      <c r="M47" s="39">
         <v>106.42</v>
       </c>
-      <c r="N47" s="80">
+      <c r="N47" s="39">
         <v>107.87</v>
       </c>
-      <c r="O47" s="80">
+      <c r="O47" s="39">
         <v>112.41</v>
       </c>
-      <c r="P47" s="96">
+      <c r="P47" s="41">
         <v>114.82</v>
       </c>
-      <c r="Q47" s="96">
+      <c r="Q47" s="41">
         <v>118.71</v>
       </c>
-      <c r="R47" s="92">
+      <c r="R47" s="73">
         <v>121.76</v>
       </c>
-      <c r="S47" s="92">
+      <c r="S47" s="73">
         <v>127.6</v>
       </c>
-      <c r="T47" s="102">
+      <c r="T47" s="68">
         <v>126.9</v>
       </c>
-      <c r="U47" s="104">
+      <c r="U47" s="70">
         <v>131.29</v>
       </c>
     </row>
     <row r="48" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="65"/>
-      <c r="B48" s="65"/>
+      <c r="A48" s="43"/>
+      <c r="B48" s="43"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="75"/>
-      <c r="E48" s="64"/>
-      <c r="F48" s="81"/>
-      <c r="G48" s="81"/>
-      <c r="H48" s="81"/>
-      <c r="I48" s="81"/>
-      <c r="J48" s="81"/>
-      <c r="K48" s="81"/>
-      <c r="L48" s="81"/>
-      <c r="M48" s="81"/>
-      <c r="N48" s="81"/>
-      <c r="O48" s="81"/>
-      <c r="P48" s="97"/>
-      <c r="Q48" s="97"/>
-      <c r="R48" s="93"/>
-      <c r="S48" s="93"/>
-      <c r="T48" s="103"/>
-      <c r="U48" s="105"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="40"/>
+      <c r="J48" s="40"/>
+      <c r="K48" s="40"/>
+      <c r="L48" s="40"/>
+      <c r="M48" s="40"/>
+      <c r="N48" s="40"/>
+      <c r="O48" s="40"/>
+      <c r="P48" s="42"/>
+      <c r="Q48" s="42"/>
+      <c r="R48" s="74"/>
+      <c r="S48" s="74"/>
+      <c r="T48" s="69"/>
+      <c r="U48" s="71"/>
     </row>
     <row r="49" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="65"/>
-      <c r="B49" s="65">
+      <c r="A49" s="43"/>
+      <c r="B49" s="43">
         <v>6</v>
       </c>
       <c r="C49" s="7"/>
-      <c r="D49" s="72">
+      <c r="D49" s="46">
         <v>55</v>
       </c>
-      <c r="E49" s="76">
+      <c r="E49" s="54">
         <v>56</v>
       </c>
-      <c r="F49" s="82" t="s">
+      <c r="F49" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="G49" s="77">
+      <c r="G49" s="36">
         <v>72</v>
       </c>
-      <c r="H49" s="77">
+      <c r="H49" s="36">
         <v>73</v>
       </c>
-      <c r="I49" s="77">
+      <c r="I49" s="36">
         <v>74</v>
       </c>
-      <c r="J49" s="77">
+      <c r="J49" s="36">
         <v>75</v>
       </c>
-      <c r="K49" s="77">
+      <c r="K49" s="36">
         <v>76</v>
       </c>
-      <c r="L49" s="77">
+      <c r="L49" s="36">
         <v>77</v>
       </c>
-      <c r="M49" s="77">
+      <c r="M49" s="36">
         <v>78</v>
       </c>
-      <c r="N49" s="77">
+      <c r="N49" s="36">
         <v>79</v>
       </c>
-      <c r="O49" s="77">
+      <c r="O49" s="36">
         <v>80</v>
       </c>
-      <c r="P49" s="94">
+      <c r="P49" s="91">
         <v>81</v>
       </c>
-      <c r="Q49" s="94">
+      <c r="Q49" s="91">
         <v>82</v>
       </c>
-      <c r="R49" s="94">
+      <c r="R49" s="91">
         <v>83</v>
       </c>
-      <c r="S49" s="98">
+      <c r="S49" s="89">
         <v>84</v>
       </c>
-      <c r="T49" s="106">
+      <c r="T49" s="65">
         <v>85</v>
       </c>
-      <c r="U49" s="107">
+      <c r="U49" s="72">
         <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="65"/>
-      <c r="B50" s="65"/>
+      <c r="A50" s="43"/>
+      <c r="B50" s="43"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="62"/>
-      <c r="E50" s="61"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="78"/>
-      <c r="H50" s="78"/>
-      <c r="I50" s="78"/>
-      <c r="J50" s="78"/>
-      <c r="K50" s="78"/>
-      <c r="L50" s="78"/>
-      <c r="M50" s="78"/>
-      <c r="N50" s="78"/>
-      <c r="O50" s="78"/>
-      <c r="P50" s="95"/>
-      <c r="Q50" s="95"/>
-      <c r="R50" s="95"/>
-      <c r="S50" s="99"/>
-      <c r="T50" s="91"/>
-      <c r="U50" s="90"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="94"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="37"/>
+      <c r="I50" s="37"/>
+      <c r="J50" s="37"/>
+      <c r="K50" s="37"/>
+      <c r="L50" s="37"/>
+      <c r="M50" s="37"/>
+      <c r="N50" s="37"/>
+      <c r="O50" s="37"/>
+      <c r="P50" s="92"/>
+      <c r="Q50" s="92"/>
+      <c r="R50" s="92"/>
+      <c r="S50" s="90"/>
+      <c r="T50" s="66"/>
+      <c r="U50" s="67"/>
     </row>
     <row r="51" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="65"/>
-      <c r="B51" s="65"/>
+      <c r="A51" s="43"/>
+      <c r="B51" s="43"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="73" t="s">
+      <c r="D51" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="E51" s="66" t="s">
+      <c r="E51" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="83"/>
-      <c r="G51" s="79" t="s">
+      <c r="F51" s="94"/>
+      <c r="G51" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="H51" s="79" t="s">
+      <c r="H51" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="I51" s="79" t="s">
+      <c r="I51" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="J51" s="79" t="s">
+      <c r="J51" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="K51" s="79" t="s">
+      <c r="K51" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="L51" s="79" t="s">
+      <c r="L51" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="M51" s="79" t="s">
+      <c r="M51" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="N51" s="79" t="s">
+      <c r="N51" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="O51" s="79" t="s">
+      <c r="O51" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="P51" s="88" t="s">
+      <c r="P51" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="Q51" s="88" t="s">
+      <c r="Q51" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="R51" s="88" t="s">
+      <c r="R51" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="S51" s="89" t="s">
+      <c r="S51" s="60" t="s">
         <v>82</v>
       </c>
-      <c r="T51" s="100" t="s">
+      <c r="T51" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="U51" s="101" t="s">
+      <c r="U51" s="63" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="65"/>
-      <c r="B52" s="65"/>
+      <c r="A52" s="43"/>
+      <c r="B52" s="43"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="73"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="79"/>
-      <c r="H52" s="79"/>
-      <c r="I52" s="79"/>
-      <c r="J52" s="79"/>
-      <c r="K52" s="79"/>
-      <c r="L52" s="79"/>
-      <c r="M52" s="79"/>
-      <c r="N52" s="79"/>
-      <c r="O52" s="79"/>
-      <c r="P52" s="88"/>
-      <c r="Q52" s="88"/>
-      <c r="R52" s="88"/>
-      <c r="S52" s="89"/>
-      <c r="T52" s="100"/>
-      <c r="U52" s="101"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="94"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
+      <c r="M52" s="35"/>
+      <c r="N52" s="35"/>
+      <c r="O52" s="35"/>
+      <c r="P52" s="77"/>
+      <c r="Q52" s="77"/>
+      <c r="R52" s="77"/>
+      <c r="S52" s="60"/>
+      <c r="T52" s="62"/>
+      <c r="U52" s="63"/>
     </row>
     <row r="53" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="65"/>
-      <c r="B53" s="65"/>
+      <c r="A53" s="43"/>
+      <c r="B53" s="43"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="73"/>
-      <c r="E53" s="66"/>
-      <c r="F53" s="83"/>
-      <c r="G53" s="79"/>
-      <c r="H53" s="79"/>
-      <c r="I53" s="79"/>
-      <c r="J53" s="79"/>
-      <c r="K53" s="79"/>
-      <c r="L53" s="79"/>
-      <c r="M53" s="79"/>
-      <c r="N53" s="79"/>
-      <c r="O53" s="79"/>
-      <c r="P53" s="88"/>
-      <c r="Q53" s="88"/>
-      <c r="R53" s="88"/>
-      <c r="S53" s="89"/>
-      <c r="T53" s="100"/>
-      <c r="U53" s="101"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="94"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="77"/>
+      <c r="Q53" s="77"/>
+      <c r="R53" s="77"/>
+      <c r="S53" s="60"/>
+      <c r="T53" s="62"/>
+      <c r="U53" s="63"/>
     </row>
     <row r="54" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="65"/>
-      <c r="B54" s="65"/>
+      <c r="A54" s="43"/>
+      <c r="B54" s="43"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="62" t="s">
+      <c r="D54" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="E54" s="61" t="s">
+      <c r="E54" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="F54" s="83"/>
-      <c r="G54" s="78" t="s">
+      <c r="F54" s="94"/>
+      <c r="G54" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="H54" s="78" t="s">
+      <c r="H54" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="I54" s="78" t="s">
+      <c r="I54" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="J54" s="78" t="s">
+      <c r="J54" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="K54" s="78" t="s">
+      <c r="K54" s="37" t="s">
         <v>231</v>
       </c>
-      <c r="L54" s="78" t="s">
+      <c r="L54" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="M54" s="78" t="s">
+      <c r="M54" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="N54" s="78" t="s">
+      <c r="N54" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="O54" s="78" t="s">
+      <c r="O54" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="P54" s="95" t="s">
+      <c r="P54" s="92" t="s">
         <v>171</v>
       </c>
-      <c r="Q54" s="95" t="s">
+      <c r="Q54" s="92" t="s">
         <v>173</v>
       </c>
-      <c r="R54" s="95" t="s">
+      <c r="R54" s="92" t="s">
         <v>182</v>
       </c>
-      <c r="S54" s="99" t="s">
+      <c r="S54" s="90" t="s">
         <v>188</v>
       </c>
-      <c r="T54" s="91" t="s">
+      <c r="T54" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="U54" s="90" t="s">
+      <c r="U54" s="67" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="65"/>
-      <c r="B55" s="65"/>
+      <c r="A55" s="43"/>
+      <c r="B55" s="43"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="62"/>
-      <c r="E55" s="61"/>
-      <c r="F55" s="83"/>
-      <c r="G55" s="78"/>
-      <c r="H55" s="78"/>
-      <c r="I55" s="78"/>
-      <c r="J55" s="78"/>
-      <c r="K55" s="78"/>
-      <c r="L55" s="78"/>
-      <c r="M55" s="78"/>
-      <c r="N55" s="78"/>
-      <c r="O55" s="78"/>
-      <c r="P55" s="95"/>
-      <c r="Q55" s="95"/>
-      <c r="R55" s="95"/>
-      <c r="S55" s="99"/>
-      <c r="T55" s="91"/>
-      <c r="U55" s="90"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="50"/>
+      <c r="F55" s="94"/>
+      <c r="G55" s="37"/>
+      <c r="H55" s="37"/>
+      <c r="I55" s="37"/>
+      <c r="J55" s="37"/>
+      <c r="K55" s="37"/>
+      <c r="L55" s="37"/>
+      <c r="M55" s="37"/>
+      <c r="N55" s="37"/>
+      <c r="O55" s="37"/>
+      <c r="P55" s="92"/>
+      <c r="Q55" s="92"/>
+      <c r="R55" s="92"/>
+      <c r="S55" s="90"/>
+      <c r="T55" s="66"/>
+      <c r="U55" s="67"/>
     </row>
     <row r="56" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="65"/>
-      <c r="B56" s="65"/>
+      <c r="A56" s="43"/>
+      <c r="B56" s="43"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="74">
+      <c r="D56" s="55">
         <v>132.91</v>
       </c>
-      <c r="E56" s="63">
+      <c r="E56" s="51">
         <v>137.33000000000001</v>
       </c>
-      <c r="F56" s="83"/>
-      <c r="G56" s="80">
+      <c r="F56" s="94"/>
+      <c r="G56" s="39">
         <v>178.49</v>
       </c>
-      <c r="H56" s="80">
+      <c r="H56" s="39">
         <v>180.95</v>
       </c>
-      <c r="I56" s="80">
+      <c r="I56" s="39">
         <v>183.84</v>
       </c>
-      <c r="J56" s="80">
+      <c r="J56" s="39">
         <v>186.21</v>
       </c>
-      <c r="K56" s="80">
+      <c r="K56" s="39">
         <v>190.23</v>
       </c>
-      <c r="L56" s="80">
+      <c r="L56" s="39">
         <v>192.22</v>
       </c>
-      <c r="M56" s="80">
+      <c r="M56" s="39">
         <v>195.08</v>
       </c>
-      <c r="N56" s="80">
+      <c r="N56" s="39">
         <v>196.97</v>
       </c>
-      <c r="O56" s="80">
+      <c r="O56" s="39">
         <v>200.59</v>
       </c>
-      <c r="P56" s="96">
+      <c r="P56" s="41">
         <v>204.38</v>
       </c>
-      <c r="Q56" s="96">
+      <c r="Q56" s="41">
         <v>207.2</v>
       </c>
-      <c r="R56" s="96">
+      <c r="R56" s="41">
         <v>208.98</v>
       </c>
-      <c r="S56" s="92">
+      <c r="S56" s="73">
         <v>209</v>
       </c>
-      <c r="T56" s="102">
+      <c r="T56" s="68">
         <v>210</v>
       </c>
-      <c r="U56" s="104">
+      <c r="U56" s="70">
         <v>222</v>
       </c>
     </row>
     <row r="57" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="65"/>
-      <c r="B57" s="65"/>
+      <c r="A57" s="43"/>
+      <c r="B57" s="43"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="74"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="84"/>
-      <c r="G57" s="81"/>
-      <c r="H57" s="81"/>
-      <c r="I57" s="81"/>
-      <c r="J57" s="81"/>
-      <c r="K57" s="81"/>
-      <c r="L57" s="81"/>
-      <c r="M57" s="81"/>
-      <c r="N57" s="81"/>
-      <c r="O57" s="81"/>
-      <c r="P57" s="97"/>
-      <c r="Q57" s="97"/>
-      <c r="R57" s="97"/>
-      <c r="S57" s="93"/>
-      <c r="T57" s="103"/>
-      <c r="U57" s="105"/>
+      <c r="D57" s="55"/>
+      <c r="E57" s="52"/>
+      <c r="F57" s="95"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="40"/>
+      <c r="I57" s="40"/>
+      <c r="J57" s="40"/>
+      <c r="K57" s="40"/>
+      <c r="L57" s="40"/>
+      <c r="M57" s="40"/>
+      <c r="N57" s="40"/>
+      <c r="O57" s="40"/>
+      <c r="P57" s="42"/>
+      <c r="Q57" s="42"/>
+      <c r="R57" s="42"/>
+      <c r="S57" s="74"/>
+      <c r="T57" s="69"/>
+      <c r="U57" s="71"/>
     </row>
     <row r="58" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="65"/>
-      <c r="B58" s="65">
+      <c r="A58" s="43"/>
+      <c r="B58" s="43">
         <v>7</v>
       </c>
       <c r="C58" s="7"/>
-      <c r="D58" s="72">
+      <c r="D58" s="46">
         <v>102</v>
       </c>
-      <c r="E58" s="76">
+      <c r="E58" s="54">
         <v>102</v>
       </c>
-      <c r="F58" s="85" t="s">
+      <c r="F58" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="G58" s="77">
+      <c r="G58" s="36">
         <v>104</v>
       </c>
-      <c r="H58" s="77">
+      <c r="H58" s="36">
         <v>105</v>
       </c>
-      <c r="I58" s="77">
+      <c r="I58" s="36">
         <v>106</v>
       </c>
-      <c r="J58" s="77">
+      <c r="J58" s="36">
         <v>107</v>
       </c>
-      <c r="K58" s="77">
+      <c r="K58" s="36">
         <v>108</v>
       </c>
-      <c r="L58" s="77">
+      <c r="L58" s="36">
         <v>109</v>
       </c>
-      <c r="M58" s="77">
+      <c r="M58" s="36">
         <v>110</v>
       </c>
-      <c r="N58" s="77">
+      <c r="N58" s="36">
         <v>111</v>
       </c>
-      <c r="O58" s="77">
+      <c r="O58" s="36">
         <v>112</v>
       </c>
-      <c r="P58" s="94">
+      <c r="P58" s="91">
         <v>113</v>
       </c>
-      <c r="Q58" s="94">
+      <c r="Q58" s="91">
         <v>114</v>
       </c>
-      <c r="R58" s="94">
+      <c r="R58" s="91">
         <v>115</v>
       </c>
-      <c r="S58" s="94">
+      <c r="S58" s="91">
         <v>116</v>
       </c>
-      <c r="T58" s="94">
+      <c r="T58" s="91">
         <v>117</v>
       </c>
-      <c r="U58" s="94">
+      <c r="U58" s="91">
         <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="65"/>
-      <c r="B59" s="65"/>
+      <c r="A59" s="43"/>
+      <c r="B59" s="43"/>
       <c r="C59" s="7"/>
-      <c r="D59" s="62"/>
-      <c r="E59" s="61"/>
-      <c r="F59" s="86"/>
-      <c r="G59" s="78"/>
-      <c r="H59" s="78"/>
-      <c r="I59" s="78"/>
-      <c r="J59" s="78"/>
-      <c r="K59" s="78"/>
-      <c r="L59" s="78"/>
-      <c r="M59" s="78"/>
-      <c r="N59" s="78"/>
-      <c r="O59" s="78"/>
-      <c r="P59" s="95"/>
-      <c r="Q59" s="95"/>
-      <c r="R59" s="95"/>
-      <c r="S59" s="95"/>
-      <c r="T59" s="95"/>
-      <c r="U59" s="95"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="50"/>
+      <c r="F59" s="97"/>
+      <c r="G59" s="37"/>
+      <c r="H59" s="37"/>
+      <c r="I59" s="37"/>
+      <c r="J59" s="37"/>
+      <c r="K59" s="37"/>
+      <c r="L59" s="37"/>
+      <c r="M59" s="37"/>
+      <c r="N59" s="37"/>
+      <c r="O59" s="37"/>
+      <c r="P59" s="92"/>
+      <c r="Q59" s="92"/>
+      <c r="R59" s="92"/>
+      <c r="S59" s="92"/>
+      <c r="T59" s="92"/>
+      <c r="U59" s="92"/>
     </row>
     <row r="60" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="65"/>
-      <c r="B60" s="65"/>
+      <c r="A60" s="43"/>
+      <c r="B60" s="43"/>
       <c r="C60" s="7"/>
-      <c r="D60" s="73" t="s">
+      <c r="D60" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="66" t="s">
+      <c r="E60" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="F60" s="86"/>
-      <c r="G60" s="79" t="s">
+      <c r="F60" s="97"/>
+      <c r="G60" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="H60" s="79" t="s">
+      <c r="H60" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I60" s="79" t="s">
+      <c r="I60" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="J60" s="79" t="s">
+      <c r="J60" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="K60" s="79" t="s">
+      <c r="K60" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="L60" s="79" t="s">
+      <c r="L60" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="M60" s="79" t="s">
+      <c r="M60" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="N60" s="79" t="s">
+      <c r="N60" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="O60" s="79" t="s">
+      <c r="O60" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="P60" s="88" t="s">
+      <c r="P60" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="Q60" s="88" t="s">
+      <c r="Q60" s="77" t="s">
         <v>86</v>
       </c>
-      <c r="R60" s="88" t="s">
+      <c r="R60" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="S60" s="88" t="s">
+      <c r="S60" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="T60" s="88" t="s">
+      <c r="T60" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="U60" s="88" t="s">
+      <c r="U60" s="77" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="65"/>
-      <c r="B61" s="65"/>
+      <c r="A61" s="43"/>
+      <c r="B61" s="43"/>
       <c r="C61" s="7"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="66"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="79"/>
-      <c r="H61" s="79"/>
-      <c r="I61" s="79"/>
-      <c r="J61" s="79"/>
-      <c r="K61" s="79"/>
-      <c r="L61" s="79"/>
-      <c r="M61" s="79"/>
-      <c r="N61" s="79"/>
-      <c r="O61" s="79"/>
-      <c r="P61" s="88"/>
-      <c r="Q61" s="88"/>
-      <c r="R61" s="88"/>
-      <c r="S61" s="88"/>
-      <c r="T61" s="88"/>
-      <c r="U61" s="88"/>
+      <c r="D61" s="47"/>
+      <c r="E61" s="53"/>
+      <c r="F61" s="97"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="35"/>
+      <c r="I61" s="35"/>
+      <c r="J61" s="35"/>
+      <c r="K61" s="35"/>
+      <c r="L61" s="35"/>
+      <c r="M61" s="35"/>
+      <c r="N61" s="35"/>
+      <c r="O61" s="35"/>
+      <c r="P61" s="77"/>
+      <c r="Q61" s="77"/>
+      <c r="R61" s="77"/>
+      <c r="S61" s="77"/>
+      <c r="T61" s="77"/>
+      <c r="U61" s="77"/>
     </row>
     <row r="62" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="65"/>
-      <c r="B62" s="65"/>
+      <c r="A62" s="43"/>
+      <c r="B62" s="43"/>
       <c r="C62" s="7"/>
-      <c r="D62" s="73"/>
-      <c r="E62" s="66"/>
-      <c r="F62" s="86"/>
-      <c r="G62" s="79"/>
-      <c r="H62" s="79"/>
-      <c r="I62" s="79"/>
-      <c r="J62" s="79"/>
-      <c r="K62" s="79"/>
-      <c r="L62" s="79"/>
-      <c r="M62" s="79"/>
-      <c r="N62" s="79"/>
-      <c r="O62" s="79"/>
-      <c r="P62" s="88"/>
-      <c r="Q62" s="88"/>
-      <c r="R62" s="88"/>
-      <c r="S62" s="88"/>
-      <c r="T62" s="88"/>
-      <c r="U62" s="88"/>
+      <c r="D62" s="47"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="97"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="35"/>
+      <c r="J62" s="35"/>
+      <c r="K62" s="35"/>
+      <c r="L62" s="35"/>
+      <c r="M62" s="35"/>
+      <c r="N62" s="35"/>
+      <c r="O62" s="35"/>
+      <c r="P62" s="77"/>
+      <c r="Q62" s="77"/>
+      <c r="R62" s="77"/>
+      <c r="S62" s="77"/>
+      <c r="T62" s="77"/>
+      <c r="U62" s="77"/>
     </row>
     <row r="63" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="65"/>
-      <c r="B63" s="65"/>
+      <c r="A63" s="43"/>
+      <c r="B63" s="43"/>
       <c r="C63" s="7"/>
-      <c r="D63" s="62" t="s">
+      <c r="D63" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="E63" s="61" t="s">
+      <c r="E63" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="F63" s="86"/>
-      <c r="G63" s="78" t="s">
+      <c r="F63" s="97"/>
+      <c r="G63" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="H63" s="78" t="s">
+      <c r="H63" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="I63" s="78" t="s">
+      <c r="I63" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="J63" s="78" t="s">
+      <c r="J63" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="K63" s="78" t="s">
+      <c r="K63" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="L63" s="78" t="s">
+      <c r="L63" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="M63" s="78" t="s">
+      <c r="M63" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="N63" s="78" t="s">
+      <c r="N63" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="O63" s="78" t="s">
+      <c r="O63" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="P63" s="95" t="s">
+      <c r="P63" s="92" t="s">
         <v>233</v>
       </c>
-      <c r="Q63" s="95" t="s">
+      <c r="Q63" s="92" t="s">
         <v>172</v>
       </c>
-      <c r="R63" s="95" t="s">
+      <c r="R63" s="92" t="s">
         <v>183</v>
       </c>
-      <c r="S63" s="95" t="s">
+      <c r="S63" s="92" t="s">
         <v>189</v>
       </c>
-      <c r="T63" s="95" t="s">
+      <c r="T63" s="92" t="s">
         <v>234</v>
       </c>
-      <c r="U63" s="95" t="s">
+      <c r="U63" s="92" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="64" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="65"/>
-      <c r="B64" s="65"/>
+      <c r="A64" s="43"/>
+      <c r="B64" s="43"/>
       <c r="C64" s="7"/>
-      <c r="D64" s="62"/>
-      <c r="E64" s="61"/>
-      <c r="F64" s="86"/>
-      <c r="G64" s="78"/>
-      <c r="H64" s="78"/>
-      <c r="I64" s="78"/>
-      <c r="J64" s="78"/>
-      <c r="K64" s="78"/>
-      <c r="L64" s="78"/>
-      <c r="M64" s="78"/>
-      <c r="N64" s="78"/>
-      <c r="O64" s="78"/>
-      <c r="P64" s="95"/>
-      <c r="Q64" s="95"/>
-      <c r="R64" s="95"/>
-      <c r="S64" s="95"/>
-      <c r="T64" s="95"/>
-      <c r="U64" s="95"/>
+      <c r="D64" s="44"/>
+      <c r="E64" s="50"/>
+      <c r="F64" s="97"/>
+      <c r="G64" s="37"/>
+      <c r="H64" s="37"/>
+      <c r="I64" s="37"/>
+      <c r="J64" s="37"/>
+      <c r="K64" s="37"/>
+      <c r="L64" s="37"/>
+      <c r="M64" s="37"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="92"/>
+      <c r="Q64" s="92"/>
+      <c r="R64" s="92"/>
+      <c r="S64" s="92"/>
+      <c r="T64" s="92"/>
+      <c r="U64" s="92"/>
     </row>
     <row r="65" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="65"/>
-      <c r="B65" s="65"/>
+      <c r="A65" s="43"/>
+      <c r="B65" s="43"/>
       <c r="C65" s="7"/>
-      <c r="D65" s="74">
+      <c r="D65" s="55">
         <v>223</v>
       </c>
-      <c r="E65" s="63">
+      <c r="E65" s="51">
         <v>226</v>
       </c>
-      <c r="F65" s="86"/>
-      <c r="G65" s="80">
+      <c r="F65" s="97"/>
+      <c r="G65" s="39">
         <v>267</v>
       </c>
-      <c r="H65" s="80">
+      <c r="H65" s="39">
         <v>268</v>
       </c>
-      <c r="I65" s="80">
+      <c r="I65" s="39">
         <v>269</v>
       </c>
-      <c r="J65" s="80">
+      <c r="J65" s="39">
         <v>270</v>
       </c>
-      <c r="K65" s="80">
+      <c r="K65" s="39">
         <v>269</v>
       </c>
-      <c r="L65" s="80">
+      <c r="L65" s="39">
         <v>277</v>
       </c>
-      <c r="M65" s="80">
+      <c r="M65" s="39">
         <v>281</v>
       </c>
-      <c r="N65" s="80">
+      <c r="N65" s="39">
         <v>282</v>
       </c>
-      <c r="O65" s="80">
+      <c r="O65" s="39">
         <v>285</v>
       </c>
-      <c r="P65" s="96">
+      <c r="P65" s="41">
         <v>286</v>
       </c>
-      <c r="Q65" s="96">
+      <c r="Q65" s="41">
         <v>290</v>
       </c>
-      <c r="R65" s="96">
+      <c r="R65" s="41">
         <v>290</v>
       </c>
-      <c r="S65" s="96">
+      <c r="S65" s="41">
         <v>293</v>
       </c>
-      <c r="T65" s="96">
+      <c r="T65" s="41">
         <v>294</v>
       </c>
-      <c r="U65" s="96">
+      <c r="U65" s="41">
         <v>294</v>
       </c>
     </row>
     <row r="66" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="65"/>
-      <c r="B66" s="65"/>
+      <c r="A66" s="43"/>
+      <c r="B66" s="43"/>
       <c r="C66" s="7"/>
-      <c r="D66" s="75"/>
-      <c r="E66" s="64"/>
-      <c r="F66" s="87"/>
-      <c r="G66" s="81"/>
-      <c r="H66" s="81"/>
-      <c r="I66" s="81"/>
-      <c r="J66" s="81"/>
-      <c r="K66" s="81"/>
-      <c r="L66" s="81"/>
-      <c r="M66" s="81"/>
-      <c r="N66" s="81"/>
-      <c r="O66" s="81"/>
-      <c r="P66" s="97"/>
-      <c r="Q66" s="97"/>
-      <c r="R66" s="97"/>
-      <c r="S66" s="97"/>
-      <c r="T66" s="97"/>
-      <c r="U66" s="97"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="52"/>
+      <c r="F66" s="98"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="40"/>
+      <c r="I66" s="40"/>
+      <c r="J66" s="40"/>
+      <c r="K66" s="40"/>
+      <c r="L66" s="40"/>
+      <c r="M66" s="40"/>
+      <c r="N66" s="40"/>
+      <c r="O66" s="40"/>
+      <c r="P66" s="42"/>
+      <c r="Q66" s="42"/>
+      <c r="R66" s="42"/>
+      <c r="S66" s="42"/>
+      <c r="T66" s="42"/>
+      <c r="U66" s="42"/>
     </row>
     <row r="67" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="12"/>
@@ -4475,207 +4475,207 @@
     </row>
     <row r="69" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E69" s="8"/>
-      <c r="F69" s="127" t="s">
+      <c r="F69" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="G69" s="121">
+      <c r="G69" s="33">
         <v>57</v>
       </c>
-      <c r="H69" s="121">
+      <c r="H69" s="33">
         <v>58</v>
       </c>
-      <c r="I69" s="121">
+      <c r="I69" s="33">
         <v>59</v>
       </c>
-      <c r="J69" s="121">
+      <c r="J69" s="33">
         <v>60</v>
       </c>
-      <c r="K69" s="121">
+      <c r="K69" s="33">
         <v>61</v>
       </c>
-      <c r="L69" s="121">
+      <c r="L69" s="33">
         <v>62</v>
       </c>
-      <c r="M69" s="121">
+      <c r="M69" s="33">
         <v>63</v>
       </c>
-      <c r="N69" s="121">
+      <c r="N69" s="33">
         <v>64</v>
       </c>
-      <c r="O69" s="121">
+      <c r="O69" s="33">
         <v>65</v>
       </c>
-      <c r="P69" s="121">
+      <c r="P69" s="33">
         <v>66</v>
       </c>
-      <c r="Q69" s="121">
+      <c r="Q69" s="33">
         <v>67</v>
       </c>
-      <c r="R69" s="121">
+      <c r="R69" s="33">
         <v>68</v>
       </c>
-      <c r="S69" s="121">
+      <c r="S69" s="33">
         <v>69</v>
       </c>
-      <c r="T69" s="121">
+      <c r="T69" s="33">
         <v>70</v>
       </c>
-      <c r="U69" s="121">
+      <c r="U69" s="33">
         <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E70" s="8"/>
-      <c r="F70" s="128"/>
-      <c r="G70" s="120"/>
-      <c r="H70" s="120"/>
-      <c r="I70" s="121"/>
-      <c r="J70" s="121"/>
-      <c r="K70" s="121"/>
-      <c r="L70" s="121"/>
-      <c r="M70" s="121"/>
-      <c r="N70" s="121"/>
-      <c r="O70" s="120"/>
-      <c r="P70" s="120"/>
-      <c r="Q70" s="120"/>
-      <c r="R70" s="120"/>
-      <c r="S70" s="120"/>
-      <c r="T70" s="120"/>
-      <c r="U70" s="121"/>
+      <c r="F70" s="49"/>
+      <c r="G70" s="34"/>
+      <c r="H70" s="34"/>
+      <c r="I70" s="33"/>
+      <c r="J70" s="33"/>
+      <c r="K70" s="33"/>
+      <c r="L70" s="33"/>
+      <c r="M70" s="33"/>
+      <c r="N70" s="33"/>
+      <c r="O70" s="34"/>
+      <c r="P70" s="34"/>
+      <c r="Q70" s="34"/>
+      <c r="R70" s="34"/>
+      <c r="S70" s="34"/>
+      <c r="T70" s="34"/>
+      <c r="U70" s="33"/>
     </row>
     <row r="71" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E71" s="8"/>
-      <c r="F71" s="128"/>
-      <c r="G71" s="122" t="s">
+      <c r="F71" s="49"/>
+      <c r="G71" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="H71" s="122" t="s">
+      <c r="H71" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="I71" s="122" t="s">
+      <c r="I71" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="J71" s="122" t="s">
+      <c r="J71" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="K71" s="122" t="s">
+      <c r="K71" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="L71" s="122" t="s">
+      <c r="L71" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="M71" s="122" t="s">
+      <c r="M71" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="N71" s="122" t="s">
+      <c r="N71" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="O71" s="122" t="s">
+      <c r="O71" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="P71" s="122" t="s">
+      <c r="P71" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="Q71" s="122" t="s">
+      <c r="Q71" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="R71" s="122" t="s">
+      <c r="R71" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="S71" s="122" t="s">
+      <c r="S71" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="T71" s="122" t="s">
+      <c r="T71" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="U71" s="122" t="s">
+      <c r="U71" s="32" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E72" s="8"/>
-      <c r="F72" s="128"/>
-      <c r="G72" s="122"/>
-      <c r="H72" s="122"/>
-      <c r="I72" s="122"/>
-      <c r="J72" s="122"/>
-      <c r="K72" s="122"/>
-      <c r="L72" s="122"/>
-      <c r="M72" s="122"/>
-      <c r="N72" s="122"/>
-      <c r="O72" s="122"/>
-      <c r="P72" s="122"/>
-      <c r="Q72" s="122"/>
-      <c r="R72" s="122"/>
-      <c r="S72" s="122"/>
-      <c r="T72" s="122"/>
-      <c r="U72" s="122"/>
+      <c r="F72" s="49"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="32"/>
+      <c r="K72" s="32"/>
+      <c r="L72" s="32"/>
+      <c r="M72" s="32"/>
+      <c r="N72" s="32"/>
+      <c r="O72" s="32"/>
+      <c r="P72" s="32"/>
+      <c r="Q72" s="32"/>
+      <c r="R72" s="32"/>
+      <c r="S72" s="32"/>
+      <c r="T72" s="32"/>
+      <c r="U72" s="32"/>
     </row>
     <row r="73" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E73" s="8"/>
-      <c r="F73" s="128"/>
-      <c r="G73" s="122"/>
-      <c r="H73" s="122"/>
-      <c r="I73" s="122"/>
-      <c r="J73" s="122"/>
-      <c r="K73" s="122"/>
-      <c r="L73" s="122"/>
-      <c r="M73" s="122"/>
-      <c r="N73" s="122"/>
-      <c r="O73" s="122"/>
-      <c r="P73" s="122"/>
-      <c r="Q73" s="122"/>
-      <c r="R73" s="122"/>
-      <c r="S73" s="122"/>
-      <c r="T73" s="122"/>
-      <c r="U73" s="122"/>
+      <c r="F73" s="49"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="32"/>
+      <c r="J73" s="32"/>
+      <c r="K73" s="32"/>
+      <c r="L73" s="32"/>
+      <c r="M73" s="32"/>
+      <c r="N73" s="32"/>
+      <c r="O73" s="32"/>
+      <c r="P73" s="32"/>
+      <c r="Q73" s="32"/>
+      <c r="R73" s="32"/>
+      <c r="S73" s="32"/>
+      <c r="T73" s="32"/>
+      <c r="U73" s="32"/>
     </row>
     <row r="74" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E74" s="8"/>
-      <c r="F74" s="128"/>
-      <c r="G74" s="120" t="s">
+      <c r="F74" s="49"/>
+      <c r="G74" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="H74" s="120" t="s">
+      <c r="H74" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="I74" s="120" t="s">
+      <c r="I74" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="J74" s="120" t="s">
+      <c r="J74" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="K74" s="120" t="s">
+      <c r="K74" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="L74" s="120" t="s">
+      <c r="L74" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="M74" s="120" t="s">
+      <c r="M74" s="34" t="s">
         <v>206</v>
       </c>
-      <c r="N74" s="120" t="s">
+      <c r="N74" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="O74" s="120" t="s">
+      <c r="O74" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="P74" s="120" t="s">
+      <c r="P74" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="Q74" s="120" t="s">
+      <c r="Q74" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="R74" s="120" t="s">
+      <c r="R74" s="34" t="s">
         <v>211</v>
       </c>
-      <c r="S74" s="120" t="s">
+      <c r="S74" s="34" t="s">
         <v>212</v>
       </c>
-      <c r="T74" s="120" t="s">
+      <c r="T74" s="34" t="s">
         <v>213</v>
       </c>
-      <c r="U74" s="120" t="s">
+      <c r="U74" s="34" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4683,71 +4683,71 @@
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="E75" s="8"/>
-      <c r="F75" s="128"/>
-      <c r="G75" s="120"/>
-      <c r="H75" s="120"/>
-      <c r="I75" s="120"/>
-      <c r="J75" s="120"/>
-      <c r="K75" s="120"/>
-      <c r="L75" s="120"/>
-      <c r="M75" s="120"/>
-      <c r="N75" s="120"/>
-      <c r="O75" s="120"/>
-      <c r="P75" s="120"/>
-      <c r="Q75" s="120"/>
-      <c r="R75" s="120"/>
-      <c r="S75" s="120"/>
-      <c r="T75" s="120"/>
-      <c r="U75" s="120"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="34"/>
+      <c r="H75" s="34"/>
+      <c r="I75" s="34"/>
+      <c r="J75" s="34"/>
+      <c r="K75" s="34"/>
+      <c r="L75" s="34"/>
+      <c r="M75" s="34"/>
+      <c r="N75" s="34"/>
+      <c r="O75" s="34"/>
+      <c r="P75" s="34"/>
+      <c r="Q75" s="34"/>
+      <c r="R75" s="34"/>
+      <c r="S75" s="34"/>
+      <c r="T75" s="34"/>
+      <c r="U75" s="34"/>
     </row>
     <row r="76" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="E76" s="8"/>
-      <c r="F76" s="128"/>
-      <c r="G76" s="124">
+      <c r="F76" s="49"/>
+      <c r="G76" s="31">
         <v>138.91</v>
       </c>
-      <c r="H76" s="124">
+      <c r="H76" s="31">
         <v>140.12</v>
       </c>
-      <c r="I76" s="124">
+      <c r="I76" s="31">
         <v>140.91</v>
       </c>
-      <c r="J76" s="124">
+      <c r="J76" s="31">
         <v>144.24</v>
       </c>
-      <c r="K76" s="124">
+      <c r="K76" s="31">
         <v>145</v>
       </c>
-      <c r="L76" s="124">
+      <c r="L76" s="31">
         <v>150.36000000000001</v>
       </c>
-      <c r="M76" s="124">
+      <c r="M76" s="31">
         <v>151.96</v>
       </c>
-      <c r="N76" s="124">
+      <c r="N76" s="31">
         <v>157.25</v>
       </c>
-      <c r="O76" s="124">
+      <c r="O76" s="31">
         <v>158.93</v>
       </c>
-      <c r="P76" s="124">
+      <c r="P76" s="31">
         <v>162.5</v>
       </c>
-      <c r="Q76" s="124">
+      <c r="Q76" s="31">
         <v>164.93</v>
       </c>
-      <c r="R76" s="124">
+      <c r="R76" s="31">
         <v>167.26</v>
       </c>
-      <c r="S76" s="124">
+      <c r="S76" s="31">
         <v>168.93</v>
       </c>
-      <c r="T76" s="124">
+      <c r="T76" s="31">
         <v>173.05</v>
       </c>
-      <c r="U76" s="124">
+      <c r="U76" s="31">
         <v>174.97</v>
       </c>
     </row>
@@ -4755,338 +4755,338 @@
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="E77" s="8"/>
-      <c r="F77" s="128"/>
-      <c r="G77" s="125"/>
-      <c r="H77" s="125"/>
-      <c r="I77" s="125"/>
-      <c r="J77" s="125"/>
-      <c r="K77" s="125"/>
-      <c r="L77" s="125"/>
-      <c r="M77" s="125"/>
-      <c r="N77" s="125"/>
-      <c r="O77" s="124"/>
-      <c r="P77" s="124"/>
-      <c r="Q77" s="124"/>
-      <c r="R77" s="124"/>
-      <c r="S77" s="124"/>
-      <c r="T77" s="124"/>
-      <c r="U77" s="124"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="38"/>
+      <c r="H77" s="38"/>
+      <c r="I77" s="38"/>
+      <c r="J77" s="38"/>
+      <c r="K77" s="38"/>
+      <c r="L77" s="38"/>
+      <c r="M77" s="38"/>
+      <c r="N77" s="38"/>
+      <c r="O77" s="31"/>
+      <c r="P77" s="31"/>
+      <c r="Q77" s="31"/>
+      <c r="R77" s="31"/>
+      <c r="S77" s="31"/>
+      <c r="T77" s="31"/>
+      <c r="U77" s="31"/>
     </row>
     <row r="78" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D78" s="39" t="s">
+      <c r="D78" s="104" t="s">
         <v>248</v>
       </c>
-      <c r="E78" s="51"/>
-      <c r="F78" s="54" t="s">
+      <c r="E78" s="116"/>
+      <c r="F78" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="G78" s="55">
+      <c r="G78" s="30">
         <v>89</v>
       </c>
-      <c r="H78" s="55">
+      <c r="H78" s="30">
         <v>90</v>
       </c>
-      <c r="I78" s="55">
+      <c r="I78" s="30">
         <v>91</v>
       </c>
-      <c r="J78" s="55">
+      <c r="J78" s="30">
         <v>92</v>
       </c>
-      <c r="K78" s="55">
+      <c r="K78" s="30">
         <v>93</v>
       </c>
-      <c r="L78" s="55">
+      <c r="L78" s="30">
         <v>94</v>
       </c>
-      <c r="M78" s="55">
+      <c r="M78" s="30">
         <v>95</v>
       </c>
-      <c r="N78" s="55">
+      <c r="N78" s="30">
         <v>96</v>
       </c>
-      <c r="O78" s="55">
+      <c r="O78" s="30">
         <v>97</v>
       </c>
-      <c r="P78" s="55">
+      <c r="P78" s="30">
         <v>98</v>
       </c>
-      <c r="Q78" s="55">
+      <c r="Q78" s="30">
         <v>99</v>
       </c>
-      <c r="R78" s="55">
+      <c r="R78" s="30">
         <v>100</v>
       </c>
-      <c r="S78" s="55">
+      <c r="S78" s="30">
         <v>101</v>
       </c>
-      <c r="T78" s="55">
+      <c r="T78" s="30">
         <v>102</v>
       </c>
-      <c r="U78" s="55">
+      <c r="U78" s="30">
         <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D79" s="39"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="54"/>
-      <c r="G79" s="55"/>
-      <c r="H79" s="55"/>
-      <c r="I79" s="55"/>
-      <c r="J79" s="55"/>
-      <c r="K79" s="55"/>
-      <c r="L79" s="55"/>
-      <c r="M79" s="55"/>
-      <c r="N79" s="55"/>
-      <c r="O79" s="55"/>
-      <c r="P79" s="55"/>
-      <c r="Q79" s="55"/>
-      <c r="R79" s="55"/>
-      <c r="S79" s="55"/>
-      <c r="T79" s="55"/>
-      <c r="U79" s="55"/>
+      <c r="D79" s="104"/>
+      <c r="E79" s="116"/>
+      <c r="F79" s="119"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
+      <c r="J79" s="30"/>
+      <c r="K79" s="30"/>
+      <c r="L79" s="30"/>
+      <c r="M79" s="30"/>
+      <c r="N79" s="30"/>
+      <c r="O79" s="30"/>
+      <c r="P79" s="30"/>
+      <c r="Q79" s="30"/>
+      <c r="R79" s="30"/>
+      <c r="S79" s="30"/>
+      <c r="T79" s="30"/>
+      <c r="U79" s="30"/>
     </row>
     <row r="80" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D80" s="40" t="s">
+      <c r="D80" s="105" t="s">
         <v>249</v>
       </c>
-      <c r="E80" s="52"/>
-      <c r="F80" s="54"/>
-      <c r="G80" s="50" t="s">
+      <c r="E80" s="117"/>
+      <c r="F80" s="119"/>
+      <c r="G80" s="115" t="s">
         <v>106</v>
       </c>
-      <c r="H80" s="108" t="s">
+      <c r="H80" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="I80" s="123" t="s">
+      <c r="I80" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="J80" s="108" t="s">
+      <c r="J80" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="K80" s="112" t="s">
+      <c r="K80" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="L80" s="108" t="s">
+      <c r="L80" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="M80" s="108" t="s">
+      <c r="M80" s="58" t="s">
         <v>112</v>
       </c>
-      <c r="N80" s="108" t="s">
+      <c r="N80" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="O80" s="108" t="s">
+      <c r="O80" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="P80" s="108" t="s">
+      <c r="P80" s="58" t="s">
         <v>115</v>
       </c>
-      <c r="Q80" s="108" t="s">
+      <c r="Q80" s="58" t="s">
         <v>116</v>
       </c>
-      <c r="R80" s="108" t="s">
+      <c r="R80" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="S80" s="108" t="s">
+      <c r="S80" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="T80" s="108" t="s">
+      <c r="T80" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="U80" s="108" t="s">
+      <c r="U80" s="58" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D81" s="40"/>
-      <c r="E81" s="52"/>
-      <c r="F81" s="54"/>
-      <c r="G81" s="50"/>
-      <c r="H81" s="108"/>
-      <c r="I81" s="123"/>
-      <c r="J81" s="108"/>
-      <c r="K81" s="112"/>
-      <c r="L81" s="108"/>
-      <c r="M81" s="108"/>
-      <c r="N81" s="108"/>
-      <c r="O81" s="108"/>
-      <c r="P81" s="108"/>
-      <c r="Q81" s="108"/>
-      <c r="R81" s="108"/>
-      <c r="S81" s="108"/>
-      <c r="T81" s="108"/>
-      <c r="U81" s="108"/>
+      <c r="D81" s="105"/>
+      <c r="E81" s="117"/>
+      <c r="F81" s="119"/>
+      <c r="G81" s="115"/>
+      <c r="H81" s="58"/>
+      <c r="I81" s="59"/>
+      <c r="J81" s="58"/>
+      <c r="K81" s="82"/>
+      <c r="L81" s="58"/>
+      <c r="M81" s="58"/>
+      <c r="N81" s="58"/>
+      <c r="O81" s="58"/>
+      <c r="P81" s="58"/>
+      <c r="Q81" s="58"/>
+      <c r="R81" s="58"/>
+      <c r="S81" s="58"/>
+      <c r="T81" s="58"/>
+      <c r="U81" s="58"/>
     </row>
     <row r="82" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D82" s="40"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="54"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="108"/>
-      <c r="I82" s="123"/>
-      <c r="J82" s="108"/>
-      <c r="K82" s="112"/>
-      <c r="L82" s="108"/>
-      <c r="M82" s="108"/>
-      <c r="N82" s="108"/>
-      <c r="O82" s="108"/>
-      <c r="P82" s="108"/>
-      <c r="Q82" s="108"/>
-      <c r="R82" s="108"/>
-      <c r="S82" s="108"/>
-      <c r="T82" s="108"/>
-      <c r="U82" s="108"/>
+      <c r="D82" s="105"/>
+      <c r="E82" s="117"/>
+      <c r="F82" s="119"/>
+      <c r="G82" s="115"/>
+      <c r="H82" s="58"/>
+      <c r="I82" s="59"/>
+      <c r="J82" s="58"/>
+      <c r="K82" s="82"/>
+      <c r="L82" s="58"/>
+      <c r="M82" s="58"/>
+      <c r="N82" s="58"/>
+      <c r="O82" s="58"/>
+      <c r="P82" s="58"/>
+      <c r="Q82" s="58"/>
+      <c r="R82" s="58"/>
+      <c r="S82" s="58"/>
+      <c r="T82" s="58"/>
+      <c r="U82" s="58"/>
     </row>
     <row r="83" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D83" s="39" t="s">
+      <c r="D83" s="104" t="s">
         <v>250</v>
       </c>
-      <c r="E83" s="51"/>
-      <c r="F83" s="54"/>
-      <c r="G83" s="119" t="s">
+      <c r="E83" s="116"/>
+      <c r="F83" s="119"/>
+      <c r="G83" s="78" t="s">
         <v>215</v>
       </c>
-      <c r="H83" s="109" t="s">
+      <c r="H83" s="81" t="s">
         <v>216</v>
       </c>
-      <c r="I83" s="113" t="s">
+      <c r="I83" s="83" t="s">
         <v>217</v>
       </c>
-      <c r="J83" s="109" t="s">
+      <c r="J83" s="81" t="s">
         <v>218</v>
       </c>
-      <c r="K83" s="114" t="s">
+      <c r="K83" s="84" t="s">
         <v>236</v>
       </c>
-      <c r="L83" s="109" t="s">
+      <c r="L83" s="81" t="s">
         <v>219</v>
       </c>
-      <c r="M83" s="109" t="s">
+      <c r="M83" s="81" t="s">
         <v>220</v>
       </c>
-      <c r="N83" s="109" t="s">
+      <c r="N83" s="81" t="s">
         <v>221</v>
       </c>
-      <c r="O83" s="109" t="s">
+      <c r="O83" s="81" t="s">
         <v>222</v>
       </c>
-      <c r="P83" s="109" t="s">
+      <c r="P83" s="81" t="s">
         <v>223</v>
       </c>
-      <c r="Q83" s="109" t="s">
+      <c r="Q83" s="81" t="s">
         <v>224</v>
       </c>
-      <c r="R83" s="109" t="s">
+      <c r="R83" s="81" t="s">
         <v>225</v>
       </c>
-      <c r="S83" s="109" t="s">
+      <c r="S83" s="81" t="s">
         <v>237</v>
       </c>
-      <c r="T83" s="109" t="s">
+      <c r="T83" s="81" t="s">
         <v>226</v>
       </c>
-      <c r="U83" s="109" t="s">
+      <c r="U83" s="81" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="84" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
-      <c r="D84" s="39"/>
-      <c r="E84" s="51"/>
-      <c r="F84" s="54"/>
-      <c r="G84" s="119"/>
-      <c r="H84" s="109"/>
-      <c r="I84" s="113"/>
-      <c r="J84" s="109"/>
-      <c r="K84" s="114"/>
-      <c r="L84" s="109"/>
-      <c r="M84" s="109"/>
-      <c r="N84" s="109"/>
-      <c r="O84" s="109"/>
-      <c r="P84" s="109"/>
-      <c r="Q84" s="109"/>
-      <c r="R84" s="109"/>
-      <c r="S84" s="109"/>
-      <c r="T84" s="109"/>
-      <c r="U84" s="109"/>
+      <c r="D84" s="104"/>
+      <c r="E84" s="116"/>
+      <c r="F84" s="119"/>
+      <c r="G84" s="78"/>
+      <c r="H84" s="81"/>
+      <c r="I84" s="83"/>
+      <c r="J84" s="81"/>
+      <c r="K84" s="84"/>
+      <c r="L84" s="81"/>
+      <c r="M84" s="81"/>
+      <c r="N84" s="81"/>
+      <c r="O84" s="81"/>
+      <c r="P84" s="81"/>
+      <c r="Q84" s="81"/>
+      <c r="R84" s="81"/>
+      <c r="S84" s="81"/>
+      <c r="T84" s="81"/>
+      <c r="U84" s="81"/>
     </row>
     <row r="85" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
-      <c r="D85" s="41" t="s">
+      <c r="D85" s="106" t="s">
         <v>251</v>
       </c>
-      <c r="E85" s="53"/>
-      <c r="F85" s="54"/>
-      <c r="G85" s="48">
+      <c r="E85" s="118"/>
+      <c r="F85" s="119"/>
+      <c r="G85" s="113">
         <v>227</v>
       </c>
-      <c r="H85" s="110">
+      <c r="H85" s="79">
         <v>232.04</v>
       </c>
-      <c r="I85" s="115">
+      <c r="I85" s="85">
         <v>231.04</v>
       </c>
-      <c r="J85" s="110">
+      <c r="J85" s="79">
         <v>238.03</v>
       </c>
-      <c r="K85" s="117">
+      <c r="K85" s="87">
         <v>237</v>
       </c>
-      <c r="L85" s="110">
+      <c r="L85" s="79">
         <v>244</v>
       </c>
-      <c r="M85" s="110">
+      <c r="M85" s="79">
         <v>243</v>
       </c>
-      <c r="N85" s="110">
+      <c r="N85" s="79">
         <v>247</v>
       </c>
-      <c r="O85" s="110">
+      <c r="O85" s="79">
         <v>247</v>
       </c>
-      <c r="P85" s="110">
+      <c r="P85" s="79">
         <v>251</v>
       </c>
-      <c r="Q85" s="110">
+      <c r="Q85" s="79">
         <v>252</v>
       </c>
-      <c r="R85" s="110">
+      <c r="R85" s="79">
         <v>257</v>
       </c>
-      <c r="S85" s="110">
+      <c r="S85" s="79">
         <v>258</v>
       </c>
-      <c r="T85" s="110">
+      <c r="T85" s="79">
         <v>259</v>
       </c>
-      <c r="U85" s="110">
+      <c r="U85" s="79">
         <v>266</v>
       </c>
     </row>
     <row r="86" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
-      <c r="D86" s="41"/>
-      <c r="E86" s="53"/>
-      <c r="F86" s="54"/>
-      <c r="G86" s="49"/>
-      <c r="H86" s="111"/>
-      <c r="I86" s="116"/>
-      <c r="J86" s="111"/>
-      <c r="K86" s="118"/>
-      <c r="L86" s="111"/>
-      <c r="M86" s="111"/>
-      <c r="N86" s="111"/>
-      <c r="O86" s="111"/>
-      <c r="P86" s="111"/>
-      <c r="Q86" s="111"/>
-      <c r="R86" s="111"/>
-      <c r="S86" s="111"/>
-      <c r="T86" s="111"/>
-      <c r="U86" s="111"/>
+      <c r="D86" s="106"/>
+      <c r="E86" s="118"/>
+      <c r="F86" s="119"/>
+      <c r="G86" s="114"/>
+      <c r="H86" s="80"/>
+      <c r="I86" s="86"/>
+      <c r="J86" s="80"/>
+      <c r="K86" s="88"/>
+      <c r="L86" s="80"/>
+      <c r="M86" s="80"/>
+      <c r="N86" s="80"/>
+      <c r="O86" s="80"/>
+      <c r="P86" s="80"/>
+      <c r="Q86" s="80"/>
+      <c r="R86" s="80"/>
+      <c r="S86" s="80"/>
+      <c r="T86" s="80"/>
+      <c r="U86" s="80"/>
     </row>
     <row r="87" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
@@ -5137,50 +5137,50 @@
       <c r="B89" s="3"/>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
-      <c r="H89" s="42" t="s">
+      <c r="H89" s="107" t="s">
         <v>240</v>
       </c>
-      <c r="I89" s="42"/>
+      <c r="I89" s="107"/>
       <c r="J89" s="16"/>
-      <c r="K89" s="44" t="s">
+      <c r="K89" s="109" t="s">
         <v>252</v>
       </c>
-      <c r="L89" s="44"/>
+      <c r="L89" s="109"/>
       <c r="M89" s="15"/>
-      <c r="N89" s="46" t="s">
+      <c r="N89" s="111" t="s">
         <v>244</v>
       </c>
-      <c r="O89" s="46"/>
+      <c r="O89" s="111"/>
       <c r="P89" s="15"/>
-      <c r="Q89" s="56" t="s">
+      <c r="Q89" s="99" t="s">
         <v>242</v>
       </c>
-      <c r="R89" s="56"/>
+      <c r="R89" s="99"/>
       <c r="S89" s="16"/>
-      <c r="T89" s="58" t="s">
+      <c r="T89" s="101" t="s">
         <v>246</v>
       </c>
-      <c r="U89" s="58"/>
+      <c r="U89" s="101"/>
     </row>
     <row r="90" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="E90" s="11"/>
       <c r="F90" s="11"/>
-      <c r="H90" s="42"/>
-      <c r="I90" s="42"/>
+      <c r="H90" s="107"/>
+      <c r="I90" s="107"/>
       <c r="J90" s="16"/>
-      <c r="K90" s="44"/>
-      <c r="L90" s="44"/>
+      <c r="K90" s="109"/>
+      <c r="L90" s="109"/>
       <c r="M90" s="15"/>
-      <c r="N90" s="46"/>
-      <c r="O90" s="46"/>
+      <c r="N90" s="111"/>
+      <c r="O90" s="111"/>
       <c r="P90" s="15"/>
-      <c r="Q90" s="56"/>
-      <c r="R90" s="56"/>
+      <c r="Q90" s="99"/>
+      <c r="R90" s="99"/>
       <c r="S90" s="16"/>
-      <c r="T90" s="58"/>
-      <c r="U90" s="58"/>
+      <c r="T90" s="101"/>
+      <c r="U90" s="101"/>
     </row>
     <row r="91" spans="1:21" s="6" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
@@ -5227,48 +5227,48 @@
       <c r="B93" s="3"/>
       <c r="E93" s="11"/>
       <c r="F93" s="11"/>
-      <c r="H93" s="43" t="s">
+      <c r="H93" s="108" t="s">
         <v>239</v>
       </c>
-      <c r="I93" s="43"/>
+      <c r="I93" s="108"/>
       <c r="J93" s="16"/>
-      <c r="K93" s="45" t="s">
+      <c r="K93" s="110" t="s">
         <v>247</v>
       </c>
-      <c r="L93" s="45"/>
+      <c r="L93" s="110"/>
       <c r="M93" s="15"/>
-      <c r="N93" s="47" t="s">
+      <c r="N93" s="112" t="s">
         <v>245</v>
       </c>
-      <c r="O93" s="47"/>
+      <c r="O93" s="112"/>
       <c r="P93" s="15"/>
-      <c r="Q93" s="57" t="s">
+      <c r="Q93" s="100" t="s">
         <v>241</v>
       </c>
-      <c r="R93" s="57"/>
+      <c r="R93" s="100"/>
       <c r="S93" s="16"/>
-      <c r="T93" s="59" t="s">
+      <c r="T93" s="102" t="s">
         <v>243</v>
       </c>
-      <c r="U93" s="59"/>
+      <c r="U93" s="102"/>
     </row>
     <row r="94" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E94" s="11"/>
       <c r="F94" s="11"/>
-      <c r="H94" s="43"/>
-      <c r="I94" s="43"/>
+      <c r="H94" s="108"/>
+      <c r="I94" s="108"/>
       <c r="J94" s="16"/>
-      <c r="K94" s="45"/>
-      <c r="L94" s="45"/>
+      <c r="K94" s="110"/>
+      <c r="L94" s="110"/>
       <c r="M94" s="15"/>
-      <c r="N94" s="47"/>
-      <c r="O94" s="47"/>
+      <c r="N94" s="112"/>
+      <c r="O94" s="112"/>
       <c r="P94" s="15"/>
-      <c r="Q94" s="57"/>
-      <c r="R94" s="57"/>
+      <c r="Q94" s="100"/>
+      <c r="R94" s="100"/>
       <c r="S94" s="16"/>
-      <c r="T94" s="59"/>
-      <c r="U94" s="59"/>
+      <c r="T94" s="102"/>
+      <c r="U94" s="102"/>
     </row>
     <row r="95" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4"/>
@@ -5596,27 +5596,27 @@
       <c r="U112" s="10"/>
     </row>
     <row r="113" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="60"/>
-      <c r="B113" s="60"/>
-      <c r="C113" s="60"/>
-      <c r="D113" s="60"/>
-      <c r="E113" s="60"/>
-      <c r="F113" s="60"/>
-      <c r="G113" s="60"/>
-      <c r="H113" s="60"/>
-      <c r="I113" s="60"/>
-      <c r="J113" s="60"/>
-      <c r="K113" s="60"/>
-      <c r="L113" s="60"/>
-      <c r="M113" s="60"/>
-      <c r="N113" s="60"/>
-      <c r="O113" s="60"/>
-      <c r="P113" s="60"/>
-      <c r="Q113" s="60"/>
-      <c r="R113" s="60"/>
-      <c r="S113" s="60"/>
-      <c r="T113" s="60"/>
-      <c r="U113" s="60"/>
+      <c r="A113" s="103"/>
+      <c r="B113" s="103"/>
+      <c r="C113" s="103"/>
+      <c r="D113" s="103"/>
+      <c r="E113" s="103"/>
+      <c r="F113" s="103"/>
+      <c r="G113" s="103"/>
+      <c r="H113" s="103"/>
+      <c r="I113" s="103"/>
+      <c r="J113" s="103"/>
+      <c r="K113" s="103"/>
+      <c r="L113" s="103"/>
+      <c r="M113" s="103"/>
+      <c r="N113" s="103"/>
+      <c r="O113" s="103"/>
+      <c r="P113" s="103"/>
+      <c r="Q113" s="103"/>
+      <c r="R113" s="103"/>
+      <c r="S113" s="103"/>
+      <c r="T113" s="103"/>
+      <c r="U113" s="103"/>
     </row>
     <row r="114" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="115" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5626,23 +5626,493 @@
     <row r="119" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="528">
-    <mergeCell ref="U78:U79"/>
-    <mergeCell ref="U76:U77"/>
-    <mergeCell ref="U71:U73"/>
-    <mergeCell ref="U69:U70"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="R74:R75"/>
-    <mergeCell ref="S74:S75"/>
-    <mergeCell ref="T74:T75"/>
-    <mergeCell ref="U74:U75"/>
-    <mergeCell ref="R78:R79"/>
-    <mergeCell ref="T76:T77"/>
-    <mergeCell ref="S76:S77"/>
-    <mergeCell ref="T78:T79"/>
-    <mergeCell ref="S78:S79"/>
-    <mergeCell ref="Q71:Q73"/>
-    <mergeCell ref="R71:R73"/>
-    <mergeCell ref="S71:S73"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="H89:I90"/>
+    <mergeCell ref="H93:I94"/>
+    <mergeCell ref="K89:L90"/>
+    <mergeCell ref="K93:L94"/>
+    <mergeCell ref="N89:O90"/>
+    <mergeCell ref="N93:O94"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="G80:G82"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F78:F86"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="Q89:R90"/>
+    <mergeCell ref="Q93:R94"/>
+    <mergeCell ref="T89:U90"/>
+    <mergeCell ref="T93:U94"/>
+    <mergeCell ref="A113:U113"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="A4:A12"/>
+    <mergeCell ref="A13:A21"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="A31:A39"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="A49:A57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="E60:E62"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="I51:I53"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="I60:I62"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="H60:H62"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="F49:F57"/>
+    <mergeCell ref="F58:F66"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H42:H44"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="L42:L44"/>
+    <mergeCell ref="M42:M44"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="L38:L39"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="K40:K41"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="J42:J44"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="M45:M46"/>
+    <mergeCell ref="L45:L46"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I35"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="J33:J35"/>
+    <mergeCell ref="K33:K35"/>
+    <mergeCell ref="L33:L35"/>
+    <mergeCell ref="M33:M35"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="L56:L57"/>
+    <mergeCell ref="M56:M57"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="J51:J53"/>
+    <mergeCell ref="K51:K53"/>
+    <mergeCell ref="L51:L53"/>
+    <mergeCell ref="M51:M53"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="M54:M55"/>
+    <mergeCell ref="L54:L55"/>
+    <mergeCell ref="N51:N53"/>
+    <mergeCell ref="O51:O53"/>
+    <mergeCell ref="P51:P53"/>
+    <mergeCell ref="Q51:Q53"/>
+    <mergeCell ref="R51:R53"/>
+    <mergeCell ref="S51:S53"/>
+    <mergeCell ref="U54:U55"/>
+    <mergeCell ref="T54:T55"/>
+    <mergeCell ref="S47:S48"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P49:P50"/>
+    <mergeCell ref="Q49:Q50"/>
+    <mergeCell ref="Q65:Q66"/>
+    <mergeCell ref="R65:R66"/>
+    <mergeCell ref="S65:S66"/>
+    <mergeCell ref="R49:R50"/>
+    <mergeCell ref="S49:S50"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="Q47:Q48"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="Q60:Q62"/>
+    <mergeCell ref="R60:R62"/>
+    <mergeCell ref="S60:S62"/>
+    <mergeCell ref="P63:P64"/>
+    <mergeCell ref="S63:S64"/>
+    <mergeCell ref="R63:R64"/>
+    <mergeCell ref="Q63:Q64"/>
+    <mergeCell ref="R45:R46"/>
+    <mergeCell ref="Q45:Q46"/>
+    <mergeCell ref="N58:N59"/>
+    <mergeCell ref="O58:O59"/>
+    <mergeCell ref="P58:P59"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="R58:R59"/>
+    <mergeCell ref="S58:S59"/>
+    <mergeCell ref="P33:P35"/>
+    <mergeCell ref="Q33:Q35"/>
+    <mergeCell ref="P54:P55"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="O54:O55"/>
+    <mergeCell ref="P56:P57"/>
+    <mergeCell ref="Q56:Q57"/>
+    <mergeCell ref="R56:R57"/>
+    <mergeCell ref="S56:S57"/>
+    <mergeCell ref="R42:R44"/>
+    <mergeCell ref="S42:S44"/>
+    <mergeCell ref="P42:P44"/>
+    <mergeCell ref="Q42:Q44"/>
+    <mergeCell ref="N40:N41"/>
+    <mergeCell ref="O40:O41"/>
+    <mergeCell ref="P40:P41"/>
+    <mergeCell ref="Q40:Q41"/>
+    <mergeCell ref="T58:T59"/>
+    <mergeCell ref="U58:U59"/>
+    <mergeCell ref="P60:P62"/>
+    <mergeCell ref="P36:P37"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="T60:T62"/>
+    <mergeCell ref="U60:U62"/>
+    <mergeCell ref="T42:T44"/>
+    <mergeCell ref="U42:U44"/>
+    <mergeCell ref="R40:R41"/>
+    <mergeCell ref="S40:S41"/>
+    <mergeCell ref="T56:T57"/>
+    <mergeCell ref="U56:U57"/>
+    <mergeCell ref="T49:T50"/>
+    <mergeCell ref="U49:U50"/>
+    <mergeCell ref="U31:U32"/>
+    <mergeCell ref="Q27:Q28"/>
+    <mergeCell ref="R33:R35"/>
+    <mergeCell ref="S33:S35"/>
+    <mergeCell ref="S36:S37"/>
+    <mergeCell ref="R36:R37"/>
+    <mergeCell ref="Q36:Q37"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="T33:T35"/>
+    <mergeCell ref="U33:U35"/>
+    <mergeCell ref="P31:P32"/>
+    <mergeCell ref="Q31:Q32"/>
+    <mergeCell ref="R31:R32"/>
+    <mergeCell ref="P27:P28"/>
+    <mergeCell ref="T65:T66"/>
+    <mergeCell ref="U65:U66"/>
+    <mergeCell ref="U63:U64"/>
+    <mergeCell ref="T63:T64"/>
+    <mergeCell ref="P38:P39"/>
+    <mergeCell ref="Q38:Q39"/>
+    <mergeCell ref="R38:R39"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:T39"/>
+    <mergeCell ref="U38:U39"/>
+    <mergeCell ref="S54:S55"/>
+    <mergeCell ref="R54:R55"/>
+    <mergeCell ref="Q54:Q55"/>
+    <mergeCell ref="U45:U46"/>
+    <mergeCell ref="T45:T46"/>
+    <mergeCell ref="S45:S46"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="Q20:Q21"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="T20:T21"/>
+    <mergeCell ref="U20:U21"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="Q15:Q17"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="Q80:Q82"/>
+    <mergeCell ref="M83:M84"/>
+    <mergeCell ref="N83:N84"/>
+    <mergeCell ref="S85:S86"/>
+    <mergeCell ref="K80:K82"/>
+    <mergeCell ref="L80:L82"/>
+    <mergeCell ref="M80:M82"/>
+    <mergeCell ref="N80:N82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="J83:J84"/>
+    <mergeCell ref="K83:K84"/>
+    <mergeCell ref="L83:L84"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="K85:K86"/>
+    <mergeCell ref="L85:L86"/>
+    <mergeCell ref="P80:P82"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="T85:T86"/>
+    <mergeCell ref="U80:U82"/>
+    <mergeCell ref="U85:U86"/>
+    <mergeCell ref="M85:M86"/>
+    <mergeCell ref="N85:N86"/>
+    <mergeCell ref="O85:O86"/>
+    <mergeCell ref="P85:P86"/>
+    <mergeCell ref="Q85:Q86"/>
+    <mergeCell ref="R85:R86"/>
+    <mergeCell ref="R80:R82"/>
+    <mergeCell ref="S80:S82"/>
+    <mergeCell ref="T80:T82"/>
+    <mergeCell ref="O80:O82"/>
+    <mergeCell ref="P83:P84"/>
+    <mergeCell ref="O83:O84"/>
+    <mergeCell ref="U83:U84"/>
+    <mergeCell ref="T83:T84"/>
+    <mergeCell ref="S83:S84"/>
+    <mergeCell ref="R83:R84"/>
+    <mergeCell ref="Q83:Q84"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="S29:S30"/>
+    <mergeCell ref="T29:T30"/>
+    <mergeCell ref="U29:U30"/>
+    <mergeCell ref="P24:P26"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="U18:U19"/>
+    <mergeCell ref="T18:T19"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="R15:R17"/>
+    <mergeCell ref="S15:S17"/>
+    <mergeCell ref="T15:T17"/>
+    <mergeCell ref="U15:U17"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="U1:U2"/>
+    <mergeCell ref="T71:T73"/>
+    <mergeCell ref="S69:S70"/>
+    <mergeCell ref="T69:T70"/>
+    <mergeCell ref="Q69:Q70"/>
+    <mergeCell ref="R69:R70"/>
+    <mergeCell ref="Q24:Q26"/>
+    <mergeCell ref="R24:R26"/>
+    <mergeCell ref="S24:S26"/>
+    <mergeCell ref="T24:T26"/>
+    <mergeCell ref="U24:U26"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="U36:U37"/>
+    <mergeCell ref="T36:T37"/>
+    <mergeCell ref="T51:T53"/>
+    <mergeCell ref="U51:U53"/>
+    <mergeCell ref="T47:T48"/>
+    <mergeCell ref="U47:U48"/>
+    <mergeCell ref="T40:T41"/>
+    <mergeCell ref="U40:U41"/>
+    <mergeCell ref="S31:S32"/>
+    <mergeCell ref="T31:T32"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="K63:K64"/>
+    <mergeCell ref="J63:J64"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="M60:M62"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="N60:N62"/>
+    <mergeCell ref="O69:O70"/>
+    <mergeCell ref="P69:P70"/>
+    <mergeCell ref="N74:N75"/>
+    <mergeCell ref="M65:M66"/>
+    <mergeCell ref="N63:N64"/>
+    <mergeCell ref="M63:M64"/>
+    <mergeCell ref="L63:L64"/>
+    <mergeCell ref="O60:O62"/>
+    <mergeCell ref="N71:N73"/>
+    <mergeCell ref="O71:O73"/>
+    <mergeCell ref="P71:P73"/>
+    <mergeCell ref="M74:M75"/>
+    <mergeCell ref="K74:K75"/>
+    <mergeCell ref="L74:L75"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="O63:O64"/>
+    <mergeCell ref="N65:N66"/>
+    <mergeCell ref="G71:G73"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="J65:J66"/>
+    <mergeCell ref="K65:K66"/>
+    <mergeCell ref="L65:L66"/>
+    <mergeCell ref="H80:H82"/>
+    <mergeCell ref="I80:I82"/>
+    <mergeCell ref="J80:J82"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="L69:L70"/>
+    <mergeCell ref="N78:N79"/>
+    <mergeCell ref="J78:J79"/>
+    <mergeCell ref="I78:I79"/>
+    <mergeCell ref="H78:H79"/>
+    <mergeCell ref="I76:I77"/>
+    <mergeCell ref="J76:J77"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="I74:I75"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="K71:K73"/>
+    <mergeCell ref="L71:L73"/>
+    <mergeCell ref="M71:M73"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="D60:D62"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F4:O30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="O36:O37"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="N56:N57"/>
+    <mergeCell ref="O56:O57"/>
+    <mergeCell ref="N33:N35"/>
+    <mergeCell ref="O33:O35"/>
+    <mergeCell ref="N38:N39"/>
+    <mergeCell ref="O38:O39"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="N54:N55"/>
+    <mergeCell ref="B13:B21"/>
+    <mergeCell ref="B22:B30"/>
+    <mergeCell ref="B31:B39"/>
+    <mergeCell ref="B40:B48"/>
+    <mergeCell ref="B49:B57"/>
+    <mergeCell ref="B58:B66"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="N31:N32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="H33:H35"/>
+    <mergeCell ref="J60:J62"/>
+    <mergeCell ref="K60:K62"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="A58:A66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F69:F77"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="H76:H77"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="G60:G62"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="B4:B12"/>
     <mergeCell ref="O42:O44"/>
     <mergeCell ref="K58:K59"/>
     <mergeCell ref="L58:L59"/>
@@ -5667,493 +6137,23 @@
     <mergeCell ref="O74:O75"/>
     <mergeCell ref="P65:P66"/>
     <mergeCell ref="L60:L62"/>
-    <mergeCell ref="A58:A66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="F69:F77"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="H76:H77"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="G60:G62"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="B4:B12"/>
-    <mergeCell ref="E65:E66"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="N45:N46"/>
-    <mergeCell ref="N54:N55"/>
-    <mergeCell ref="B13:B21"/>
-    <mergeCell ref="B22:B30"/>
-    <mergeCell ref="B31:B39"/>
-    <mergeCell ref="B40:B48"/>
-    <mergeCell ref="B49:B57"/>
-    <mergeCell ref="B58:B66"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="N31:N32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="H33:H35"/>
-    <mergeCell ref="J60:J62"/>
-    <mergeCell ref="K60:K62"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="K36:K37"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="D60:D62"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F4:O30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="F33:F35"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="O36:O37"/>
-    <mergeCell ref="N36:N37"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="N56:N57"/>
-    <mergeCell ref="O56:O57"/>
-    <mergeCell ref="N33:N35"/>
-    <mergeCell ref="O33:O35"/>
-    <mergeCell ref="N38:N39"/>
-    <mergeCell ref="O38:O39"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="J65:J66"/>
-    <mergeCell ref="K65:K66"/>
-    <mergeCell ref="L65:L66"/>
-    <mergeCell ref="H80:H82"/>
-    <mergeCell ref="I80:I82"/>
-    <mergeCell ref="J80:J82"/>
-    <mergeCell ref="H74:H75"/>
-    <mergeCell ref="L69:L70"/>
-    <mergeCell ref="N78:N79"/>
-    <mergeCell ref="J78:J79"/>
-    <mergeCell ref="I78:I79"/>
-    <mergeCell ref="H78:H79"/>
-    <mergeCell ref="I76:I77"/>
-    <mergeCell ref="J76:J77"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="J74:J75"/>
-    <mergeCell ref="I74:I75"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="K71:K73"/>
-    <mergeCell ref="L71:L73"/>
-    <mergeCell ref="M71:M73"/>
-    <mergeCell ref="M60:M62"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="N60:N62"/>
-    <mergeCell ref="O69:O70"/>
-    <mergeCell ref="P69:P70"/>
-    <mergeCell ref="N74:N75"/>
-    <mergeCell ref="M65:M66"/>
-    <mergeCell ref="N63:N64"/>
-    <mergeCell ref="M63:M64"/>
-    <mergeCell ref="L63:L64"/>
-    <mergeCell ref="O60:O62"/>
-    <mergeCell ref="N71:N73"/>
-    <mergeCell ref="O71:O73"/>
-    <mergeCell ref="P71:P73"/>
-    <mergeCell ref="M74:M75"/>
-    <mergeCell ref="K74:K75"/>
-    <mergeCell ref="L74:L75"/>
-    <mergeCell ref="P74:P75"/>
-    <mergeCell ref="O63:O64"/>
-    <mergeCell ref="N65:N66"/>
-    <mergeCell ref="G71:G73"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="J54:J55"/>
-    <mergeCell ref="K54:K55"/>
-    <mergeCell ref="K63:K64"/>
-    <mergeCell ref="J63:J64"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="G63:G64"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="U1:U2"/>
-    <mergeCell ref="T71:T73"/>
-    <mergeCell ref="S69:S70"/>
-    <mergeCell ref="T69:T70"/>
-    <mergeCell ref="Q69:Q70"/>
-    <mergeCell ref="R69:R70"/>
-    <mergeCell ref="Q24:Q26"/>
-    <mergeCell ref="R24:R26"/>
-    <mergeCell ref="S24:S26"/>
-    <mergeCell ref="T24:T26"/>
-    <mergeCell ref="U24:U26"/>
-    <mergeCell ref="R22:R23"/>
-    <mergeCell ref="S22:S23"/>
-    <mergeCell ref="T22:T23"/>
-    <mergeCell ref="U36:U37"/>
-    <mergeCell ref="T36:T37"/>
-    <mergeCell ref="T51:T53"/>
-    <mergeCell ref="U51:U53"/>
-    <mergeCell ref="T47:T48"/>
-    <mergeCell ref="U47:U48"/>
-    <mergeCell ref="T40:T41"/>
-    <mergeCell ref="U40:U41"/>
-    <mergeCell ref="S31:S32"/>
-    <mergeCell ref="T31:T32"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="P29:P30"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="S29:S30"/>
-    <mergeCell ref="T29:T30"/>
-    <mergeCell ref="U29:U30"/>
-    <mergeCell ref="P24:P26"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="U18:U19"/>
-    <mergeCell ref="T18:T19"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="R18:R19"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="U22:U23"/>
-    <mergeCell ref="R15:R17"/>
-    <mergeCell ref="S15:S17"/>
-    <mergeCell ref="T15:T17"/>
-    <mergeCell ref="U15:U17"/>
-    <mergeCell ref="T27:T28"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="T85:T86"/>
-    <mergeCell ref="U80:U82"/>
-    <mergeCell ref="U85:U86"/>
-    <mergeCell ref="M85:M86"/>
-    <mergeCell ref="N85:N86"/>
-    <mergeCell ref="O85:O86"/>
-    <mergeCell ref="P85:P86"/>
-    <mergeCell ref="Q85:Q86"/>
-    <mergeCell ref="R85:R86"/>
-    <mergeCell ref="R80:R82"/>
-    <mergeCell ref="S80:S82"/>
-    <mergeCell ref="T80:T82"/>
-    <mergeCell ref="O80:O82"/>
-    <mergeCell ref="P83:P84"/>
-    <mergeCell ref="O83:O84"/>
-    <mergeCell ref="U83:U84"/>
-    <mergeCell ref="T83:T84"/>
-    <mergeCell ref="S83:S84"/>
-    <mergeCell ref="R83:R84"/>
-    <mergeCell ref="Q83:Q84"/>
-    <mergeCell ref="Q80:Q82"/>
-    <mergeCell ref="M83:M84"/>
-    <mergeCell ref="N83:N84"/>
-    <mergeCell ref="S85:S86"/>
-    <mergeCell ref="K80:K82"/>
-    <mergeCell ref="L80:L82"/>
-    <mergeCell ref="M80:M82"/>
-    <mergeCell ref="N80:N82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="J83:J84"/>
-    <mergeCell ref="K83:K84"/>
-    <mergeCell ref="L83:L84"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="K85:K86"/>
-    <mergeCell ref="L85:L86"/>
-    <mergeCell ref="P80:P82"/>
-    <mergeCell ref="P20:P21"/>
-    <mergeCell ref="Q20:Q21"/>
-    <mergeCell ref="R20:R21"/>
-    <mergeCell ref="S20:S21"/>
-    <mergeCell ref="T20:T21"/>
-    <mergeCell ref="U20:U21"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="Q15:Q17"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="P22:P23"/>
-    <mergeCell ref="Q22:Q23"/>
-    <mergeCell ref="T33:T35"/>
-    <mergeCell ref="U33:U35"/>
-    <mergeCell ref="P31:P32"/>
-    <mergeCell ref="Q31:Q32"/>
-    <mergeCell ref="R31:R32"/>
-    <mergeCell ref="P27:P28"/>
-    <mergeCell ref="T65:T66"/>
-    <mergeCell ref="U65:U66"/>
-    <mergeCell ref="U63:U64"/>
-    <mergeCell ref="T63:T64"/>
-    <mergeCell ref="P38:P39"/>
-    <mergeCell ref="Q38:Q39"/>
-    <mergeCell ref="R38:R39"/>
-    <mergeCell ref="S38:S39"/>
-    <mergeCell ref="T38:T39"/>
-    <mergeCell ref="U38:U39"/>
-    <mergeCell ref="S54:S55"/>
-    <mergeCell ref="R54:R55"/>
-    <mergeCell ref="Q54:Q55"/>
-    <mergeCell ref="U45:U46"/>
-    <mergeCell ref="T45:T46"/>
-    <mergeCell ref="S45:S46"/>
-    <mergeCell ref="T58:T59"/>
-    <mergeCell ref="U58:U59"/>
-    <mergeCell ref="P60:P62"/>
-    <mergeCell ref="P36:P37"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="T60:T62"/>
-    <mergeCell ref="U60:U62"/>
-    <mergeCell ref="T42:T44"/>
-    <mergeCell ref="U42:U44"/>
-    <mergeCell ref="R40:R41"/>
-    <mergeCell ref="S40:S41"/>
-    <mergeCell ref="T56:T57"/>
-    <mergeCell ref="U56:U57"/>
-    <mergeCell ref="T49:T50"/>
-    <mergeCell ref="U49:U50"/>
-    <mergeCell ref="U31:U32"/>
-    <mergeCell ref="Q27:Q28"/>
-    <mergeCell ref="R33:R35"/>
-    <mergeCell ref="S33:S35"/>
-    <mergeCell ref="S36:S37"/>
-    <mergeCell ref="R36:R37"/>
-    <mergeCell ref="Q36:Q37"/>
-    <mergeCell ref="N58:N59"/>
-    <mergeCell ref="O58:O59"/>
-    <mergeCell ref="P58:P59"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="R58:R59"/>
-    <mergeCell ref="S58:S59"/>
-    <mergeCell ref="P33:P35"/>
-    <mergeCell ref="Q33:Q35"/>
-    <mergeCell ref="P54:P55"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="O54:O55"/>
-    <mergeCell ref="P56:P57"/>
-    <mergeCell ref="Q56:Q57"/>
-    <mergeCell ref="R56:R57"/>
-    <mergeCell ref="S56:S57"/>
-    <mergeCell ref="R42:R44"/>
-    <mergeCell ref="S42:S44"/>
-    <mergeCell ref="P42:P44"/>
-    <mergeCell ref="Q42:Q44"/>
-    <mergeCell ref="N40:N41"/>
-    <mergeCell ref="O40:O41"/>
-    <mergeCell ref="P40:P41"/>
-    <mergeCell ref="Q40:Q41"/>
-    <mergeCell ref="Q65:Q66"/>
-    <mergeCell ref="R65:R66"/>
-    <mergeCell ref="S65:S66"/>
-    <mergeCell ref="R49:R50"/>
-    <mergeCell ref="S49:S50"/>
-    <mergeCell ref="P47:P48"/>
-    <mergeCell ref="Q47:Q48"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="P45:P46"/>
-    <mergeCell ref="Q60:Q62"/>
-    <mergeCell ref="R60:R62"/>
-    <mergeCell ref="S60:S62"/>
-    <mergeCell ref="P63:P64"/>
-    <mergeCell ref="S63:S64"/>
-    <mergeCell ref="R63:R64"/>
-    <mergeCell ref="Q63:Q64"/>
-    <mergeCell ref="R45:R46"/>
-    <mergeCell ref="Q45:Q46"/>
-    <mergeCell ref="N51:N53"/>
-    <mergeCell ref="O51:O53"/>
-    <mergeCell ref="P51:P53"/>
-    <mergeCell ref="Q51:Q53"/>
-    <mergeCell ref="R51:R53"/>
-    <mergeCell ref="S51:S53"/>
-    <mergeCell ref="U54:U55"/>
-    <mergeCell ref="T54:T55"/>
-    <mergeCell ref="S47:S48"/>
-    <mergeCell ref="N49:N50"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P49:P50"/>
-    <mergeCell ref="Q49:Q50"/>
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="L56:L57"/>
-    <mergeCell ref="M56:M57"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="K49:K50"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="J51:J53"/>
-    <mergeCell ref="K51:K53"/>
-    <mergeCell ref="L51:L53"/>
-    <mergeCell ref="M51:M53"/>
-    <mergeCell ref="J56:J57"/>
-    <mergeCell ref="K56:K57"/>
-    <mergeCell ref="M54:M55"/>
-    <mergeCell ref="L54:L55"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I35"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="J33:J35"/>
-    <mergeCell ref="K33:K35"/>
-    <mergeCell ref="L33:L35"/>
-    <mergeCell ref="M33:M35"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="K40:K41"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="J42:J44"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="M45:M46"/>
-    <mergeCell ref="L45:L46"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H42:H44"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="L42:L44"/>
-    <mergeCell ref="M42:M44"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="L38:L39"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I42:I44"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="E60:E62"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="I51:I53"/>
-    <mergeCell ref="I56:I57"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="I60:I62"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="H51:H53"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="H60:H62"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="F49:F57"/>
-    <mergeCell ref="F58:F66"/>
-    <mergeCell ref="Q89:R90"/>
-    <mergeCell ref="Q93:R94"/>
-    <mergeCell ref="T89:U90"/>
-    <mergeCell ref="T93:U94"/>
-    <mergeCell ref="A113:U113"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="A4:A12"/>
-    <mergeCell ref="A13:A21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="A31:A39"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="A49:A57"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="E51:E53"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="D80:D82"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="H89:I90"/>
-    <mergeCell ref="H93:I94"/>
-    <mergeCell ref="K89:L90"/>
-    <mergeCell ref="K93:L94"/>
-    <mergeCell ref="N89:O90"/>
-    <mergeCell ref="N93:O94"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="G80:G82"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="E80:E82"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F78:F86"/>
-    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="U78:U79"/>
+    <mergeCell ref="U76:U77"/>
+    <mergeCell ref="U71:U73"/>
+    <mergeCell ref="U69:U70"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="R74:R75"/>
+    <mergeCell ref="S74:S75"/>
+    <mergeCell ref="T74:T75"/>
+    <mergeCell ref="U74:U75"/>
+    <mergeCell ref="R78:R79"/>
+    <mergeCell ref="T76:T77"/>
+    <mergeCell ref="S76:S77"/>
+    <mergeCell ref="T78:T79"/>
+    <mergeCell ref="S78:S79"/>
+    <mergeCell ref="Q71:Q73"/>
+    <mergeCell ref="R71:R73"/>
+    <mergeCell ref="S71:S73"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="27" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -6162,7 +6162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE1F860-D8D1-477E-9869-3C897E940DEF}">
-  <dimension ref="B2:P25"/>
+  <dimension ref="B4:P27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -6175,302 +6175,250 @@
     <col min="12" max="12" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
+    <row r="4" spans="2:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="122" t="s">
         <v>271</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="I2" s="30" t="s">
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="I4" s="123" t="s">
         <v>275</v>
       </c>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-    </row>
-    <row r="3" spans="2:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-    </row>
-    <row r="4" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="21" t="s">
+      <c r="J4" s="123"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="123"/>
+      <c r="N4" s="123"/>
+    </row>
+    <row r="5" spans="2:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+    </row>
+    <row r="6" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C6" s="124" t="s">
         <v>254</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="21" t="s">
+      <c r="D6" s="124"/>
+      <c r="E6" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F6" s="121" t="s">
         <v>256</v>
       </c>
-      <c r="G4" s="33"/>
-      <c r="I4" s="24" t="s">
+      <c r="G6" s="121"/>
+      <c r="I6" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J6" s="24" t="s">
         <v>254</v>
       </c>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24" t="s">
+      <c r="K6" s="24"/>
+      <c r="L6" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="M4" s="35" t="s">
+      <c r="M6" s="125" t="s">
         <v>256</v>
       </c>
-      <c r="N4" s="36"/>
-    </row>
-    <row r="5" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
+      <c r="N6" s="126"/>
+    </row>
+    <row r="7" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C7" s="22">
         <v>1</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D7" s="22" t="s">
         <v>258</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E7" s="22">
         <f>tabela_periodica!Q20</f>
         <v>12.010999999999999</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F7" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="G5" s="22">
-        <f>C5*E5</f>
+      <c r="G7" s="22">
+        <f>C7*E7</f>
         <v>12.010999999999999</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="I7" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26" t="s">
+      <c r="J7" s="26"/>
+      <c r="K7" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26" t="s">
+      <c r="L7" s="26"/>
+      <c r="M7" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="N5" s="26"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-    </row>
-    <row r="6" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
+      <c r="N7" s="26"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+    </row>
+    <row r="8" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C8" s="22">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D8" s="22" t="s">
         <v>258</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E8" s="22">
         <f>tabela_periodica!S20</f>
         <v>15.999000000000001</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F8" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="G6" s="22">
-        <f>C6*E6</f>
+      <c r="G8" s="22">
+        <f>C8*E8</f>
         <v>31.998000000000001</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I8" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26" t="s">
+      <c r="J8" s="26"/>
+      <c r="K8" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26" t="s">
+      <c r="L8" s="26"/>
+      <c r="M8" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="N6" s="26"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-    </row>
-    <row r="7" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="G7" s="29">
-        <f>SUM(G5:G6)</f>
-        <v>44.009</v>
-      </c>
-      <c r="I7" s="31" t="s">
-        <v>276</v>
-      </c>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="N7" s="28"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-    </row>
-    <row r="8" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
+      <c r="N8" s="26"/>
       <c r="O8" s="18"/>
       <c r="P8" s="18"/>
     </row>
-    <row r="9" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-    </row>
-    <row r="10" spans="2:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="B10" s="34" t="s">
+    <row r="9" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="121" t="s">
+        <v>277</v>
+      </c>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="G9" s="29">
+        <f>SUM(G7:G8)</f>
+        <v>44.009</v>
+      </c>
+      <c r="I9" s="120" t="s">
+        <v>276</v>
+      </c>
+      <c r="J9" s="120"/>
+      <c r="K9" s="120"/>
+      <c r="L9" s="120"/>
+      <c r="M9" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="N9" s="28"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+    </row>
+    <row r="10" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+    </row>
+    <row r="11" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:16" ht="21" x14ac:dyDescent="0.35">
+      <c r="B12" s="122" t="s">
         <v>272</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="I10" s="30" t="s">
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="I12" s="123" t="s">
         <v>273</v>
       </c>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-    </row>
-    <row r="11" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-    </row>
-    <row r="12" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="21" t="s">
+      <c r="J12" s="123"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="123"/>
+      <c r="M12" s="123"/>
+      <c r="N12" s="123"/>
+    </row>
+    <row r="13" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+    </row>
+    <row r="14" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C14" s="124" t="s">
         <v>254</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="21" t="s">
+      <c r="D14" s="124"/>
+      <c r="E14" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="F14" s="121" t="s">
         <v>256</v>
       </c>
-      <c r="G12" s="33"/>
-      <c r="I12" s="24" t="s">
+      <c r="G14" s="121"/>
+      <c r="I14" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J14" s="24" t="s">
         <v>254</v>
       </c>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24" t="s">
+      <c r="K14" s="24"/>
+      <c r="L14" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="M12" s="35" t="s">
+      <c r="M14" s="125" t="s">
         <v>256</v>
       </c>
-      <c r="N12" s="36"/>
-    </row>
-    <row r="13" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="G13" s="22"/>
-      <c r="I13" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="N13" s="26"/>
-    </row>
-    <row r="14" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="G14" s="22"/>
-      <c r="I14" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="N14" s="26"/>
+      <c r="N14" s="126"/>
     </row>
     <row r="15" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22" t="s">
@@ -6482,7 +6430,7 @@
       </c>
       <c r="G15" s="22"/>
       <c r="I15" s="28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J15" s="26"/>
       <c r="K15" s="26" t="s">
@@ -6495,144 +6443,144 @@
       <c r="N15" s="26"/>
     </row>
     <row r="16" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="33" t="s">
-        <v>278</v>
-      </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
+      <c r="B16" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="E16" s="22"/>
       <c r="F16" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="G16" s="19"/>
-      <c r="I16" s="31" t="s">
-        <v>274</v>
-      </c>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
+      <c r="G16" s="22"/>
+      <c r="I16" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="L16" s="26"/>
       <c r="M16" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="N16" s="28"/>
-    </row>
-    <row r="19" spans="2:14" ht="21" x14ac:dyDescent="0.35">
-      <c r="B19" s="30" t="s">
+      <c r="N16" s="26"/>
+    </row>
+    <row r="17" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="G17" s="22"/>
+      <c r="I17" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="N17" s="26"/>
+    </row>
+    <row r="18" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="121" t="s">
+        <v>278</v>
+      </c>
+      <c r="C18" s="121"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="G18" s="19"/>
+      <c r="I18" s="120" t="s">
+        <v>274</v>
+      </c>
+      <c r="J18" s="120"/>
+      <c r="K18" s="120"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="N18" s="28"/>
+    </row>
+    <row r="21" spans="2:14" ht="21" x14ac:dyDescent="0.35">
+      <c r="B21" s="123" t="s">
         <v>279</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="I19" s="30" t="s">
+      <c r="C21" s="123"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="123"/>
+      <c r="I21" s="123" t="s">
         <v>281</v>
       </c>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-    </row>
-    <row r="20" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-    </row>
-    <row r="21" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="24" t="s">
+      <c r="J21" s="123"/>
+      <c r="K21" s="123"/>
+      <c r="L21" s="123"/>
+      <c r="M21" s="123"/>
+      <c r="N21" s="123"/>
+    </row>
+    <row r="22" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+    </row>
+    <row r="23" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C23" s="24" t="s">
         <v>254</v>
       </c>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24" t="s">
+      <c r="D23" s="24"/>
+      <c r="E23" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F23" s="127" t="s">
         <v>256</v>
       </c>
-      <c r="G21" s="38"/>
-      <c r="I21" s="24" t="s">
+      <c r="G23" s="128"/>
+      <c r="I23" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="J21" s="24" t="s">
+      <c r="J23" s="24" t="s">
         <v>254</v>
       </c>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24" t="s">
+      <c r="K23" s="24"/>
+      <c r="L23" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="M21" s="24" t="s">
+      <c r="M23" s="24" t="s">
         <v>256</v>
       </c>
-      <c r="N21" s="25"/>
-    </row>
-    <row r="22" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="G22" s="26"/>
-      <c r="I22" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="N22" s="26"/>
-    </row>
-    <row r="23" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="G23" s="26"/>
-      <c r="I23" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="N23" s="26"/>
+      <c r="N23" s="25"/>
     </row>
     <row r="24" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="26" t="s">
@@ -6644,7 +6592,7 @@
       </c>
       <c r="G24" s="26"/>
       <c r="I24" s="28" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="J24" s="26"/>
       <c r="K24" s="26" t="s">
@@ -6657,48 +6605,100 @@
       <c r="N24" s="26"/>
     </row>
     <row r="25" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
+      <c r="B25" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="E25" s="26"/>
       <c r="F25" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="G25" s="28"/>
-      <c r="I25" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
+      <c r="G25" s="26"/>
+      <c r="I25" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="L25" s="26"/>
       <c r="M25" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="N25" s="28"/>
+      <c r="N25" s="26"/>
+    </row>
+    <row r="26" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="G26" s="26"/>
+      <c r="I26" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="N26" s="26"/>
+    </row>
+    <row r="27" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="120" t="s">
+        <v>280</v>
+      </c>
+      <c r="C27" s="120"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="G27" s="28"/>
+      <c r="I27" s="120" t="s">
+        <v>282</v>
+      </c>
+      <c r="J27" s="120"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="120"/>
+      <c r="M27" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="N27" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="I10:N10"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="I2:N2"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="I12:N12"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I21:N21"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="F23:G23"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
